--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY111"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14202,6 +14202,1243 @@
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>122485589</v>
+      </c>
+      <c r="B112" t="n">
+        <v>98240</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Väst Sothällen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>563487</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6626901</v>
+      </c>
+      <c r="S112" t="n">
+        <v>25</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>122485586</v>
+      </c>
+      <c r="B113" t="n">
+        <v>100506</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Väst Sothällen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>564170</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6626836</v>
+      </c>
+      <c r="S113" t="n">
+        <v>25</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>Äldre barrskog, fuktstråk</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>122485583</v>
+      </c>
+      <c r="B114" t="n">
+        <v>94904</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Väst Sothällen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>563793</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6626760</v>
+      </c>
+      <c r="S114" t="n">
+        <v>25</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>Äldre barrskog, fyktig ristyp</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Murken tallved</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>122485578</v>
+      </c>
+      <c r="B115" t="n">
+        <v>90218</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Väst Sothällen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>563356</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6626854</v>
+      </c>
+      <c r="S115" t="n">
+        <v>25</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Liggande tallstam</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>122485582</v>
+      </c>
+      <c r="B116" t="n">
+        <v>91124</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>658</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Väst Sothällen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>564072</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6626685</v>
+      </c>
+      <c r="S116" t="n">
+        <v>25</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>122485588</v>
+      </c>
+      <c r="B117" t="n">
+        <v>98240</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Väst Sothällen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>564140</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6626788</v>
+      </c>
+      <c r="S117" t="n">
+        <v>25</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>Äldre barrskog,</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>122485580</v>
+      </c>
+      <c r="B118" t="n">
+        <v>92114</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Väst Sothällen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>563671</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6626790</v>
+      </c>
+      <c r="S118" t="n">
+        <v>25</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>Äldre barrskog, ristyp</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>122485585</v>
+      </c>
+      <c r="B119" t="n">
+        <v>105346</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Väst Sothällen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>564155</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6626751</v>
+      </c>
+      <c r="S119" t="n">
+        <v>25</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>122485581</v>
+      </c>
+      <c r="B120" t="n">
+        <v>92106</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Väst Sothällen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>563669</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6626870</v>
+      </c>
+      <c r="S120" t="n">
+        <v>25</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>Äldre talldominerad barrskog</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>122485579</v>
+      </c>
+      <c r="B121" t="n">
+        <v>92116</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>788</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Väst Sothällen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>563414</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6626837</v>
+      </c>
+      <c r="S121" t="n">
+        <v>25</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>122485576</v>
+      </c>
+      <c r="B122" t="n">
+        <v>92149</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Väst Sothällen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>563758</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6626923</v>
+      </c>
+      <c r="S122" t="n">
+        <v>25</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>Äldre lavtallskog, hällmark</t>
+        </is>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -14204,10 +14204,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122485589</v>
+        <v>122485582</v>
       </c>
       <c r="B112" t="n">
-        <v>98240</v>
+        <v>91124</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14216,25 +14216,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>563487</v>
+        <v>564072</v>
       </c>
       <c r="R112" t="n">
-        <v>6626901</v>
+        <v>6626685</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -14294,6 +14294,11 @@
       <c r="AI112" t="inlineStr">
         <is>
           <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14426,10 +14431,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122485583</v>
+        <v>122485576</v>
       </c>
       <c r="B114" t="n">
-        <v>94904</v>
+        <v>92149</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14438,25 +14443,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2170</v>
+        <v>5966</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14466,10 +14471,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>563793</v>
+        <v>563758</v>
       </c>
       <c r="R114" t="n">
-        <v>6626760</v>
+        <v>6626923</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14510,18 +14515,12 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fyktig ristyp</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Murken tallved</t>
+          <t>Äldre lavtallskog, hällmark</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14543,10 +14542,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122485578</v>
+        <v>122485588</v>
       </c>
       <c r="B115" t="n">
-        <v>90218</v>
+        <v>98240</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14555,25 +14554,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5685</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14583,10 +14582,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>563356</v>
+        <v>564140</v>
       </c>
       <c r="R115" t="n">
-        <v>6626854</v>
+        <v>6626788</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -14632,12 +14631,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Liggande tallstam</t>
+          <t>Äldre barrskog,</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -14659,10 +14653,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122485582</v>
+        <v>122485579</v>
       </c>
       <c r="B116" t="n">
-        <v>91124</v>
+        <v>92116</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14675,21 +14669,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>658</v>
+        <v>788</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14699,10 +14693,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>564072</v>
+        <v>563414</v>
       </c>
       <c r="R116" t="n">
-        <v>6626685</v>
+        <v>6626837</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14748,12 +14742,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14775,10 +14764,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122485588</v>
+        <v>122485581</v>
       </c>
       <c r="B117" t="n">
-        <v>98240</v>
+        <v>92106</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14787,25 +14776,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14815,10 +14804,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>564140</v>
+        <v>563669</v>
       </c>
       <c r="R117" t="n">
-        <v>6626788</v>
+        <v>6626870</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -14864,7 +14853,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Äldre barrskog,</t>
+          <t>Äldre talldominerad barrskog</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14886,10 +14875,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122485580</v>
+        <v>122485578</v>
       </c>
       <c r="B118" t="n">
-        <v>92114</v>
+        <v>90218</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14902,21 +14891,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>5685</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14926,10 +14915,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>563671</v>
+        <v>563356</v>
       </c>
       <c r="R118" t="n">
-        <v>6626790</v>
+        <v>6626854</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14975,7 +14964,12 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Äldre barrskog, ristyp</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14997,10 +14991,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122485585</v>
+        <v>122485589</v>
       </c>
       <c r="B119" t="n">
-        <v>105346</v>
+        <v>98240</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15009,25 +15003,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15037,10 +15031,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>564155</v>
+        <v>563487</v>
       </c>
       <c r="R119" t="n">
-        <v>6626751</v>
+        <v>6626901</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -15086,7 +15080,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15108,10 +15102,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122485581</v>
+        <v>122485583</v>
       </c>
       <c r="B120" t="n">
-        <v>92106</v>
+        <v>94904</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15120,25 +15114,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4361</v>
+        <v>2170</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -15148,10 +15142,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>563669</v>
+        <v>563793</v>
       </c>
       <c r="R120" t="n">
-        <v>6626870</v>
+        <v>6626760</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -15192,12 +15186,18 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Äldre talldominerad barrskog</t>
+          <t>Äldre barrskog, fyktig ristyp</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Murken tallved</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15219,10 +15219,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122485579</v>
+        <v>122485585</v>
       </c>
       <c r="B121" t="n">
-        <v>92116</v>
+        <v>105346</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15231,25 +15231,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>788</v>
+        <v>221144</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15259,10 +15259,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>563414</v>
+        <v>564155</v>
       </c>
       <c r="R121" t="n">
-        <v>6626837</v>
+        <v>6626751</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15308,7 +15308,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15330,10 +15330,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122485576</v>
+        <v>122485580</v>
       </c>
       <c r="B122" t="n">
-        <v>92149</v>
+        <v>92114</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15342,25 +15342,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -15370,10 +15370,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>563758</v>
+        <v>563671</v>
       </c>
       <c r="R122" t="n">
-        <v>6626923</v>
+        <v>6626790</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Äldre lavtallskog, hällmark</t>
+          <t>Äldre barrskog, ristyp</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -14204,10 +14204,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122485582</v>
+        <v>122485576</v>
       </c>
       <c r="B112" t="n">
-        <v>91124</v>
+        <v>92150</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14220,21 +14220,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>658</v>
+        <v>5966</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>564072</v>
+        <v>563758</v>
       </c>
       <c r="R112" t="n">
-        <v>6626685</v>
+        <v>6626923</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -14293,12 +14293,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre lavtallskog, hällmark</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14320,10 +14315,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122485586</v>
+        <v>122485585</v>
       </c>
       <c r="B113" t="n">
-        <v>100506</v>
+        <v>105347</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14336,21 +14331,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14360,10 +14355,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>564170</v>
+        <v>564155</v>
       </c>
       <c r="R113" t="n">
-        <v>6626836</v>
+        <v>6626751</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -14409,7 +14404,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14431,10 +14426,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122485576</v>
+        <v>122485579</v>
       </c>
       <c r="B114" t="n">
-        <v>92149</v>
+        <v>92117</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14447,21 +14442,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5966</v>
+        <v>788</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14471,10 +14466,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>563758</v>
+        <v>563414</v>
       </c>
       <c r="R114" t="n">
-        <v>6626923</v>
+        <v>6626837</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14520,7 +14515,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Äldre lavtallskog, hällmark</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14542,10 +14537,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122485588</v>
+        <v>122485586</v>
       </c>
       <c r="B115" t="n">
-        <v>98240</v>
+        <v>100507</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14554,25 +14549,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14582,10 +14577,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>564140</v>
+        <v>564170</v>
       </c>
       <c r="R115" t="n">
-        <v>6626788</v>
+        <v>6626836</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -14631,7 +14626,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Äldre barrskog,</t>
+          <t>Äldre barrskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -14653,10 +14648,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122485579</v>
+        <v>122485578</v>
       </c>
       <c r="B116" t="n">
-        <v>92116</v>
+        <v>90219</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14665,25 +14660,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>788</v>
+        <v>5685</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14693,10 +14688,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>563414</v>
+        <v>563356</v>
       </c>
       <c r="R116" t="n">
-        <v>6626837</v>
+        <v>6626854</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14742,7 +14737,12 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14764,10 +14764,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122485581</v>
+        <v>122485582</v>
       </c>
       <c r="B117" t="n">
-        <v>92106</v>
+        <v>91125</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14780,21 +14780,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4361</v>
+        <v>658</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14804,10 +14804,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>563669</v>
+        <v>564072</v>
       </c>
       <c r="R117" t="n">
-        <v>6626870</v>
+        <v>6626685</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -14853,7 +14853,12 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Äldre talldominerad barrskog</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14875,10 +14880,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122485578</v>
+        <v>122485580</v>
       </c>
       <c r="B118" t="n">
-        <v>90218</v>
+        <v>92115</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14891,21 +14896,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14915,10 +14920,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>563356</v>
+        <v>563671</v>
       </c>
       <c r="R118" t="n">
-        <v>6626854</v>
+        <v>6626790</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14964,12 +14969,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Liggande tallstam</t>
+          <t>Äldre barrskog, ristyp</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14994,7 +14994,7 @@
         <v>122485589</v>
       </c>
       <c r="B119" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15102,10 +15102,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122485583</v>
+        <v>122485581</v>
       </c>
       <c r="B120" t="n">
-        <v>94904</v>
+        <v>92107</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15114,25 +15114,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2170</v>
+        <v>4361</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -15142,10 +15142,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>563793</v>
+        <v>563669</v>
       </c>
       <c r="R120" t="n">
-        <v>6626760</v>
+        <v>6626870</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -15186,18 +15186,12 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fyktig ristyp</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Murken tallved</t>
+          <t>Äldre talldominerad barrskog</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15219,10 +15213,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122485585</v>
+        <v>122485588</v>
       </c>
       <c r="B121" t="n">
-        <v>105346</v>
+        <v>98241</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15231,25 +15225,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15259,10 +15253,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>564155</v>
+        <v>564140</v>
       </c>
       <c r="R121" t="n">
-        <v>6626751</v>
+        <v>6626788</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15308,7 +15302,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog,</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15330,10 +15324,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122485580</v>
+        <v>122485583</v>
       </c>
       <c r="B122" t="n">
-        <v>92114</v>
+        <v>94905</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15346,21 +15340,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -15370,10 +15364,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>563671</v>
+        <v>563793</v>
       </c>
       <c r="R122" t="n">
-        <v>6626790</v>
+        <v>6626760</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15414,12 +15408,18 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Äldre barrskog, ristyp</t>
+          <t>Äldre barrskog, fyktig ristyp</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Murken tallved</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -14204,10 +14204,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122485576</v>
+        <v>122485581</v>
       </c>
       <c r="B112" t="n">
-        <v>92150</v>
+        <v>92110</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14220,21 +14220,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>563758</v>
+        <v>563669</v>
       </c>
       <c r="R112" t="n">
-        <v>6626923</v>
+        <v>6626870</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -14293,7 +14293,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Äldre lavtallskog, hällmark</t>
+          <t>Äldre talldominerad barrskog</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14315,10 +14315,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122485585</v>
+        <v>122485586</v>
       </c>
       <c r="B113" t="n">
-        <v>105347</v>
+        <v>100510</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14331,21 +14331,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14355,10 +14355,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>564155</v>
+        <v>564170</v>
       </c>
       <c r="R113" t="n">
-        <v>6626751</v>
+        <v>6626836</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14426,10 +14426,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122485579</v>
+        <v>122485588</v>
       </c>
       <c r="B114" t="n">
-        <v>92117</v>
+        <v>98244</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14438,25 +14438,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>788</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14466,10 +14466,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>563414</v>
+        <v>564140</v>
       </c>
       <c r="R114" t="n">
-        <v>6626837</v>
+        <v>6626788</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14515,7 +14515,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre barrskog,</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14537,10 +14537,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122485586</v>
+        <v>122485583</v>
       </c>
       <c r="B115" t="n">
-        <v>100507</v>
+        <v>94908</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14553,21 +14553,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>222498</v>
+        <v>2170</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14577,10 +14577,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>564170</v>
+        <v>563793</v>
       </c>
       <c r="R115" t="n">
-        <v>6626836</v>
+        <v>6626760</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -14621,12 +14621,18 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Äldre barrskog, fyktig ristyp</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Murken tallved</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -14648,10 +14654,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122485578</v>
+        <v>122485579</v>
       </c>
       <c r="B116" t="n">
-        <v>90219</v>
+        <v>92120</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14660,25 +14666,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5685</v>
+        <v>788</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14688,10 +14694,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>563356</v>
+        <v>563414</v>
       </c>
       <c r="R116" t="n">
-        <v>6626854</v>
+        <v>6626837</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14737,12 +14743,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Liggande tallstam</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14764,10 +14765,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122485582</v>
+        <v>122485576</v>
       </c>
       <c r="B117" t="n">
-        <v>91125</v>
+        <v>92153</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14780,21 +14781,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>5966</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14804,10 +14805,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>564072</v>
+        <v>563758</v>
       </c>
       <c r="R117" t="n">
-        <v>6626685</v>
+        <v>6626923</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -14853,12 +14854,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre lavtallskog, hällmark</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14880,10 +14876,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122485580</v>
+        <v>122485589</v>
       </c>
       <c r="B118" t="n">
-        <v>92115</v>
+        <v>98244</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14892,25 +14888,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14920,10 +14916,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>563671</v>
+        <v>563487</v>
       </c>
       <c r="R118" t="n">
-        <v>6626790</v>
+        <v>6626901</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14969,7 +14965,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Äldre barrskog, ristyp</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14991,10 +14987,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122485589</v>
+        <v>122485585</v>
       </c>
       <c r="B119" t="n">
-        <v>98241</v>
+        <v>105350</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15003,25 +14999,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15031,10 +15027,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>563487</v>
+        <v>564155</v>
       </c>
       <c r="R119" t="n">
-        <v>6626901</v>
+        <v>6626751</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -15080,7 +15076,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15102,10 +15098,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122485581</v>
+        <v>122485580</v>
       </c>
       <c r="B120" t="n">
-        <v>92107</v>
+        <v>92118</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15114,25 +15110,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -15142,10 +15138,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>563669</v>
+        <v>563671</v>
       </c>
       <c r="R120" t="n">
-        <v>6626870</v>
+        <v>6626790</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -15191,7 +15187,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Äldre talldominerad barrskog</t>
+          <t>Äldre barrskog, ristyp</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15213,10 +15209,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122485588</v>
+        <v>122485582</v>
       </c>
       <c r="B121" t="n">
-        <v>98241</v>
+        <v>91128</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15225,25 +15221,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15253,10 +15249,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>564140</v>
+        <v>564072</v>
       </c>
       <c r="R121" t="n">
-        <v>6626788</v>
+        <v>6626685</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15302,7 +15298,12 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Äldre barrskog,</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15324,10 +15325,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122485583</v>
+        <v>122485578</v>
       </c>
       <c r="B122" t="n">
-        <v>94905</v>
+        <v>90222</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15340,21 +15341,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2170</v>
+        <v>5685</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -15364,10 +15365,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>563793</v>
+        <v>563356</v>
       </c>
       <c r="R122" t="n">
-        <v>6626760</v>
+        <v>6626854</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15408,18 +15409,17 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fyktig ristyp</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Murken tallved</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -14204,10 +14204,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122485581</v>
+        <v>122485589</v>
       </c>
       <c r="B112" t="n">
-        <v>92110</v>
+        <v>98244</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14216,25 +14216,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>563669</v>
+        <v>563487</v>
       </c>
       <c r="R112" t="n">
-        <v>6626870</v>
+        <v>6626901</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -14293,7 +14293,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Äldre talldominerad barrskog</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14315,10 +14315,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122485586</v>
+        <v>122485580</v>
       </c>
       <c r="B113" t="n">
-        <v>100510</v>
+        <v>92118</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14331,21 +14331,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14355,10 +14355,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>564170</v>
+        <v>563671</v>
       </c>
       <c r="R113" t="n">
-        <v>6626836</v>
+        <v>6626790</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Äldre barrskog, ristyp</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14426,10 +14426,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122485588</v>
+        <v>122485586</v>
       </c>
       <c r="B114" t="n">
-        <v>98244</v>
+        <v>100510</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14438,25 +14438,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14466,10 +14466,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>564140</v>
+        <v>564170</v>
       </c>
       <c r="R114" t="n">
-        <v>6626788</v>
+        <v>6626836</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14515,7 +14515,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Äldre barrskog,</t>
+          <t>Äldre barrskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14537,10 +14537,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122485583</v>
+        <v>122485588</v>
       </c>
       <c r="B115" t="n">
-        <v>94908</v>
+        <v>98244</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14549,25 +14549,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14577,10 +14577,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>563793</v>
+        <v>564140</v>
       </c>
       <c r="R115" t="n">
-        <v>6626760</v>
+        <v>6626788</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -14621,18 +14621,12 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fyktig ristyp</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Murken tallved</t>
+          <t>Äldre barrskog,</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -14654,10 +14648,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122485579</v>
+        <v>122485583</v>
       </c>
       <c r="B116" t="n">
-        <v>92120</v>
+        <v>94908</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14666,25 +14660,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>788</v>
+        <v>2170</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14694,10 +14688,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>563414</v>
+        <v>563793</v>
       </c>
       <c r="R116" t="n">
-        <v>6626837</v>
+        <v>6626760</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14738,12 +14732,18 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre barrskog, fyktig ristyp</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Murken tallved</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14876,10 +14876,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122485589</v>
+        <v>122485582</v>
       </c>
       <c r="B118" t="n">
-        <v>98244</v>
+        <v>91128</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14888,25 +14888,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14916,10 +14916,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>563487</v>
+        <v>564072</v>
       </c>
       <c r="R118" t="n">
-        <v>6626901</v>
+        <v>6626685</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14966,6 +14966,11 @@
       <c r="AI118" t="inlineStr">
         <is>
           <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15098,10 +15103,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122485580</v>
+        <v>122485581</v>
       </c>
       <c r="B120" t="n">
-        <v>92118</v>
+        <v>92110</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15110,25 +15115,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -15138,10 +15143,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>563671</v>
+        <v>563669</v>
       </c>
       <c r="R120" t="n">
-        <v>6626790</v>
+        <v>6626870</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -15187,7 +15192,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Äldre barrskog, ristyp</t>
+          <t>Äldre talldominerad barrskog</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15209,10 +15214,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122485582</v>
+        <v>122485579</v>
       </c>
       <c r="B121" t="n">
-        <v>91128</v>
+        <v>92120</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15225,21 +15230,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>658</v>
+        <v>788</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15249,10 +15254,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>564072</v>
+        <v>563414</v>
       </c>
       <c r="R121" t="n">
-        <v>6626685</v>
+        <v>6626837</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15298,12 +15303,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -15214,10 +15214,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122485579</v>
+        <v>122485578</v>
       </c>
       <c r="B121" t="n">
-        <v>92120</v>
+        <v>90222</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15226,25 +15226,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>788</v>
+        <v>5685</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15254,10 +15254,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>563414</v>
+        <v>563356</v>
       </c>
       <c r="R121" t="n">
-        <v>6626837</v>
+        <v>6626854</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15303,7 +15303,12 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15325,10 +15330,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122485578</v>
+        <v>122485579</v>
       </c>
       <c r="B122" t="n">
-        <v>90222</v>
+        <v>92120</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15337,25 +15342,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5685</v>
+        <v>788</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -15365,10 +15370,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>563356</v>
+        <v>563414</v>
       </c>
       <c r="R122" t="n">
-        <v>6626854</v>
+        <v>6626837</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15414,12 +15419,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Liggande tallstam</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -15214,10 +15214,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122485578</v>
+        <v>122485579</v>
       </c>
       <c r="B121" t="n">
-        <v>90222</v>
+        <v>92120</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15226,25 +15226,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5685</v>
+        <v>788</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15254,10 +15254,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>563356</v>
+        <v>563414</v>
       </c>
       <c r="R121" t="n">
-        <v>6626854</v>
+        <v>6626837</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15303,12 +15303,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Liggande tallstam</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15330,10 +15325,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122485579</v>
+        <v>122485578</v>
       </c>
       <c r="B122" t="n">
-        <v>92120</v>
+        <v>90222</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15342,25 +15337,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>788</v>
+        <v>5685</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -15370,10 +15365,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>563414</v>
+        <v>563356</v>
       </c>
       <c r="R122" t="n">
-        <v>6626837</v>
+        <v>6626854</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15419,7 +15414,12 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -14204,10 +14204,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122485589</v>
+        <v>122485586</v>
       </c>
       <c r="B112" t="n">
-        <v>98244</v>
+        <v>100510</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14216,25 +14216,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>563487</v>
+        <v>564170</v>
       </c>
       <c r="R112" t="n">
-        <v>6626901</v>
+        <v>6626836</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -14293,7 +14293,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
+          <t>Äldre barrskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14315,10 +14315,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122485580</v>
+        <v>122485589</v>
       </c>
       <c r="B113" t="n">
-        <v>92118</v>
+        <v>98244</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14327,25 +14327,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14355,10 +14355,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>563671</v>
+        <v>563487</v>
       </c>
       <c r="R113" t="n">
-        <v>6626790</v>
+        <v>6626901</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Äldre barrskog, ristyp</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14426,10 +14426,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122485586</v>
+        <v>122485580</v>
       </c>
       <c r="B114" t="n">
-        <v>100510</v>
+        <v>92118</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14442,21 +14442,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14466,10 +14466,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>564170</v>
+        <v>563671</v>
       </c>
       <c r="R114" t="n">
-        <v>6626836</v>
+        <v>6626790</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14515,7 +14515,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Äldre barrskog, ristyp</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -14204,10 +14204,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122485586</v>
+        <v>122485589</v>
       </c>
       <c r="B112" t="n">
-        <v>100510</v>
+        <v>98244</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14216,25 +14216,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>564170</v>
+        <v>563487</v>
       </c>
       <c r="R112" t="n">
-        <v>6626836</v>
+        <v>6626901</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -14293,7 +14293,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14315,10 +14315,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122485589</v>
+        <v>122485580</v>
       </c>
       <c r="B113" t="n">
-        <v>98244</v>
+        <v>92118</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14327,25 +14327,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14355,10 +14355,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>563487</v>
+        <v>563671</v>
       </c>
       <c r="R113" t="n">
-        <v>6626901</v>
+        <v>6626790</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
+          <t>Äldre barrskog, ristyp</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14426,10 +14426,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122485580</v>
+        <v>122485586</v>
       </c>
       <c r="B114" t="n">
-        <v>92118</v>
+        <v>100510</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14442,21 +14442,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14466,10 +14466,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>563671</v>
+        <v>564170</v>
       </c>
       <c r="R114" t="n">
-        <v>6626790</v>
+        <v>6626836</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14515,7 +14515,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Äldre barrskog, ristyp</t>
+          <t>Äldre barrskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -14204,10 +14204,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122485589</v>
+        <v>122485585</v>
       </c>
       <c r="B112" t="n">
-        <v>98244</v>
+        <v>105453</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14216,25 +14216,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>563487</v>
+        <v>564155</v>
       </c>
       <c r="R112" t="n">
-        <v>6626901</v>
+        <v>6626751</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -14293,7 +14293,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14315,10 +14315,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122485580</v>
+        <v>122485589</v>
       </c>
       <c r="B113" t="n">
-        <v>92118</v>
+        <v>98347</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14327,25 +14327,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14355,10 +14355,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>563671</v>
+        <v>563487</v>
       </c>
       <c r="R113" t="n">
-        <v>6626790</v>
+        <v>6626901</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Äldre barrskog, ristyp</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14426,10 +14426,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122485586</v>
+        <v>122485582</v>
       </c>
       <c r="B114" t="n">
-        <v>100510</v>
+        <v>91231</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14438,25 +14438,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14466,10 +14466,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>564170</v>
+        <v>564072</v>
       </c>
       <c r="R114" t="n">
-        <v>6626836</v>
+        <v>6626685</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14515,7 +14515,12 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14537,10 +14542,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122485588</v>
+        <v>122485576</v>
       </c>
       <c r="B115" t="n">
-        <v>98244</v>
+        <v>92256</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14549,25 +14554,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14577,10 +14582,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>564140</v>
+        <v>563758</v>
       </c>
       <c r="R115" t="n">
-        <v>6626788</v>
+        <v>6626923</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -14626,7 +14631,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Äldre barrskog,</t>
+          <t>Äldre lavtallskog, hällmark</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -14648,10 +14653,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122485583</v>
+        <v>122485580</v>
       </c>
       <c r="B116" t="n">
-        <v>94908</v>
+        <v>92221</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14664,21 +14669,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14688,10 +14693,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>563793</v>
+        <v>563671</v>
       </c>
       <c r="R116" t="n">
-        <v>6626760</v>
+        <v>6626790</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14732,18 +14737,12 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fyktig ristyp</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Murken tallved</t>
+          <t>Äldre barrskog, ristyp</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14765,10 +14764,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122485576</v>
+        <v>122485581</v>
       </c>
       <c r="B117" t="n">
-        <v>92153</v>
+        <v>92213</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14781,21 +14780,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14805,10 +14804,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>563758</v>
+        <v>563669</v>
       </c>
       <c r="R117" t="n">
-        <v>6626923</v>
+        <v>6626870</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -14854,7 +14853,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Äldre lavtallskog, hällmark</t>
+          <t>Äldre talldominerad barrskog</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14876,10 +14875,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122485582</v>
+        <v>122485588</v>
       </c>
       <c r="B118" t="n">
-        <v>91128</v>
+        <v>98347</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14888,25 +14887,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14916,10 +14915,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>564072</v>
+        <v>564140</v>
       </c>
       <c r="R118" t="n">
-        <v>6626685</v>
+        <v>6626788</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14965,12 +14964,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre barrskog,</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14992,10 +14986,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122485585</v>
+        <v>122485578</v>
       </c>
       <c r="B119" t="n">
-        <v>105350</v>
+        <v>90325</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15008,21 +15002,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221144</v>
+        <v>5685</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15032,10 +15026,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>564155</v>
+        <v>563356</v>
       </c>
       <c r="R119" t="n">
-        <v>6626751</v>
+        <v>6626854</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -15081,7 +15075,12 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15103,10 +15102,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122485581</v>
+        <v>122485586</v>
       </c>
       <c r="B120" t="n">
-        <v>92110</v>
+        <v>100613</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15115,25 +15114,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4361</v>
+        <v>222498</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -15143,10 +15142,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>563669</v>
+        <v>564170</v>
       </c>
       <c r="R120" t="n">
-        <v>6626870</v>
+        <v>6626836</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -15192,7 +15191,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Äldre talldominerad barrskog</t>
+          <t>Äldre barrskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15214,10 +15213,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122485578</v>
+        <v>122485579</v>
       </c>
       <c r="B121" t="n">
-        <v>90222</v>
+        <v>92223</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15226,25 +15225,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5685</v>
+        <v>788</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15254,10 +15253,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>563356</v>
+        <v>563414</v>
       </c>
       <c r="R121" t="n">
-        <v>6626854</v>
+        <v>6626837</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15303,12 +15302,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Liggande tallstam</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15330,10 +15324,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122485579</v>
+        <v>122485583</v>
       </c>
       <c r="B122" t="n">
-        <v>92120</v>
+        <v>95011</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15342,25 +15336,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>788</v>
+        <v>2170</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -15370,10 +15364,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>563414</v>
+        <v>563793</v>
       </c>
       <c r="R122" t="n">
-        <v>6626837</v>
+        <v>6626760</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15414,12 +15408,18 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre barrskog, fyktig ristyp</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Murken tallved</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -15102,10 +15102,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122485586</v>
+        <v>122485579</v>
       </c>
       <c r="B120" t="n">
-        <v>100613</v>
+        <v>92223</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15114,25 +15114,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>222498</v>
+        <v>788</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -15142,10 +15142,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>564170</v>
+        <v>563414</v>
       </c>
       <c r="R120" t="n">
-        <v>6626836</v>
+        <v>6626837</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15213,10 +15213,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122485579</v>
+        <v>122485586</v>
       </c>
       <c r="B121" t="n">
-        <v>92223</v>
+        <v>100613</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15225,25 +15225,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15253,10 +15253,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>563414</v>
+        <v>564170</v>
       </c>
       <c r="R121" t="n">
-        <v>6626837</v>
+        <v>6626836</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre barrskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -14204,10 +14204,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122485585</v>
+        <v>122485581</v>
       </c>
       <c r="B112" t="n">
-        <v>105453</v>
+        <v>92217</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14216,25 +14216,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221144</v>
+        <v>4361</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>564155</v>
+        <v>563669</v>
       </c>
       <c r="R112" t="n">
-        <v>6626751</v>
+        <v>6626870</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -14293,7 +14293,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre talldominerad barrskog</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14315,10 +14315,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122485589</v>
+        <v>122485578</v>
       </c>
       <c r="B113" t="n">
-        <v>98347</v>
+        <v>90329</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14327,25 +14327,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>5685</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14355,10 +14355,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>563487</v>
+        <v>563356</v>
       </c>
       <c r="R113" t="n">
-        <v>6626901</v>
+        <v>6626854</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -14405,6 +14405,11 @@
       <c r="AI113" t="inlineStr">
         <is>
           <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14426,10 +14431,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122485582</v>
+        <v>122485586</v>
       </c>
       <c r="B114" t="n">
-        <v>91231</v>
+        <v>100621</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14438,25 +14443,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14466,10 +14471,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>564072</v>
+        <v>564170</v>
       </c>
       <c r="R114" t="n">
-        <v>6626685</v>
+        <v>6626836</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14515,12 +14520,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre barrskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14542,10 +14542,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122485576</v>
+        <v>122485582</v>
       </c>
       <c r="B115" t="n">
-        <v>92256</v>
+        <v>91235</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14558,21 +14558,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5966</v>
+        <v>658</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14582,10 +14582,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>563758</v>
+        <v>564072</v>
       </c>
       <c r="R115" t="n">
-        <v>6626923</v>
+        <v>6626685</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -14631,7 +14631,12 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Äldre lavtallskog, hällmark</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -14653,10 +14658,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122485580</v>
+        <v>122485576</v>
       </c>
       <c r="B116" t="n">
-        <v>92221</v>
+        <v>92260</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14665,25 +14670,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14693,10 +14698,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>563671</v>
+        <v>563758</v>
       </c>
       <c r="R116" t="n">
-        <v>6626790</v>
+        <v>6626923</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14742,7 +14747,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Äldre barrskog, ristyp</t>
+          <t>Äldre lavtallskog, hällmark</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14764,10 +14769,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122485581</v>
+        <v>122485579</v>
       </c>
       <c r="B117" t="n">
-        <v>92213</v>
+        <v>92227</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14780,21 +14785,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4361</v>
+        <v>788</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14804,10 +14809,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>563669</v>
+        <v>563414</v>
       </c>
       <c r="R117" t="n">
-        <v>6626870</v>
+        <v>6626837</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -14853,7 +14858,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Äldre talldominerad barrskog</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14875,10 +14880,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122485588</v>
+        <v>122485589</v>
       </c>
       <c r="B118" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14915,10 +14920,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>564140</v>
+        <v>563487</v>
       </c>
       <c r="R118" t="n">
-        <v>6626788</v>
+        <v>6626901</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14964,7 +14969,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Äldre barrskog,</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14986,10 +14991,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122485578</v>
+        <v>122485580</v>
       </c>
       <c r="B119" t="n">
-        <v>90325</v>
+        <v>92225</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15002,21 +15007,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15026,10 +15031,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>563356</v>
+        <v>563671</v>
       </c>
       <c r="R119" t="n">
-        <v>6626854</v>
+        <v>6626790</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -15075,12 +15080,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Liggande tallstam</t>
+          <t>Äldre barrskog, ristyp</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15102,10 +15102,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122485579</v>
+        <v>122485588</v>
       </c>
       <c r="B120" t="n">
-        <v>92223</v>
+        <v>98355</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15114,25 +15114,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>788</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -15142,10 +15142,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>563414</v>
+        <v>564140</v>
       </c>
       <c r="R120" t="n">
-        <v>6626837</v>
+        <v>6626788</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre barrskog,</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15213,10 +15213,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122485586</v>
+        <v>122485585</v>
       </c>
       <c r="B121" t="n">
-        <v>100613</v>
+        <v>105461</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15229,21 +15229,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15253,10 +15253,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>564170</v>
+        <v>564155</v>
       </c>
       <c r="R121" t="n">
-        <v>6626836</v>
+        <v>6626751</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15327,7 +15327,7 @@
         <v>122485583</v>
       </c>
       <c r="B122" t="n">
-        <v>95011</v>
+        <v>95019</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -14204,10 +14204,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122485581</v>
+        <v>122485580</v>
       </c>
       <c r="B112" t="n">
-        <v>92217</v>
+        <v>92225</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14216,25 +14216,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>563669</v>
+        <v>563671</v>
       </c>
       <c r="R112" t="n">
-        <v>6626870</v>
+        <v>6626790</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -14293,7 +14293,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Äldre talldominerad barrskog</t>
+          <t>Äldre barrskog, ristyp</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14315,10 +14315,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122485578</v>
+        <v>122485589</v>
       </c>
       <c r="B113" t="n">
-        <v>90329</v>
+        <v>98355</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14327,25 +14327,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5685</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14355,10 +14355,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>563356</v>
+        <v>563487</v>
       </c>
       <c r="R113" t="n">
-        <v>6626854</v>
+        <v>6626901</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -14405,11 +14405,6 @@
       <c r="AI113" t="inlineStr">
         <is>
           <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14431,10 +14426,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122485586</v>
+        <v>122485582</v>
       </c>
       <c r="B114" t="n">
-        <v>100621</v>
+        <v>91235</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14443,25 +14438,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14471,10 +14466,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>564170</v>
+        <v>564072</v>
       </c>
       <c r="R114" t="n">
-        <v>6626836</v>
+        <v>6626685</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14520,7 +14515,12 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14542,10 +14542,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122485582</v>
+        <v>122485588</v>
       </c>
       <c r="B115" t="n">
-        <v>91235</v>
+        <v>98355</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14554,25 +14554,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14582,10 +14582,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>564072</v>
+        <v>564140</v>
       </c>
       <c r="R115" t="n">
-        <v>6626685</v>
+        <v>6626788</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -14631,12 +14631,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre barrskog,</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -14658,10 +14653,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122485576</v>
+        <v>122485579</v>
       </c>
       <c r="B116" t="n">
-        <v>92260</v>
+        <v>92227</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14674,21 +14669,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5966</v>
+        <v>788</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14698,10 +14693,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>563758</v>
+        <v>563414</v>
       </c>
       <c r="R116" t="n">
-        <v>6626923</v>
+        <v>6626837</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14747,7 +14742,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Äldre lavtallskog, hällmark</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14769,10 +14764,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122485579</v>
+        <v>122485583</v>
       </c>
       <c r="B117" t="n">
-        <v>92227</v>
+        <v>95019</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14781,25 +14776,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>788</v>
+        <v>2170</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14809,10 +14804,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>563414</v>
+        <v>563793</v>
       </c>
       <c r="R117" t="n">
-        <v>6626837</v>
+        <v>6626760</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -14853,12 +14848,18 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre barrskog, fyktig ristyp</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Murken tallved</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14880,10 +14881,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122485589</v>
+        <v>122485585</v>
       </c>
       <c r="B118" t="n">
-        <v>98355</v>
+        <v>105461</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14892,25 +14893,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14920,10 +14921,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>563487</v>
+        <v>564155</v>
       </c>
       <c r="R118" t="n">
-        <v>6626901</v>
+        <v>6626751</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14969,7 +14970,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14991,10 +14992,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122485580</v>
+        <v>122485578</v>
       </c>
       <c r="B119" t="n">
-        <v>92225</v>
+        <v>90329</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15007,21 +15008,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>5685</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15031,10 +15032,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>563671</v>
+        <v>563356</v>
       </c>
       <c r="R119" t="n">
-        <v>6626790</v>
+        <v>6626854</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -15080,7 +15081,12 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Äldre barrskog, ristyp</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15102,10 +15108,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122485588</v>
+        <v>122485581</v>
       </c>
       <c r="B120" t="n">
-        <v>98355</v>
+        <v>92217</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15114,25 +15120,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -15142,10 +15148,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>564140</v>
+        <v>563669</v>
       </c>
       <c r="R120" t="n">
-        <v>6626788</v>
+        <v>6626870</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -15191,7 +15197,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Äldre barrskog,</t>
+          <t>Äldre talldominerad barrskog</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15213,10 +15219,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122485585</v>
+        <v>122485576</v>
       </c>
       <c r="B121" t="n">
-        <v>105461</v>
+        <v>92260</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15225,25 +15231,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15253,10 +15259,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>564155</v>
+        <v>563758</v>
       </c>
       <c r="R121" t="n">
-        <v>6626751</v>
+        <v>6626923</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15302,7 +15308,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre lavtallskog, hällmark</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15324,10 +15330,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122485583</v>
+        <v>122485586</v>
       </c>
       <c r="B122" t="n">
-        <v>95019</v>
+        <v>100621</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15340,21 +15346,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2170</v>
+        <v>222498</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -15364,10 +15370,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>563793</v>
+        <v>564170</v>
       </c>
       <c r="R122" t="n">
-        <v>6626760</v>
+        <v>6626836</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15408,18 +15414,12 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fyktig ristyp</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Murken tallved</t>
+          <t>Äldre barrskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -14204,10 +14204,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122485580</v>
+        <v>122485589</v>
       </c>
       <c r="B112" t="n">
-        <v>92225</v>
+        <v>98357</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14216,25 +14216,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>563671</v>
+        <v>563487</v>
       </c>
       <c r="R112" t="n">
-        <v>6626790</v>
+        <v>6626901</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -14293,7 +14293,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Äldre barrskog, ristyp</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14315,10 +14315,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122485589</v>
+        <v>122485582</v>
       </c>
       <c r="B113" t="n">
-        <v>98355</v>
+        <v>91235</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14327,25 +14327,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14355,10 +14355,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>563487</v>
+        <v>564072</v>
       </c>
       <c r="R113" t="n">
-        <v>6626901</v>
+        <v>6626685</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -14405,6 +14405,11 @@
       <c r="AI113" t="inlineStr">
         <is>
           <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14426,10 +14431,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122485582</v>
+        <v>122485578</v>
       </c>
       <c r="B114" t="n">
-        <v>91235</v>
+        <v>90329</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14438,25 +14443,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>658</v>
+        <v>5685</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14466,10 +14471,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>564072</v>
+        <v>563356</v>
       </c>
       <c r="R114" t="n">
-        <v>6626685</v>
+        <v>6626854</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14520,7 +14525,7 @@
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14542,10 +14547,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122485588</v>
+        <v>122485583</v>
       </c>
       <c r="B115" t="n">
-        <v>98355</v>
+        <v>95021</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14554,25 +14559,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14582,10 +14587,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>564140</v>
+        <v>563793</v>
       </c>
       <c r="R115" t="n">
-        <v>6626788</v>
+        <v>6626760</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -14626,12 +14631,18 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Äldre barrskog,</t>
+          <t>Äldre barrskog, fyktig ristyp</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Murken tallved</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -14653,10 +14664,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122485579</v>
+        <v>122485586</v>
       </c>
       <c r="B116" t="n">
-        <v>92227</v>
+        <v>100623</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14665,25 +14676,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14693,10 +14704,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>563414</v>
+        <v>564170</v>
       </c>
       <c r="R116" t="n">
-        <v>6626837</v>
+        <v>6626836</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14742,7 +14753,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre barrskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14764,10 +14775,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122485583</v>
+        <v>122485581</v>
       </c>
       <c r="B117" t="n">
-        <v>95019</v>
+        <v>92217</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14776,25 +14787,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2170</v>
+        <v>4361</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14804,10 +14815,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>563793</v>
+        <v>563669</v>
       </c>
       <c r="R117" t="n">
-        <v>6626760</v>
+        <v>6626870</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -14848,18 +14859,12 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fyktig ristyp</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Murken tallved</t>
+          <t>Äldre talldominerad barrskog</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14881,10 +14886,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122485585</v>
+        <v>122485579</v>
       </c>
       <c r="B118" t="n">
-        <v>105461</v>
+        <v>92227</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14893,25 +14898,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221144</v>
+        <v>788</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14921,10 +14926,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>564155</v>
+        <v>563414</v>
       </c>
       <c r="R118" t="n">
-        <v>6626751</v>
+        <v>6626837</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14970,7 +14975,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14992,10 +14997,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122485578</v>
+        <v>122485585</v>
       </c>
       <c r="B119" t="n">
-        <v>90329</v>
+        <v>105463</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15008,21 +15013,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5685</v>
+        <v>221144</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15032,10 +15037,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>563356</v>
+        <v>564155</v>
       </c>
       <c r="R119" t="n">
-        <v>6626854</v>
+        <v>6626751</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -15081,12 +15086,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Liggande tallstam</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15108,10 +15108,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122485581</v>
+        <v>122485576</v>
       </c>
       <c r="B120" t="n">
-        <v>92217</v>
+        <v>92260</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15124,21 +15124,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -15148,10 +15148,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>563669</v>
+        <v>563758</v>
       </c>
       <c r="R120" t="n">
-        <v>6626870</v>
+        <v>6626923</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -15197,7 +15197,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Äldre talldominerad barrskog</t>
+          <t>Äldre lavtallskog, hällmark</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15219,10 +15219,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122485576</v>
+        <v>122485580</v>
       </c>
       <c r="B121" t="n">
-        <v>92260</v>
+        <v>92225</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15231,25 +15231,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15259,10 +15259,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>563758</v>
+        <v>563671</v>
       </c>
       <c r="R121" t="n">
-        <v>6626923</v>
+        <v>6626790</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15308,7 +15308,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Äldre lavtallskog, hällmark</t>
+          <t>Äldre barrskog, ristyp</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15330,10 +15330,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122485586</v>
+        <v>122485588</v>
       </c>
       <c r="B122" t="n">
-        <v>100621</v>
+        <v>98357</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15342,25 +15342,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -15370,10 +15370,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>564170</v>
+        <v>564140</v>
       </c>
       <c r="R122" t="n">
-        <v>6626836</v>
+        <v>6626788</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Äldre barrskog,</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -14664,10 +14664,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122485586</v>
+        <v>122485581</v>
       </c>
       <c r="B116" t="n">
-        <v>100623</v>
+        <v>92217</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14676,25 +14676,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>222498</v>
+        <v>4361</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14704,10 +14704,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>564170</v>
+        <v>563669</v>
       </c>
       <c r="R116" t="n">
-        <v>6626836</v>
+        <v>6626870</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14753,7 +14753,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Äldre talldominerad barrskog</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14775,10 +14775,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122485581</v>
+        <v>122485586</v>
       </c>
       <c r="B117" t="n">
-        <v>92217</v>
+        <v>100623</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14787,25 +14787,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4361</v>
+        <v>222498</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>563669</v>
+        <v>564170</v>
       </c>
       <c r="R117" t="n">
-        <v>6626870</v>
+        <v>6626836</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Äldre talldominerad barrskog</t>
+          <t>Äldre barrskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14886,10 +14886,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122485579</v>
+        <v>122485585</v>
       </c>
       <c r="B118" t="n">
-        <v>92227</v>
+        <v>105463</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14898,25 +14898,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>788</v>
+        <v>221144</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14926,10 +14926,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>563414</v>
+        <v>564155</v>
       </c>
       <c r="R118" t="n">
-        <v>6626837</v>
+        <v>6626751</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14975,7 +14975,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14997,10 +14997,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122485585</v>
+        <v>122485579</v>
       </c>
       <c r="B119" t="n">
-        <v>105463</v>
+        <v>92227</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15009,25 +15009,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221144</v>
+        <v>788</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15037,10 +15037,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>564155</v>
+        <v>563414</v>
       </c>
       <c r="R119" t="n">
-        <v>6626751</v>
+        <v>6626837</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -14204,10 +14204,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122485589</v>
+        <v>122485578</v>
       </c>
       <c r="B112" t="n">
-        <v>98357</v>
+        <v>90329</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14216,25 +14216,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>5685</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>563487</v>
+        <v>563356</v>
       </c>
       <c r="R112" t="n">
-        <v>6626901</v>
+        <v>6626854</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -14294,6 +14294,11 @@
       <c r="AI112" t="inlineStr">
         <is>
           <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14315,10 +14320,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122485582</v>
+        <v>122485585</v>
       </c>
       <c r="B113" t="n">
-        <v>91235</v>
+        <v>105463</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14327,25 +14332,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>658</v>
+        <v>221144</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14355,10 +14360,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>564072</v>
+        <v>564155</v>
       </c>
       <c r="R113" t="n">
-        <v>6626685</v>
+        <v>6626751</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -14404,12 +14409,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14431,10 +14431,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122485578</v>
+        <v>122485576</v>
       </c>
       <c r="B114" t="n">
-        <v>90329</v>
+        <v>92260</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14443,25 +14443,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5685</v>
+        <v>5966</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14471,10 +14471,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>563356</v>
+        <v>563758</v>
       </c>
       <c r="R114" t="n">
-        <v>6626854</v>
+        <v>6626923</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14520,12 +14520,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Liggande tallstam</t>
+          <t>Äldre lavtallskog, hällmark</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14664,10 +14659,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122485581</v>
+        <v>122485580</v>
       </c>
       <c r="B116" t="n">
-        <v>92217</v>
+        <v>92225</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14676,25 +14671,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14704,10 +14699,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>563669</v>
+        <v>563671</v>
       </c>
       <c r="R116" t="n">
-        <v>6626870</v>
+        <v>6626790</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14753,7 +14748,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Äldre talldominerad barrskog</t>
+          <t>Äldre barrskog, ristyp</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14775,10 +14770,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122485586</v>
+        <v>122485581</v>
       </c>
       <c r="B117" t="n">
-        <v>100623</v>
+        <v>92217</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14787,25 +14782,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>222498</v>
+        <v>4361</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14815,10 +14810,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>564170</v>
+        <v>563669</v>
       </c>
       <c r="R117" t="n">
-        <v>6626836</v>
+        <v>6626870</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -14864,7 +14859,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Äldre talldominerad barrskog</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14886,10 +14881,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122485585</v>
+        <v>122485582</v>
       </c>
       <c r="B118" t="n">
-        <v>105463</v>
+        <v>91235</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14898,25 +14893,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221144</v>
+        <v>658</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14926,10 +14921,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>564155</v>
+        <v>564072</v>
       </c>
       <c r="R118" t="n">
-        <v>6626751</v>
+        <v>6626685</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14975,7 +14970,12 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14997,10 +14997,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122485579</v>
+        <v>122485586</v>
       </c>
       <c r="B119" t="n">
-        <v>92227</v>
+        <v>100623</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15009,25 +15009,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15037,10 +15037,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>563414</v>
+        <v>564170</v>
       </c>
       <c r="R119" t="n">
-        <v>6626837</v>
+        <v>6626836</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre barrskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15108,10 +15108,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122485576</v>
+        <v>122485589</v>
       </c>
       <c r="B120" t="n">
-        <v>92260</v>
+        <v>98357</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15120,25 +15120,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -15148,10 +15148,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>563758</v>
+        <v>563487</v>
       </c>
       <c r="R120" t="n">
-        <v>6626923</v>
+        <v>6626901</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -15197,7 +15197,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Äldre lavtallskog, hällmark</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15219,10 +15219,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122485580</v>
+        <v>122485588</v>
       </c>
       <c r="B121" t="n">
-        <v>92225</v>
+        <v>98357</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15231,25 +15231,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15259,10 +15259,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>563671</v>
+        <v>564140</v>
       </c>
       <c r="R121" t="n">
-        <v>6626790</v>
+        <v>6626788</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15308,7 +15308,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Äldre barrskog, ristyp</t>
+          <t>Äldre barrskog,</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15330,10 +15330,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122485588</v>
+        <v>122485579</v>
       </c>
       <c r="B122" t="n">
-        <v>98357</v>
+        <v>92227</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15342,25 +15342,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -15370,10 +15370,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>564140</v>
+        <v>563414</v>
       </c>
       <c r="R122" t="n">
-        <v>6626788</v>
+        <v>6626837</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Äldre barrskog,</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -14204,10 +14204,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122485578</v>
+        <v>122485579</v>
       </c>
       <c r="B112" t="n">
-        <v>90329</v>
+        <v>92235</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14216,25 +14216,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5685</v>
+        <v>788</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>563356</v>
+        <v>563414</v>
       </c>
       <c r="R112" t="n">
-        <v>6626854</v>
+        <v>6626837</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -14293,12 +14293,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Liggande tallstam</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14320,10 +14315,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122485585</v>
+        <v>122485576</v>
       </c>
       <c r="B113" t="n">
-        <v>105463</v>
+        <v>92268</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14332,25 +14327,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14360,10 +14355,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>564155</v>
+        <v>563758</v>
       </c>
       <c r="R113" t="n">
-        <v>6626751</v>
+        <v>6626923</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -14409,7 +14404,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre lavtallskog, hällmark</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14431,10 +14426,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122485576</v>
+        <v>122485580</v>
       </c>
       <c r="B114" t="n">
-        <v>92260</v>
+        <v>92233</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14443,25 +14438,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14471,10 +14466,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>563758</v>
+        <v>563671</v>
       </c>
       <c r="R114" t="n">
-        <v>6626923</v>
+        <v>6626790</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14520,7 +14515,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Äldre lavtallskog, hällmark</t>
+          <t>Äldre barrskog, ristyp</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14545,7 +14540,7 @@
         <v>122485583</v>
       </c>
       <c r="B115" t="n">
-        <v>95021</v>
+        <v>95029</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14659,10 +14654,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122485580</v>
+        <v>122485585</v>
       </c>
       <c r="B116" t="n">
-        <v>92225</v>
+        <v>105471</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14675,21 +14670,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14699,10 +14694,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>563671</v>
+        <v>564155</v>
       </c>
       <c r="R116" t="n">
-        <v>6626790</v>
+        <v>6626751</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14748,7 +14743,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Äldre barrskog, ristyp</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14770,10 +14765,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122485581</v>
+        <v>122485589</v>
       </c>
       <c r="B117" t="n">
-        <v>92217</v>
+        <v>98365</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14782,25 +14777,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14810,10 +14805,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>563669</v>
+        <v>563487</v>
       </c>
       <c r="R117" t="n">
-        <v>6626870</v>
+        <v>6626901</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -14859,7 +14854,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Äldre talldominerad barrskog</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14884,7 +14879,7 @@
         <v>122485582</v>
       </c>
       <c r="B118" t="n">
-        <v>91235</v>
+        <v>91243</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14997,10 +14992,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122485586</v>
+        <v>122485588</v>
       </c>
       <c r="B119" t="n">
-        <v>100623</v>
+        <v>98365</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15009,25 +15004,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15037,10 +15032,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>564170</v>
+        <v>564140</v>
       </c>
       <c r="R119" t="n">
-        <v>6626836</v>
+        <v>6626788</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -15086,7 +15081,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Äldre barrskog,</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15108,10 +15103,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122485589</v>
+        <v>122485581</v>
       </c>
       <c r="B120" t="n">
-        <v>98357</v>
+        <v>92225</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15120,25 +15115,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -15148,10 +15143,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>563487</v>
+        <v>563669</v>
       </c>
       <c r="R120" t="n">
-        <v>6626901</v>
+        <v>6626870</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -15197,7 +15192,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
+          <t>Äldre talldominerad barrskog</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15219,10 +15214,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122485588</v>
+        <v>122485578</v>
       </c>
       <c r="B121" t="n">
-        <v>98357</v>
+        <v>90337</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15231,25 +15226,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>5685</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15259,10 +15254,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>564140</v>
+        <v>563356</v>
       </c>
       <c r="R121" t="n">
-        <v>6626788</v>
+        <v>6626854</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15308,7 +15303,12 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Äldre barrskog,</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15330,10 +15330,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122485579</v>
+        <v>122485586</v>
       </c>
       <c r="B122" t="n">
-        <v>92227</v>
+        <v>100631</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15342,25 +15342,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -15370,10 +15370,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>563414</v>
+        <v>564170</v>
       </c>
       <c r="R122" t="n">
-        <v>6626837</v>
+        <v>6626836</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre barrskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -14876,10 +14876,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122485582</v>
+        <v>122485588</v>
       </c>
       <c r="B118" t="n">
-        <v>91243</v>
+        <v>98365</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14888,25 +14888,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14916,10 +14916,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>564072</v>
+        <v>564140</v>
       </c>
       <c r="R118" t="n">
-        <v>6626685</v>
+        <v>6626788</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14965,12 +14965,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre barrskog,</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14992,10 +14987,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122485588</v>
+        <v>122485582</v>
       </c>
       <c r="B119" t="n">
-        <v>98365</v>
+        <v>91243</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15004,25 +14999,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15032,10 +15027,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>564140</v>
+        <v>564072</v>
       </c>
       <c r="R119" t="n">
-        <v>6626788</v>
+        <v>6626685</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -15081,7 +15076,12 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Äldre barrskog,</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -14204,10 +14204,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122485579</v>
+        <v>122485581</v>
       </c>
       <c r="B112" t="n">
-        <v>92235</v>
+        <v>92225</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14220,21 +14220,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>788</v>
+        <v>4361</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>563414</v>
+        <v>563669</v>
       </c>
       <c r="R112" t="n">
-        <v>6626837</v>
+        <v>6626870</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -14293,7 +14293,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre talldominerad barrskog</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14315,10 +14315,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122485576</v>
+        <v>122485583</v>
       </c>
       <c r="B113" t="n">
-        <v>92268</v>
+        <v>95029</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14327,25 +14327,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5966</v>
+        <v>2170</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14355,10 +14355,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>563758</v>
+        <v>563793</v>
       </c>
       <c r="R113" t="n">
-        <v>6626923</v>
+        <v>6626760</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -14399,12 +14399,18 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Äldre lavtallskog, hällmark</t>
+          <t>Äldre barrskog, fyktig ristyp</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Murken tallved</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14426,10 +14432,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122485580</v>
+        <v>122485582</v>
       </c>
       <c r="B114" t="n">
-        <v>92233</v>
+        <v>91243</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14438,25 +14444,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14466,10 +14472,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>563671</v>
+        <v>564072</v>
       </c>
       <c r="R114" t="n">
-        <v>6626790</v>
+        <v>6626685</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14515,7 +14521,12 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Äldre barrskog, ristyp</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14537,10 +14548,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122485583</v>
+        <v>122485585</v>
       </c>
       <c r="B115" t="n">
-        <v>95029</v>
+        <v>105471</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14553,21 +14564,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14577,10 +14588,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>563793</v>
+        <v>564155</v>
       </c>
       <c r="R115" t="n">
-        <v>6626760</v>
+        <v>6626751</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -14621,18 +14632,12 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fyktig ristyp</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Murken tallved</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -14654,10 +14659,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122485585</v>
+        <v>122485588</v>
       </c>
       <c r="B116" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14666,25 +14671,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14694,10 +14699,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>564155</v>
+        <v>564140</v>
       </c>
       <c r="R116" t="n">
-        <v>6626751</v>
+        <v>6626788</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14743,7 +14748,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog,</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14765,10 +14770,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122485589</v>
+        <v>122485576</v>
       </c>
       <c r="B117" t="n">
-        <v>98365</v>
+        <v>92268</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14777,25 +14782,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14805,10 +14810,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>563487</v>
+        <v>563758</v>
       </c>
       <c r="R117" t="n">
-        <v>6626901</v>
+        <v>6626923</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -14854,7 +14859,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
+          <t>Äldre lavtallskog, hällmark</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14876,10 +14881,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122485588</v>
+        <v>122485580</v>
       </c>
       <c r="B118" t="n">
-        <v>98365</v>
+        <v>92233</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14888,25 +14893,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14916,10 +14921,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>564140</v>
+        <v>563671</v>
       </c>
       <c r="R118" t="n">
-        <v>6626788</v>
+        <v>6626790</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14965,7 +14970,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Äldre barrskog,</t>
+          <t>Äldre barrskog, ristyp</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14987,10 +14992,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122485582</v>
+        <v>122485589</v>
       </c>
       <c r="B119" t="n">
-        <v>91243</v>
+        <v>98365</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14999,25 +15004,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15027,10 +15032,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>564072</v>
+        <v>563487</v>
       </c>
       <c r="R119" t="n">
-        <v>6626685</v>
+        <v>6626901</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -15077,11 +15082,6 @@
       <c r="AI119" t="inlineStr">
         <is>
           <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15103,10 +15103,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122485581</v>
+        <v>122485586</v>
       </c>
       <c r="B120" t="n">
-        <v>92225</v>
+        <v>100631</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15115,25 +15115,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4361</v>
+        <v>222498</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -15143,10 +15143,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>563669</v>
+        <v>564170</v>
       </c>
       <c r="R120" t="n">
-        <v>6626870</v>
+        <v>6626836</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -15192,7 +15192,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Äldre talldominerad barrskog</t>
+          <t>Äldre barrskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15330,10 +15330,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122485586</v>
+        <v>122485579</v>
       </c>
       <c r="B122" t="n">
-        <v>100631</v>
+        <v>92235</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15342,25 +15342,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>222498</v>
+        <v>788</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -15370,10 +15370,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>564170</v>
+        <v>563414</v>
       </c>
       <c r="R122" t="n">
-        <v>6626836</v>
+        <v>6626837</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -14204,10 +14204,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122485581</v>
+        <v>122485582</v>
       </c>
       <c r="B112" t="n">
-        <v>92225</v>
+        <v>91243</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14220,21 +14220,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4361</v>
+        <v>658</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>563669</v>
+        <v>564072</v>
       </c>
       <c r="R112" t="n">
-        <v>6626870</v>
+        <v>6626685</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -14293,7 +14293,12 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Äldre talldominerad barrskog</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14432,10 +14437,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122485582</v>
+        <v>122485578</v>
       </c>
       <c r="B114" t="n">
-        <v>91243</v>
+        <v>90337</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14444,25 +14449,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>658</v>
+        <v>5685</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14472,10 +14477,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>564072</v>
+        <v>563356</v>
       </c>
       <c r="R114" t="n">
-        <v>6626685</v>
+        <v>6626854</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14526,7 +14531,7 @@
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14548,10 +14553,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122485585</v>
+        <v>122485580</v>
       </c>
       <c r="B115" t="n">
-        <v>105471</v>
+        <v>92233</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14564,21 +14569,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14588,10 +14593,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>564155</v>
+        <v>563671</v>
       </c>
       <c r="R115" t="n">
-        <v>6626751</v>
+        <v>6626790</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -14637,7 +14642,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog, ristyp</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -14659,10 +14664,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122485588</v>
+        <v>122485576</v>
       </c>
       <c r="B116" t="n">
-        <v>98365</v>
+        <v>92268</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14671,25 +14676,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14699,10 +14704,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>564140</v>
+        <v>563758</v>
       </c>
       <c r="R116" t="n">
-        <v>6626788</v>
+        <v>6626923</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14748,7 +14753,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Äldre barrskog,</t>
+          <t>Äldre lavtallskog, hällmark</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14770,10 +14775,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122485576</v>
+        <v>122485585</v>
       </c>
       <c r="B117" t="n">
-        <v>92268</v>
+        <v>105471</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14782,25 +14787,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14810,10 +14815,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>563758</v>
+        <v>564155</v>
       </c>
       <c r="R117" t="n">
-        <v>6626923</v>
+        <v>6626751</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -14859,7 +14864,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Äldre lavtallskog, hällmark</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14881,10 +14886,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122485580</v>
+        <v>122485588</v>
       </c>
       <c r="B118" t="n">
-        <v>92233</v>
+        <v>98365</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14893,25 +14898,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14921,10 +14926,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>563671</v>
+        <v>564140</v>
       </c>
       <c r="R118" t="n">
-        <v>6626790</v>
+        <v>6626788</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14970,7 +14975,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Äldre barrskog, ristyp</t>
+          <t>Äldre barrskog,</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15103,10 +15108,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122485586</v>
+        <v>122485579</v>
       </c>
       <c r="B120" t="n">
-        <v>100631</v>
+        <v>92235</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15115,25 +15120,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>222498</v>
+        <v>788</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -15143,10 +15148,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>564170</v>
+        <v>563414</v>
       </c>
       <c r="R120" t="n">
-        <v>6626836</v>
+        <v>6626837</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -15192,7 +15197,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15214,10 +15219,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122485578</v>
+        <v>122485586</v>
       </c>
       <c r="B121" t="n">
-        <v>90337</v>
+        <v>100631</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15230,21 +15235,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5685</v>
+        <v>222498</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15254,10 +15259,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>563356</v>
+        <v>564170</v>
       </c>
       <c r="R121" t="n">
-        <v>6626854</v>
+        <v>6626836</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15303,12 +15308,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Liggande tallstam</t>
+          <t>Äldre barrskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15330,10 +15330,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122485579</v>
+        <v>122485581</v>
       </c>
       <c r="B122" t="n">
-        <v>92235</v>
+        <v>92225</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15346,21 +15346,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>788</v>
+        <v>4361</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -15370,10 +15370,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>563414</v>
+        <v>563669</v>
       </c>
       <c r="R122" t="n">
-        <v>6626837</v>
+        <v>6626870</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre talldominerad barrskog</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY122"/>
+  <dimension ref="A1:AY124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15439,6 +15439,238 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>123809320</v>
+      </c>
+      <c r="B123" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>564165</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6626834</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog, översilning</t>
+        </is>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123809435</v>
+      </c>
+      <c r="B124" t="n">
+        <v>91428</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Sothällen VSV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>564075</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6626696</v>
+      </c>
+      <c r="S124" t="n">
+        <v>5</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -15441,10 +15441,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123809320</v>
+        <v>123809435</v>
       </c>
       <c r="B123" t="n">
-        <v>100662</v>
+        <v>91433</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15453,49 +15453,44 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>564165</v>
+        <v>564075</v>
       </c>
       <c r="R123" t="n">
-        <v>6626834</v>
+        <v>6626696</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15539,7 +15534,12 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog, översilning</t>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -15557,10 +15557,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123809435</v>
+        <v>123809320</v>
       </c>
       <c r="B124" t="n">
-        <v>91428</v>
+        <v>100680</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15569,44 +15569,49 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>564075</v>
+        <v>564165</v>
       </c>
       <c r="R124" t="n">
-        <v>6626696</v>
+        <v>6626834</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15650,12 +15655,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Gammal barrblandskog, översilning</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY124"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10438,10 +10438,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>113374825</v>
+        <v>118405005</v>
       </c>
       <c r="B81" t="n">
-        <v>97650</v>
+        <v>97855</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10471,33 +10471,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Grotten, OSO (knärot), Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>563486</v>
+        <v>563342</v>
       </c>
       <c r="R81" t="n">
-        <v>6626863</v>
+        <v>6626819</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10522,24 +10514,14 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>U-Sur-0510</t>
-        </is>
-      </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>151339/6628311(5), 105 pl, 327/322 (5), 50 pl, 319/328 (5), 200 pl foto i AP</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10552,10 +10534,15 @@
       <c r="AG81" t="b">
         <v>0</v>
       </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
@@ -10563,18 +10550,14 @@
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118405005</v>
+        <v>118703452</v>
       </c>
       <c r="B82" t="n">
-        <v>97855</v>
+        <v>97858</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10604,8 +10587,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10615,14 +10606,14 @@
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Grotten OSO, Vstm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>563342</v>
+        <v>563797</v>
       </c>
       <c r="R82" t="n">
-        <v>6626819</v>
+        <v>6626917</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10649,12 +10640,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10669,7 +10660,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Äldre barrblandskog, blåbärsris</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10687,10 +10678,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118703452</v>
+        <v>118703238</v>
       </c>
       <c r="B83" t="n">
-        <v>97858</v>
+        <v>90008</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10703,39 +10694,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10743,10 +10729,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>563797</v>
+        <v>563749</v>
       </c>
       <c r="R83" t="n">
-        <v>6626917</v>
+        <v>6626857</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10793,7 +10779,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog, blåbärsris</t>
+          <t>Barrblandskog med lingonris, ljung</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10811,10 +10797,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118703238</v>
+        <v>118725826</v>
       </c>
       <c r="B84" t="n">
-        <v>90008</v>
+        <v>97858</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10827,45 +10813,50 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Grotten OSO, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>563749</v>
+        <v>563416</v>
       </c>
       <c r="R84" t="n">
-        <v>6626857</v>
+        <v>6626839</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10892,12 +10883,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10912,7 +10903,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Barrblandskog med lingonris, ljung</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10930,7 +10921,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118725826</v>
+        <v>118726246</v>
       </c>
       <c r="B85" t="n">
         <v>97858</v>
@@ -10965,14 +10956,10 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -10986,10 +10973,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>563416</v>
+        <v>563455</v>
       </c>
       <c r="R85" t="n">
-        <v>6626839</v>
+        <v>6626817</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11022,6 +11009,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>8 blomstänglar.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11054,7 +11046,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118726246</v>
+        <v>118725842</v>
       </c>
       <c r="B86" t="n">
         <v>97858</v>
@@ -11089,10 +11081,14 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -11106,10 +11102,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>563455</v>
+        <v>563403</v>
       </c>
       <c r="R86" t="n">
-        <v>6626817</v>
+        <v>6626849</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11142,11 +11138,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>8 blomstänglar.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11179,7 +11170,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118725842</v>
+        <v>118726228</v>
       </c>
       <c r="B87" t="n">
         <v>97858</v>
@@ -11214,12 +11205,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -11235,10 +11226,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>563403</v>
+        <v>563338</v>
       </c>
       <c r="R87" t="n">
-        <v>6626849</v>
+        <v>6626827</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11303,7 +11294,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118726228</v>
+        <v>118725553</v>
       </c>
       <c r="B88" t="n">
         <v>97858</v>
@@ -11338,12 +11329,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -11359,10 +11350,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>563338</v>
+        <v>564180</v>
       </c>
       <c r="R88" t="n">
-        <v>6626827</v>
+        <v>6626838</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11389,12 +11380,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11409,7 +11400,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Äldre barrblandskog</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11427,10 +11418,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118725553</v>
+        <v>118725673</v>
       </c>
       <c r="B89" t="n">
-        <v>97858</v>
+        <v>91783</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11439,43 +11430,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -11483,10 +11469,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>564180</v>
+        <v>564091</v>
       </c>
       <c r="R89" t="n">
-        <v>6626838</v>
+        <v>6626790</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11533,7 +11519,12 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog</t>
+          <t>Fuktig blandskog</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>I sphagnum, granvitmossa</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11551,10 +11542,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118725673</v>
+        <v>118725958</v>
       </c>
       <c r="B90" t="n">
-        <v>91783</v>
+        <v>104952</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11563,38 +11554,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4361</v>
+        <v>221144</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -11602,10 +11598,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>564091</v>
+        <v>563678</v>
       </c>
       <c r="R90" t="n">
-        <v>6626790</v>
+        <v>6626862</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11632,12 +11628,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11652,12 +11648,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Fuktig blandskog</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>I sphagnum, granvitmossa</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11675,10 +11666,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118725958</v>
+        <v>118726560</v>
       </c>
       <c r="B91" t="n">
-        <v>104952</v>
+        <v>90478</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11691,39 +11682,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -11731,10 +11709,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>563678</v>
+        <v>563442</v>
       </c>
       <c r="R91" t="n">
-        <v>6626862</v>
+        <v>6626945</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11782,6 +11760,11 @@
       <c r="AI91" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11799,10 +11782,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118726560</v>
+        <v>118726258</v>
       </c>
       <c r="B92" t="n">
-        <v>90478</v>
+        <v>97858</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11811,30 +11794,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -11842,10 +11838,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>563442</v>
+        <v>563598</v>
       </c>
       <c r="R92" t="n">
-        <v>6626945</v>
+        <v>6626778</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11880,6 +11876,11 @@
           <t>2024-07-27</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>2 blomstänglar.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -11892,12 +11893,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11915,10 +11911,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118726258</v>
+        <v>118725977</v>
       </c>
       <c r="B93" t="n">
-        <v>97858</v>
+        <v>96816</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11927,42 +11923,30 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
@@ -11971,10 +11955,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>563598</v>
+        <v>563678</v>
       </c>
       <c r="R93" t="n">
-        <v>6626778</v>
+        <v>6626862</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12009,11 +11993,6 @@
           <t>2024-07-27</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>2 blomstänglar.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -12026,7 +12005,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12044,7 +12023,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118725977</v>
+        <v>118725918</v>
       </c>
       <c r="B94" t="n">
         <v>96816</v>
@@ -12088,10 +12067,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>563678</v>
+        <v>563403</v>
       </c>
       <c r="R94" t="n">
-        <v>6626862</v>
+        <v>6626849</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12138,7 +12117,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Fuktig blandskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12156,10 +12135,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118725918</v>
+        <v>118725694</v>
       </c>
       <c r="B95" t="n">
-        <v>96816</v>
+        <v>97778</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12172,23 +12151,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221946</v>
+        <v>223597</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -12200,10 +12175,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>563403</v>
+        <v>564010</v>
       </c>
       <c r="R95" t="n">
-        <v>6626849</v>
+        <v>6626775</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12230,12 +12205,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12268,7 +12243,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118725694</v>
+        <v>118724731</v>
       </c>
       <c r="B96" t="n">
         <v>97778</v>
@@ -12299,7 +12274,11 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
@@ -12308,10 +12287,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>564010</v>
+        <v>564069</v>
       </c>
       <c r="R96" t="n">
-        <v>6626775</v>
+        <v>6626755</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12358,7 +12337,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Fuktig blandskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12376,10 +12355,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118724731</v>
+        <v>118852324</v>
       </c>
       <c r="B97" t="n">
-        <v>97778</v>
+        <v>97858</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12388,28 +12367,40 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -12420,10 +12411,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>564069</v>
+        <v>564081</v>
       </c>
       <c r="R97" t="n">
-        <v>6626755</v>
+        <v>6626690</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12450,12 +12441,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>2 överblommade.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12470,7 +12466,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12488,7 +12484,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118852324</v>
+        <v>118852333</v>
       </c>
       <c r="B98" t="n">
         <v>97858</v>
@@ -12523,7 +12519,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -12544,10 +12540,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>564081</v>
+        <v>564104</v>
       </c>
       <c r="R98" t="n">
-        <v>6626690</v>
+        <v>6626694</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12584,7 +12580,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>2 överblommade.</t>
+          <t>3 överblommade.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12617,10 +12613,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118852333</v>
+        <v>119359828</v>
       </c>
       <c r="B99" t="n">
-        <v>97858</v>
+        <v>90776</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12629,43 +12625,30 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>1101</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -12673,10 +12656,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>564104</v>
+        <v>563824</v>
       </c>
       <c r="R99" t="n">
-        <v>6626694</v>
+        <v>6626769</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12703,17 +12686,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>3 överblommade.</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12728,7 +12706,12 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Barrved</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -12746,10 +12729,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119359828</v>
+        <v>119653000</v>
       </c>
       <c r="B100" t="n">
-        <v>90776</v>
+        <v>91840</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12758,25 +12741,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1101</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12785,17 +12768,17 @@
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Grotten OSO, Vstm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>563824</v>
+        <v>563681</v>
       </c>
       <c r="R100" t="n">
-        <v>6626769</v>
+        <v>6626784</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12819,12 +12802,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>intill stig (Bruksleden)</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12839,12 +12827,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Barrved</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -12862,10 +12845,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119653000</v>
+        <v>119653166</v>
       </c>
       <c r="B101" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12874,30 +12857,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -12905,10 +12901,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>563681</v>
+        <v>563655</v>
       </c>
       <c r="R101" t="n">
-        <v>6626784</v>
+        <v>6626789</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12941,11 +12937,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>intill stig (Bruksleden)</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12978,10 +12969,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119653166</v>
+        <v>119653050</v>
       </c>
       <c r="B102" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12990,43 +12981,30 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -13034,10 +13012,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>563655</v>
+        <v>563717</v>
       </c>
       <c r="R102" t="n">
-        <v>6626789</v>
+        <v>6626786</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -13084,7 +13062,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, lavhällar</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13102,10 +13080,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119653050</v>
+        <v>119653045</v>
       </c>
       <c r="B103" t="n">
-        <v>91840</v>
+        <v>89212</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13114,29 +13092,37 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4364</v>
+        <v>1593</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
@@ -13213,10 +13199,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119653434</v>
+        <v>119652976</v>
       </c>
       <c r="B104" t="n">
-        <v>105009</v>
+        <v>91840</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13229,53 +13215,40 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Grotten OSO, Vstm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>564017</v>
+        <v>563706</v>
       </c>
       <c r="R104" t="n">
-        <v>6626678</v>
+        <v>6626763</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13305,6 +13278,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>intill stig (Bruksleden)</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13319,7 +13297,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>Barrblandskog med lövislag</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -13337,10 +13315,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119653045</v>
+        <v>120496305</v>
       </c>
       <c r="B105" t="n">
-        <v>89212</v>
+        <v>8432</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13349,49 +13327,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1593</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Grotten OSO, Vstm</t>
+          <t>Naddtorpsskogen, Naddtorpsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>563717</v>
+        <v>564105</v>
       </c>
       <c r="R105" t="n">
-        <v>6626786</v>
+        <v>6626792</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -13418,12 +13385,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13432,34 +13409,48 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>Barrblandskog, lavhällar</t>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119652976</v>
+        <v>120495592</v>
       </c>
       <c r="B106" t="n">
-        <v>91840</v>
+        <v>8432</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13472,37 +13463,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Grotten OSO, Vstm</t>
+          <t>Naddtorpsskogen, Naddtorpsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>563706</v>
+        <v>563940</v>
       </c>
       <c r="R106" t="n">
-        <v>6626763</v>
+        <v>6626885</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -13529,17 +13517,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>intill stig (Bruksleden)</t>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13548,34 +13541,33 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120496305</v>
+        <v>120496678</v>
       </c>
       <c r="B107" t="n">
-        <v>8432</v>
+        <v>97010</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13588,37 +13580,53 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Naddtorpsskogen, Naddtorpsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>564105</v>
+        <v>564098</v>
       </c>
       <c r="R107" t="n">
-        <v>6626792</v>
+        <v>6626756</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13647,7 +13655,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13657,7 +13665,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13666,27 +13674,13 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -13704,10 +13698,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120495592</v>
+        <v>121228425</v>
       </c>
       <c r="B108" t="n">
-        <v>8432</v>
+        <v>98105</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13716,41 +13710,57 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Naddtorpsskogen, Naddtorpsskogen, Vstm</t>
+          <t>Sothällen, V (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>563940</v>
+        <v>564181</v>
       </c>
       <c r="R108" t="n">
-        <v>6626885</v>
+        <v>6626838</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13772,24 +13782,19 @@
           <t>Ramnäs</t>
         </is>
       </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>U-Sur-0785</t>
+        </is>
+      </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>12:50</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>12:50</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13798,33 +13803,38 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>äldre barrblandskog</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120496678</v>
+        <v>121247537</v>
       </c>
       <c r="B109" t="n">
-        <v>97010</v>
+        <v>91160</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13833,57 +13843,44 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Naddtorpsskogen, Naddtorpsskogen, Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>564098</v>
+        <v>564077</v>
       </c>
       <c r="R109" t="n">
-        <v>6626756</v>
+        <v>6626678</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13907,22 +13904,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13935,30 +13922,35 @@
       <c r="AG109" t="b">
         <v>0</v>
       </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121228425</v>
+        <v>122485582</v>
       </c>
       <c r="B110" t="n">
-        <v>98105</v>
+        <v>91243</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13967,57 +13959,41 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Sothällen, V (knärot), Vstm</t>
+          <t>Väst Sothällen, Vstm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>564181</v>
+        <v>564072</v>
       </c>
       <c r="R110" t="n">
-        <v>6626838</v>
+        <v>6626685</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -14039,19 +14015,14 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>U-Sur-0785</t>
-        </is>
-      </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14060,38 +14031,42 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>äldre barrblandskog</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121247537</v>
+        <v>122485583</v>
       </c>
       <c r="B111" t="n">
-        <v>91160</v>
+        <v>95029</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -14100,44 +14075,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1209</v>
+        <v>2170</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Väst Sothällen, Vstm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>564077</v>
+        <v>563793</v>
       </c>
       <c r="R111" t="n">
-        <v>6626678</v>
+        <v>6626760</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -14161,12 +14133,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14181,33 +14153,37 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Äldre barrskog, fyktig ristyp</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Murken tallved</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122485582</v>
+        <v>122485578</v>
       </c>
       <c r="B112" t="n">
-        <v>91243</v>
+        <v>90337</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14216,25 +14192,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>658</v>
+        <v>5685</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14244,10 +14220,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>564072</v>
+        <v>563356</v>
       </c>
       <c r="R112" t="n">
-        <v>6626685</v>
+        <v>6626854</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -14298,7 +14274,7 @@
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14320,10 +14296,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122485583</v>
+        <v>122485580</v>
       </c>
       <c r="B113" t="n">
-        <v>95029</v>
+        <v>92233</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14336,21 +14312,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14360,10 +14336,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>563793</v>
+        <v>563671</v>
       </c>
       <c r="R113" t="n">
-        <v>6626760</v>
+        <v>6626790</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -14404,18 +14380,12 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fyktig ristyp</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Murken tallved</t>
+          <t>Äldre barrskog, ristyp</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14437,10 +14407,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122485578</v>
+        <v>122485576</v>
       </c>
       <c r="B114" t="n">
-        <v>90337</v>
+        <v>92268</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14449,25 +14419,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5685</v>
+        <v>5966</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14477,10 +14447,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>563356</v>
+        <v>563758</v>
       </c>
       <c r="R114" t="n">
-        <v>6626854</v>
+        <v>6626923</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14526,12 +14496,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Liggande tallstam</t>
+          <t>Äldre lavtallskog, hällmark</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14553,10 +14518,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122485580</v>
+        <v>122485585</v>
       </c>
       <c r="B115" t="n">
-        <v>92233</v>
+        <v>105471</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14569,21 +14534,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14593,10 +14558,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>563671</v>
+        <v>564155</v>
       </c>
       <c r="R115" t="n">
-        <v>6626790</v>
+        <v>6626751</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -14642,7 +14607,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Äldre barrskog, ristyp</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -14664,10 +14629,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122485576</v>
+        <v>122485588</v>
       </c>
       <c r="B116" t="n">
-        <v>92268</v>
+        <v>98365</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14676,25 +14641,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14704,10 +14669,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>563758</v>
+        <v>564140</v>
       </c>
       <c r="R116" t="n">
-        <v>6626923</v>
+        <v>6626788</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14753,7 +14718,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Äldre lavtallskog, hällmark</t>
+          <t>Äldre barrskog,</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14775,10 +14740,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122485585</v>
+        <v>122485589</v>
       </c>
       <c r="B117" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14787,25 +14752,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14815,10 +14780,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>564155</v>
+        <v>563487</v>
       </c>
       <c r="R117" t="n">
-        <v>6626751</v>
+        <v>6626901</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -14864,7 +14829,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14886,10 +14851,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122485588</v>
+        <v>122485579</v>
       </c>
       <c r="B118" t="n">
-        <v>98365</v>
+        <v>92235</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14898,25 +14863,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14926,10 +14891,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>564140</v>
+        <v>563414</v>
       </c>
       <c r="R118" t="n">
-        <v>6626788</v>
+        <v>6626837</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14975,7 +14940,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Äldre barrskog,</t>
+          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14997,10 +14962,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122485589</v>
+        <v>122485586</v>
       </c>
       <c r="B119" t="n">
-        <v>98365</v>
+        <v>100631</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15009,25 +14974,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15037,10 +15002,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>563487</v>
+        <v>564170</v>
       </c>
       <c r="R119" t="n">
-        <v>6626901</v>
+        <v>6626836</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -15086,7 +15051,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
+          <t>Äldre barrskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15108,10 +15073,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122485579</v>
+        <v>122485581</v>
       </c>
       <c r="B120" t="n">
-        <v>92235</v>
+        <v>92225</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15124,21 +15089,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>788</v>
+        <v>4361</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -15148,10 +15113,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>563414</v>
+        <v>563669</v>
       </c>
       <c r="R120" t="n">
-        <v>6626837</v>
+        <v>6626870</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -15197,7 +15162,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Äldre barrskog, svagt fuktig ört-ristyp</t>
+          <t>Äldre talldominerad barrskog</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15219,10 +15184,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122485586</v>
+        <v>123809320</v>
       </c>
       <c r="B121" t="n">
-        <v>100631</v>
+        <v>100682</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15253,19 +15218,27 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Väst Sothällen, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>564170</v>
+        <v>564165</v>
       </c>
       <c r="R121" t="n">
-        <v>6626836</v>
+        <v>6626834</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15289,12 +15262,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15303,37 +15276,34 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Gammal barrblandskog, översilning</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122485581</v>
+        <v>123809435</v>
       </c>
       <c r="B122" t="n">
-        <v>92225</v>
+        <v>91435</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15342,41 +15312,44 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4361</v>
+        <v>1209</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Väst Sothällen, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>563669</v>
+        <v>564075</v>
       </c>
       <c r="R122" t="n">
-        <v>6626870</v>
+        <v>6626696</v>
       </c>
       <c r="S122" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15400,12 +15373,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15414,262 +15387,32 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Äldre talldominerad barrskog</t>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY122" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>123809435</v>
-      </c>
-      <c r="B123" t="n">
-        <v>91433</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E123" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="P123" t="inlineStr">
-        <is>
-          <t>Sothällen VSV, Vstm</t>
-        </is>
-      </c>
-      <c r="Q123" t="n">
-        <v>564075</v>
-      </c>
-      <c r="R123" t="n">
-        <v>6626696</v>
-      </c>
-      <c r="S123" t="n">
-        <v>5</v>
-      </c>
-      <c r="T123" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="AD123" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE123" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF123" t="inlineStr"/>
-      <c r="AG123" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AT123" t="inlineStr"/>
-      <c r="AW123" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>123809320</v>
-      </c>
-      <c r="B124" t="n">
-        <v>100680</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E124" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>Sothällen V, Vstm</t>
-        </is>
-      </c>
-      <c r="Q124" t="n">
-        <v>564165</v>
-      </c>
-      <c r="R124" t="n">
-        <v>6626834</v>
-      </c>
-      <c r="S124" t="n">
-        <v>10</v>
-      </c>
-      <c r="T124" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="AD124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF124" t="inlineStr"/>
-      <c r="AG124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog, översilning</t>
-        </is>
-      </c>
-      <c r="AT124" t="inlineStr"/>
-      <c r="AW124" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr"/>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -15184,10 +15184,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123809320</v>
+        <v>123809435</v>
       </c>
       <c r="B121" t="n">
-        <v>100682</v>
+        <v>91435</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15196,49 +15196,44 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>564165</v>
+        <v>564075</v>
       </c>
       <c r="R121" t="n">
-        <v>6626834</v>
+        <v>6626696</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15282,7 +15277,12 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog, översilning</t>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15300,10 +15300,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123809435</v>
+        <v>123809320</v>
       </c>
       <c r="B122" t="n">
-        <v>91435</v>
+        <v>100257</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15312,44 +15312,49 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>564075</v>
+        <v>564165</v>
       </c>
       <c r="R122" t="n">
-        <v>6626696</v>
+        <v>6626834</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15393,12 +15398,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Gammal barrblandskog, översilning</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -15184,10 +15184,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123809435</v>
+        <v>123809320</v>
       </c>
       <c r="B121" t="n">
-        <v>91435</v>
+        <v>100257</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15196,44 +15196,49 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>564075</v>
+        <v>564165</v>
       </c>
       <c r="R121" t="n">
-        <v>6626696</v>
+        <v>6626834</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15277,12 +15282,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Gammal barrblandskog, översilning</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15300,10 +15300,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123809320</v>
+        <v>123809435</v>
       </c>
       <c r="B122" t="n">
-        <v>100257</v>
+        <v>91435</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15312,49 +15312,44 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>564165</v>
+        <v>564075</v>
       </c>
       <c r="R122" t="n">
-        <v>6626834</v>
+        <v>6626696</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15398,7 +15393,12 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog, översilning</t>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -15184,10 +15184,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123809320</v>
+        <v>123809435</v>
       </c>
       <c r="B121" t="n">
-        <v>100257</v>
+        <v>91435</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15196,49 +15196,44 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>564165</v>
+        <v>564075</v>
       </c>
       <c r="R121" t="n">
-        <v>6626834</v>
+        <v>6626696</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15282,7 +15277,12 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog, översilning</t>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15300,10 +15300,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123809435</v>
+        <v>123809320</v>
       </c>
       <c r="B122" t="n">
-        <v>91435</v>
+        <v>100257</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15312,44 +15312,49 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>564075</v>
+        <v>564165</v>
       </c>
       <c r="R122" t="n">
-        <v>6626696</v>
+        <v>6626834</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15393,12 +15398,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Gammal barrblandskog, översilning</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -15184,10 +15184,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123809320</v>
+        <v>123809435</v>
       </c>
       <c r="B121" t="n">
-        <v>100279</v>
+        <v>91457</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15196,49 +15196,44 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>564165</v>
+        <v>564075</v>
       </c>
       <c r="R121" t="n">
-        <v>6626834</v>
+        <v>6626696</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15282,7 +15277,12 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog, översilning</t>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15300,10 +15300,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123809435</v>
+        <v>123809320</v>
       </c>
       <c r="B122" t="n">
-        <v>91457</v>
+        <v>100279</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15312,44 +15312,49 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>564075</v>
+        <v>564165</v>
       </c>
       <c r="R122" t="n">
-        <v>6626696</v>
+        <v>6626834</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15393,12 +15398,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Gammal barrblandskog, översilning</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -15416,64 +15416,59 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126857966</v>
+        <v>126858024</v>
       </c>
       <c r="B123" t="n">
-        <v>98361</v>
+        <v>92643</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Grotten OSO, Vstm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>563562</v>
+        <v>563593</v>
       </c>
       <c r="R123" t="n">
-        <v>6626774</v>
+        <v>6626829</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15535,59 +15530,64 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126858024</v>
+        <v>126857966</v>
       </c>
       <c r="B124" t="n">
-        <v>92569</v>
+        <v>98436</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Grotten OSO, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>563593</v>
+        <v>563562</v>
       </c>
       <c r="R124" t="n">
-        <v>6626829</v>
+        <v>6626774</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>126857867</v>
       </c>
       <c r="B125" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>126857945</v>
       </c>
       <c r="B126" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>126857691</v>
       </c>
       <c r="B127" t="n">
-        <v>92527</v>
+        <v>92601</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>126882807</v>
       </c>
       <c r="B128" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>126882851</v>
       </c>
       <c r="B129" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>126882801</v>
       </c>
       <c r="B131" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>126882697</v>
       </c>
       <c r="B132" t="n">
-        <v>92527</v>
+        <v>92601</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>127063880</v>
       </c>
       <c r="B133" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>127063850</v>
       </c>
       <c r="B134" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>127063878</v>
       </c>
       <c r="B135" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>127063858</v>
       </c>
       <c r="B136" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -15419,7 +15419,7 @@
         <v>126858024</v>
       </c>
       <c r="B123" t="n">
-        <v>92643</v>
+        <v>92649</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>126857966</v>
       </c>
       <c r="B124" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>126857867</v>
       </c>
       <c r="B125" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>126857945</v>
       </c>
       <c r="B126" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>126857691</v>
       </c>
       <c r="B127" t="n">
-        <v>92601</v>
+        <v>92607</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>126882807</v>
       </c>
       <c r="B128" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>126882851</v>
       </c>
       <c r="B129" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>126882801</v>
       </c>
       <c r="B131" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>126882697</v>
       </c>
       <c r="B132" t="n">
-        <v>92601</v>
+        <v>92607</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>127063880</v>
       </c>
       <c r="B133" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>127063850</v>
       </c>
       <c r="B134" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>127063878</v>
       </c>
       <c r="B135" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>127063858</v>
       </c>
       <c r="B136" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -16001,48 +16001,53 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126882807</v>
+        <v>126882851</v>
       </c>
       <c r="B128" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>564092</v>
+        <v>564111</v>
       </c>
       <c r="R128" t="n">
-        <v>6626680</v>
+        <v>6626656</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -16075,6 +16080,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>spridda förekomster.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16112,53 +16122,48 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126882851</v>
+        <v>126882807</v>
       </c>
       <c r="B129" t="n">
-        <v>98442</v>
+        <v>91325</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>564111</v>
+        <v>564092</v>
       </c>
       <c r="R129" t="n">
-        <v>6626656</v>
+        <v>6626680</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -16191,11 +16196,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>spridda förekomster.</t>
         </is>
       </c>
       <c r="AD129" t="b">

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -15419,7 +15419,7 @@
         <v>126858024</v>
       </c>
       <c r="B123" t="n">
-        <v>92649</v>
+        <v>92650</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>126857966</v>
       </c>
       <c r="B124" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>126857867</v>
       </c>
       <c r="B125" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>126857945</v>
       </c>
       <c r="B126" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>126857691</v>
       </c>
       <c r="B127" t="n">
-        <v>92607</v>
+        <v>92608</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16001,53 +16001,48 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126882851</v>
+        <v>126882807</v>
       </c>
       <c r="B128" t="n">
-        <v>98442</v>
+        <v>91326</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>564111</v>
+        <v>564092</v>
       </c>
       <c r="R128" t="n">
-        <v>6626656</v>
+        <v>6626680</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -16080,11 +16075,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>spridda förekomster.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16122,48 +16112,53 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126882807</v>
+        <v>126882851</v>
       </c>
       <c r="B129" t="n">
-        <v>91325</v>
+        <v>98443</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>564092</v>
+        <v>564111</v>
       </c>
       <c r="R129" t="n">
-        <v>6626680</v>
+        <v>6626656</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -16196,6 +16191,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>spridda förekomster.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -16366,7 +16366,7 @@
         <v>126882801</v>
       </c>
       <c r="B131" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>126882697</v>
       </c>
       <c r="B132" t="n">
-        <v>92607</v>
+        <v>92608</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>127063880</v>
       </c>
       <c r="B133" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>127063850</v>
       </c>
       <c r="B134" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>127063878</v>
       </c>
       <c r="B135" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>127063858</v>
       </c>
       <c r="B136" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -16001,48 +16001,53 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126882807</v>
+        <v>126882851</v>
       </c>
       <c r="B128" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>564092</v>
+        <v>564111</v>
       </c>
       <c r="R128" t="n">
-        <v>6626680</v>
+        <v>6626656</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -16075,6 +16080,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>spridda förekomster.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16112,53 +16122,48 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126882851</v>
+        <v>126882807</v>
       </c>
       <c r="B129" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>564111</v>
+        <v>564092</v>
       </c>
       <c r="R129" t="n">
-        <v>6626656</v>
+        <v>6626680</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -16191,11 +16196,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>spridda förekomster.</t>
         </is>
       </c>
       <c r="AD129" t="b">

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -15416,59 +15416,64 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126858024</v>
+        <v>126857966</v>
       </c>
       <c r="B123" t="n">
-        <v>92650</v>
+        <v>98443</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Grotten OSO, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>563593</v>
+        <v>563562</v>
       </c>
       <c r="R123" t="n">
-        <v>6626829</v>
+        <v>6626774</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15530,64 +15535,59 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126857966</v>
+        <v>126858024</v>
       </c>
       <c r="B124" t="n">
-        <v>98443</v>
+        <v>92650</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Grotten OSO, Vstm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>563562</v>
+        <v>563593</v>
       </c>
       <c r="R124" t="n">
-        <v>6626774</v>
+        <v>6626829</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -16001,53 +16001,48 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126882851</v>
+        <v>126882807</v>
       </c>
       <c r="B128" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>564111</v>
+        <v>564092</v>
       </c>
       <c r="R128" t="n">
-        <v>6626656</v>
+        <v>6626680</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -16080,11 +16075,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>spridda förekomster.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16122,48 +16112,53 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126882807</v>
+        <v>126882851</v>
       </c>
       <c r="B129" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>564092</v>
+        <v>564111</v>
       </c>
       <c r="R129" t="n">
-        <v>6626680</v>
+        <v>6626656</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -16196,6 +16191,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>spridda förekomster.</t>
         </is>
       </c>
       <c r="AD129" t="b">

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -15419,7 +15419,7 @@
         <v>126857966</v>
       </c>
       <c r="B123" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>126858024</v>
       </c>
       <c r="B124" t="n">
-        <v>92650</v>
+        <v>92654</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>126857867</v>
       </c>
       <c r="B125" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>126857945</v>
       </c>
       <c r="B126" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>126857691</v>
       </c>
       <c r="B127" t="n">
-        <v>92608</v>
+        <v>92612</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>126882807</v>
       </c>
       <c r="B128" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>126882851</v>
       </c>
       <c r="B129" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>126882773</v>
       </c>
       <c r="B130" t="n">
-        <v>56584</v>
+        <v>56588</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>126882801</v>
       </c>
       <c r="B131" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>126882697</v>
       </c>
       <c r="B132" t="n">
-        <v>92608</v>
+        <v>92612</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>127063880</v>
       </c>
       <c r="B133" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>127063850</v>
       </c>
       <c r="B134" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>127063878</v>
       </c>
       <c r="B135" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>127063858</v>
       </c>
       <c r="B136" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY136"/>
+  <dimension ref="A1:AY138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17042,6 +17042,235 @@
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>127689891</v>
+      </c>
+      <c r="B137" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>563516</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6626795</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>127689849</v>
+      </c>
+      <c r="B138" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>563681</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6626774</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -15416,64 +15416,59 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126857966</v>
+        <v>126858024</v>
       </c>
       <c r="B123" t="n">
-        <v>98447</v>
+        <v>92654</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Grotten OSO, Vstm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>563562</v>
+        <v>563593</v>
       </c>
       <c r="R123" t="n">
-        <v>6626774</v>
+        <v>6626829</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15535,59 +15530,64 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126858024</v>
+        <v>126857966</v>
       </c>
       <c r="B124" t="n">
-        <v>92654</v>
+        <v>98448</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Grotten OSO, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>563593</v>
+        <v>563562</v>
       </c>
       <c r="R124" t="n">
-        <v>6626829</v>
+        <v>6626774</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>126857867</v>
       </c>
       <c r="B125" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>126857945</v>
       </c>
       <c r="B126" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -16001,48 +16001,53 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126882807</v>
+        <v>126882851</v>
       </c>
       <c r="B128" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>564092</v>
+        <v>564111</v>
       </c>
       <c r="R128" t="n">
-        <v>6626680</v>
+        <v>6626656</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -16075,6 +16080,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>spridda förekomster.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16112,53 +16122,48 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126882851</v>
+        <v>126882807</v>
       </c>
       <c r="B129" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>564111</v>
+        <v>564092</v>
       </c>
       <c r="R129" t="n">
-        <v>6626656</v>
+        <v>6626680</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -16191,11 +16196,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>spridda förekomster.</t>
         </is>
       </c>
       <c r="AD129" t="b">

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -16001,53 +16001,48 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126882851</v>
+        <v>126882807</v>
       </c>
       <c r="B128" t="n">
-        <v>98448</v>
+        <v>91330</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>564111</v>
+        <v>564092</v>
       </c>
       <c r="R128" t="n">
-        <v>6626656</v>
+        <v>6626680</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -16080,11 +16075,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>spridda förekomster.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16122,48 +16112,53 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126882807</v>
+        <v>126882851</v>
       </c>
       <c r="B129" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>564092</v>
+        <v>564111</v>
       </c>
       <c r="R129" t="n">
-        <v>6626680</v>
+        <v>6626656</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -16196,6 +16191,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>spridda förekomster.</t>
         </is>
       </c>
       <c r="AD129" t="b">

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -16004,7 +16004,7 @@
         <v>126882807</v>
       </c>
       <c r="B128" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>126882851</v>
       </c>
       <c r="B129" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>126882773</v>
       </c>
       <c r="B130" t="n">
-        <v>56588</v>
+        <v>56590</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>126882801</v>
       </c>
       <c r="B131" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>126882697</v>
       </c>
       <c r="B132" t="n">
-        <v>92612</v>
+        <v>92614</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>127063880</v>
       </c>
       <c r="B133" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>127063850</v>
       </c>
       <c r="B134" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>127063878</v>
       </c>
       <c r="B135" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>127063858</v>
       </c>
       <c r="B136" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>127689891</v>
       </c>
       <c r="B137" t="n">
-        <v>92616</v>
+        <v>92618</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>127689849</v>
       </c>
       <c r="B138" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY138"/>
+  <dimension ref="A1:AY154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16591,7 +16591,7 @@
         <v>127063880</v>
       </c>
       <c r="B133" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>127063850</v>
       </c>
       <c r="B134" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>127063878</v>
       </c>
       <c r="B135" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>127063858</v>
       </c>
       <c r="B136" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>127689891</v>
       </c>
       <c r="B137" t="n">
-        <v>92618</v>
+        <v>92624</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>127689849</v>
       </c>
       <c r="B138" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17270,6 +17270,1827 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>128046156</v>
+      </c>
+      <c r="B139" t="n">
+        <v>90722</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>564059</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6626681</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>128046074</v>
+      </c>
+      <c r="B140" t="n">
+        <v>92656</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>563797</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6626921</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>128046023</v>
+      </c>
+      <c r="B141" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>563747</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6626856</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>128046036</v>
+      </c>
+      <c r="B142" t="n">
+        <v>92644</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>563752</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6626915</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>Barrblandskog, mosskant</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>128046194</v>
+      </c>
+      <c r="B143" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>563961</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6626678</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>Barrblandskog, lövinslag</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>128046174</v>
+      </c>
+      <c r="B144" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>563967</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6626681</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>128046080</v>
+      </c>
+      <c r="B145" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>563965</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6626884</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>128046037</v>
+      </c>
+      <c r="B146" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>563752</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6626915</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>128046076</v>
+      </c>
+      <c r="B147" t="n">
+        <v>90834</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>2051</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Rotfingersvamp</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Ramaria boreimaxima</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>563800</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6626921</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>128046078</v>
+      </c>
+      <c r="B148" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>563957</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6626876</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>128046184</v>
+      </c>
+      <c r="B149" t="n">
+        <v>92620</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>563967</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6626681</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>128046002</v>
+      </c>
+      <c r="B150" t="n">
+        <v>92644</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>563749</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6626807</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>128046021</v>
+      </c>
+      <c r="B151" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>563750</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6626840</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>128046123</v>
+      </c>
+      <c r="B152" t="n">
+        <v>92630</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>788</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>564163</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6626836</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>Blandskog. fuktigt</t>
+        </is>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>128046033</v>
+      </c>
+      <c r="B153" t="n">
+        <v>92644</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>563749</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6626916</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>128046041</v>
+      </c>
+      <c r="B154" t="n">
+        <v>92656</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>563741</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6626930</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY154"/>
+  <dimension ref="A1:AY158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16591,7 +16591,7 @@
         <v>127063880</v>
       </c>
       <c r="B133" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>127063850</v>
       </c>
       <c r="B134" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>127063878</v>
       </c>
       <c r="B135" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>127063858</v>
       </c>
       <c r="B136" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>127689891</v>
       </c>
       <c r="B137" t="n">
-        <v>92624</v>
+        <v>92627</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>127689849</v>
       </c>
       <c r="B138" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>128046156</v>
       </c>
       <c r="B139" t="n">
-        <v>90722</v>
+        <v>90725</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>128046074</v>
       </c>
       <c r="B140" t="n">
-        <v>92656</v>
+        <v>92659</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>128046023</v>
       </c>
       <c r="B141" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>128046036</v>
       </c>
       <c r="B142" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>128046194</v>
       </c>
       <c r="B143" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>128046174</v>
       </c>
       <c r="B144" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>128046080</v>
       </c>
       <c r="B145" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>128046037</v>
       </c>
       <c r="B146" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>128046076</v>
       </c>
       <c r="B147" t="n">
-        <v>90834</v>
+        <v>90837</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>128046078</v>
       </c>
       <c r="B148" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>128046184</v>
       </c>
       <c r="B149" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>128046002</v>
       </c>
       <c r="B150" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>128046021</v>
       </c>
       <c r="B151" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18752,10 +18752,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128046123</v>
+        <v>128046041</v>
       </c>
       <c r="B152" t="n">
-        <v>92630</v>
+        <v>92659</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18763,26 +18763,26 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>788</v>
+        <v>5449</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>564163</v>
+        <v>563741</v>
       </c>
       <c r="R152" t="n">
-        <v>6626836</v>
+        <v>6626930</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18848,7 +18848,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>Blandskog. fuktigt</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -18866,10 +18866,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128046033</v>
+        <v>128046123</v>
       </c>
       <c r="B153" t="n">
-        <v>92644</v>
+        <v>92633</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18877,26 +18877,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2059</v>
+        <v>788</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>563749</v>
+        <v>564163</v>
       </c>
       <c r="R153" t="n">
-        <v>6626916</v>
+        <v>6626836</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Blandskog. fuktigt</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -18980,10 +18980,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128046041</v>
+        <v>128046033</v>
       </c>
       <c r="B154" t="n">
-        <v>92656</v>
+        <v>92647</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18991,26 +18991,26 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -19026,10 +19026,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563741</v>
+        <v>563749</v>
       </c>
       <c r="R154" t="n">
-        <v>6626930</v>
+        <v>6626916</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -19091,6 +19091,452 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>128084971</v>
+      </c>
+      <c r="B155" t="n">
+        <v>92671</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Phellodon violascens</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>564164</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6626836</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>Blandskog, fuktstråk</t>
+        </is>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>128074263</v>
+      </c>
+      <c r="B156" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Sothällen, Sothällen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>563999</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6626788</v>
+      </c>
+      <c r="S156" t="n">
+        <v>17</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>128085081</v>
+      </c>
+      <c r="B157" t="n">
+        <v>91574</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Gropticka</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>563945</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6626738</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Barrved</t>
+        </is>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>128084970</v>
+      </c>
+      <c r="B158" t="n">
+        <v>92673</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>564164</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6626836</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>Blandskog, fuktstråk</t>
+        </is>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY158"/>
+  <dimension ref="A1:AY159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17047,7 +17047,7 @@
         <v>127689891</v>
       </c>
       <c r="B137" t="n">
-        <v>92627</v>
+        <v>92635</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>127689849</v>
       </c>
       <c r="B138" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>128046156</v>
       </c>
       <c r="B139" t="n">
-        <v>90725</v>
+        <v>90733</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>128046074</v>
       </c>
       <c r="B140" t="n">
-        <v>92659</v>
+        <v>92667</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>128046023</v>
       </c>
       <c r="B141" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>128046036</v>
       </c>
       <c r="B142" t="n">
-        <v>92647</v>
+        <v>92655</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>128046194</v>
       </c>
       <c r="B143" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>128046174</v>
       </c>
       <c r="B144" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17954,10 +17954,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128046080</v>
+        <v>128046037</v>
       </c>
       <c r="B145" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -18000,10 +18000,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>563965</v>
+        <v>563752</v>
       </c>
       <c r="R145" t="n">
-        <v>6626884</v>
+        <v>6626915</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -18068,10 +18068,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128046037</v>
+        <v>128046080</v>
       </c>
       <c r="B146" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -18114,10 +18114,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>563752</v>
+        <v>563965</v>
       </c>
       <c r="R146" t="n">
-        <v>6626915</v>
+        <v>6626884</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18164,7 +18164,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -18185,7 +18185,7 @@
         <v>128046076</v>
       </c>
       <c r="B147" t="n">
-        <v>90837</v>
+        <v>90845</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>128046078</v>
       </c>
       <c r="B148" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>128046184</v>
       </c>
       <c r="B149" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18524,37 +18524,37 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128046002</v>
+        <v>128046021</v>
       </c>
       <c r="B150" t="n">
-        <v>92647</v>
+        <v>92639</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -18570,10 +18570,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>563749</v>
+        <v>563750</v>
       </c>
       <c r="R150" t="n">
-        <v>6626807</v>
+        <v>6626840</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -18638,37 +18638,37 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128046021</v>
+        <v>128046002</v>
       </c>
       <c r="B151" t="n">
-        <v>92631</v>
+        <v>92655</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -18684,10 +18684,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>563750</v>
+        <v>563749</v>
       </c>
       <c r="R151" t="n">
-        <v>6626840</v>
+        <v>6626807</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18752,10 +18752,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128046041</v>
+        <v>128046123</v>
       </c>
       <c r="B152" t="n">
-        <v>92659</v>
+        <v>92641</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18763,26 +18763,26 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5449</v>
+        <v>788</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>563741</v>
+        <v>564163</v>
       </c>
       <c r="R152" t="n">
-        <v>6626930</v>
+        <v>6626836</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18848,7 +18848,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Blandskog. fuktigt</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -18866,10 +18866,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128046123</v>
+        <v>128046033</v>
       </c>
       <c r="B153" t="n">
-        <v>92633</v>
+        <v>92655</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18877,26 +18877,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>788</v>
+        <v>2059</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>564163</v>
+        <v>563749</v>
       </c>
       <c r="R153" t="n">
-        <v>6626836</v>
+        <v>6626916</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Blandskog. fuktigt</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -18980,10 +18980,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128046033</v>
+        <v>128046041</v>
       </c>
       <c r="B154" t="n">
-        <v>92647</v>
+        <v>92667</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18991,26 +18991,26 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -19026,10 +19026,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563749</v>
+        <v>563741</v>
       </c>
       <c r="R154" t="n">
-        <v>6626916</v>
+        <v>6626930</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -19094,59 +19094,48 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128084971</v>
+        <v>128074263</v>
       </c>
       <c r="B155" t="n">
-        <v>92671</v>
+        <v>98384</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1968</v>
+        <v>219790</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothällen, Sothällen, Vstm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>564164</v>
+        <v>563999</v>
       </c>
       <c r="R155" t="n">
-        <v>6626836</v>
+        <v>6626788</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -19173,45 +19162,49 @@
           <t>2025-08-30</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-30</t>
         </is>
       </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>Blandskog, fuktstråk</t>
-        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128074263</v>
+        <v>128073806</v>
       </c>
       <c r="B156" t="n">
-        <v>98384</v>
+        <v>56864</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19219,37 +19212,56 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Sothällen, Sothällen, Vstm</t>
+          <t>Naddtorpsskogen, Ramnäs, Naddtorpsskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>563999</v>
+        <v>564175</v>
       </c>
       <c r="R156" t="n">
-        <v>6626788</v>
+        <v>6626821</v>
       </c>
       <c r="S156" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -19278,7 +19290,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -19288,7 +19300,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -19299,26 +19311,31 @@
       </c>
       <c r="AG156" t="b">
         <v>0</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128085081</v>
+        <v>128084971</v>
       </c>
       <c r="B157" t="n">
-        <v>91574</v>
+        <v>92671</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19326,25 +19343,33 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1101</v>
+        <v>1968</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
@@ -19353,10 +19378,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>563945</v>
+        <v>564164</v>
       </c>
       <c r="R157" t="n">
-        <v>6626738</v>
+        <v>6626836</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -19403,12 +19428,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>Barrved</t>
+          <t>Blandskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -19419,51 +19439,43 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Tom Sävström, Kalle Källebrink, Staffan Öström</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128084970</v>
+        <v>128085081</v>
       </c>
       <c r="B158" t="n">
-        <v>92673</v>
+        <v>91574</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5964</v>
+        <v>1101</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
@@ -19472,10 +19484,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>564164</v>
+        <v>563945</v>
       </c>
       <c r="R158" t="n">
-        <v>6626836</v>
+        <v>6626738</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19522,7 +19534,12 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>Blandskog, fuktstråk</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>Barrved</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -19533,10 +19550,124 @@
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Tom Sävström, Kalle Källebrink, Staffan Öström</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>128084970</v>
+      </c>
+      <c r="B159" t="n">
+        <v>92673</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>564164</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6626836</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>Blandskog, fuktstråk</t>
+        </is>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Kalle Källebrink</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -17047,7 +17047,7 @@
         <v>127689891</v>
       </c>
       <c r="B137" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>127689849</v>
       </c>
       <c r="B138" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>128046156</v>
       </c>
       <c r="B139" t="n">
-        <v>90733</v>
+        <v>90734</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>128046074</v>
       </c>
       <c r="B140" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>128046023</v>
       </c>
       <c r="B141" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>128046036</v>
       </c>
       <c r="B142" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>128046194</v>
       </c>
       <c r="B143" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>128046174</v>
       </c>
       <c r="B144" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17954,10 +17954,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128046037</v>
+        <v>128046080</v>
       </c>
       <c r="B145" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -18000,10 +18000,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>563752</v>
+        <v>563965</v>
       </c>
       <c r="R145" t="n">
-        <v>6626915</v>
+        <v>6626884</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -18068,10 +18068,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128046080</v>
+        <v>128046037</v>
       </c>
       <c r="B146" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -18114,10 +18114,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>563965</v>
+        <v>563752</v>
       </c>
       <c r="R146" t="n">
-        <v>6626884</v>
+        <v>6626915</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18164,7 +18164,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -18185,7 +18185,7 @@
         <v>128046076</v>
       </c>
       <c r="B147" t="n">
-        <v>90845</v>
+        <v>90846</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>128046078</v>
       </c>
       <c r="B148" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>128046184</v>
       </c>
       <c r="B149" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18524,37 +18524,37 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128046021</v>
+        <v>128046002</v>
       </c>
       <c r="B150" t="n">
-        <v>92639</v>
+        <v>92656</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -18570,10 +18570,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>563750</v>
+        <v>563749</v>
       </c>
       <c r="R150" t="n">
-        <v>6626840</v>
+        <v>6626807</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -18638,37 +18638,37 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128046002</v>
+        <v>128046021</v>
       </c>
       <c r="B151" t="n">
-        <v>92655</v>
+        <v>92640</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -18684,10 +18684,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>563749</v>
+        <v>563750</v>
       </c>
       <c r="R151" t="n">
-        <v>6626807</v>
+        <v>6626840</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18755,7 +18755,7 @@
         <v>128046123</v>
       </c>
       <c r="B152" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18866,10 +18866,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128046033</v>
+        <v>128046041</v>
       </c>
       <c r="B153" t="n">
-        <v>92655</v>
+        <v>92668</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18877,26 +18877,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>563749</v>
+        <v>563741</v>
       </c>
       <c r="R153" t="n">
-        <v>6626916</v>
+        <v>6626930</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -18980,10 +18980,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128046041</v>
+        <v>128046033</v>
       </c>
       <c r="B154" t="n">
-        <v>92667</v>
+        <v>92656</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18991,26 +18991,26 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -19026,10 +19026,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563741</v>
+        <v>563749</v>
       </c>
       <c r="R154" t="n">
-        <v>6626930</v>
+        <v>6626916</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -19097,7 +19097,7 @@
         <v>128074263</v>
       </c>
       <c r="B155" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Staffan Öström</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -19335,7 +19335,7 @@
         <v>128084971</v>
       </c>
       <c r="B157" t="n">
-        <v>92671</v>
+        <v>92672</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>128085081</v>
       </c>
       <c r="B158" t="n">
-        <v>91574</v>
+        <v>91575</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>128084970</v>
       </c>
       <c r="B159" t="n">
-        <v>92673</v>
+        <v>92674</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -17954,7 +17954,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128046080</v>
+        <v>128046037</v>
       </c>
       <c r="B145" t="n">
         <v>92640</v>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -18000,10 +18000,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>563965</v>
+        <v>563752</v>
       </c>
       <c r="R145" t="n">
-        <v>6626884</v>
+        <v>6626915</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -18068,7 +18068,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128046037</v>
+        <v>128046080</v>
       </c>
       <c r="B146" t="n">
         <v>92640</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -18114,10 +18114,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>563752</v>
+        <v>563965</v>
       </c>
       <c r="R146" t="n">
-        <v>6626915</v>
+        <v>6626884</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18164,7 +18164,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -18866,10 +18866,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128046041</v>
+        <v>128046033</v>
       </c>
       <c r="B153" t="n">
-        <v>92668</v>
+        <v>92656</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18877,26 +18877,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>563741</v>
+        <v>563749</v>
       </c>
       <c r="R153" t="n">
-        <v>6626930</v>
+        <v>6626916</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -18980,10 +18980,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128046033</v>
+        <v>128046041</v>
       </c>
       <c r="B154" t="n">
-        <v>92656</v>
+        <v>92668</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18991,26 +18991,26 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -19026,10 +19026,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563749</v>
+        <v>563741</v>
       </c>
       <c r="R154" t="n">
-        <v>6626916</v>
+        <v>6626930</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY159"/>
+  <dimension ref="A1:AY160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17047,7 +17047,7 @@
         <v>127689891</v>
       </c>
       <c r="B137" t="n">
-        <v>92636</v>
+        <v>92637</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>127689849</v>
       </c>
       <c r="B138" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>128046156</v>
       </c>
       <c r="B139" t="n">
-        <v>90734</v>
+        <v>90735</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>128046074</v>
       </c>
       <c r="B140" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>128046023</v>
       </c>
       <c r="B141" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>128046036</v>
       </c>
       <c r="B142" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>128046194</v>
       </c>
       <c r="B143" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>128046174</v>
       </c>
       <c r="B144" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17954,10 +17954,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128046037</v>
+        <v>128046080</v>
       </c>
       <c r="B145" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -18000,10 +18000,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>563752</v>
+        <v>563965</v>
       </c>
       <c r="R145" t="n">
-        <v>6626915</v>
+        <v>6626884</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -18068,10 +18068,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128046080</v>
+        <v>128046037</v>
       </c>
       <c r="B146" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -18114,10 +18114,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>563965</v>
+        <v>563752</v>
       </c>
       <c r="R146" t="n">
-        <v>6626884</v>
+        <v>6626915</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18164,7 +18164,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -18185,7 +18185,7 @@
         <v>128046076</v>
       </c>
       <c r="B147" t="n">
-        <v>90846</v>
+        <v>90847</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>128046078</v>
       </c>
       <c r="B148" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>128046184</v>
       </c>
       <c r="B149" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>128046002</v>
       </c>
       <c r="B150" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>128046021</v>
       </c>
       <c r="B151" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>128046123</v>
       </c>
       <c r="B152" t="n">
-        <v>92642</v>
+        <v>92643</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18866,10 +18866,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128046033</v>
+        <v>128046041</v>
       </c>
       <c r="B153" t="n">
-        <v>92656</v>
+        <v>92669</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18877,26 +18877,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>563749</v>
+        <v>563741</v>
       </c>
       <c r="R153" t="n">
-        <v>6626916</v>
+        <v>6626930</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -18980,10 +18980,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128046041</v>
+        <v>128046033</v>
       </c>
       <c r="B154" t="n">
-        <v>92668</v>
+        <v>92657</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18991,26 +18991,26 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -19026,10 +19026,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563741</v>
+        <v>563749</v>
       </c>
       <c r="R154" t="n">
-        <v>6626930</v>
+        <v>6626916</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -19097,7 +19097,7 @@
         <v>128074263</v>
       </c>
       <c r="B155" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19201,67 +19201,59 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128073806</v>
+        <v>128084971</v>
       </c>
       <c r="B156" t="n">
-        <v>56864</v>
+        <v>92673</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100138</v>
+        <v>1968</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Naddtorpsskogen, Ramnäs, Naddtorpsskogen, Ramnäs, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>564175</v>
+        <v>564164</v>
       </c>
       <c r="R156" t="n">
-        <v>6626821</v>
+        <v>6626836</v>
       </c>
       <c r="S156" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -19288,54 +19280,45 @@
           <t>2025-08-30</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-30</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>Blandskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Staffan Öström</t>
+          <t>Tom Sävström, Kalle Källebrink, Staffan Öström</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128084971</v>
+        <v>128085081</v>
       </c>
       <c r="B157" t="n">
-        <v>92672</v>
+        <v>91576</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19343,33 +19326,25 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1968</v>
+        <v>1101</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
@@ -19378,10 +19353,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>564164</v>
+        <v>563945</v>
       </c>
       <c r="R157" t="n">
-        <v>6626836</v>
+        <v>6626738</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -19428,7 +19403,12 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>Blandskog, fuktstråk</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Barrved</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -19446,36 +19426,44 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128085081</v>
+        <v>128084970</v>
       </c>
       <c r="B158" t="n">
-        <v>91575</v>
+        <v>92675</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1101</v>
+        <v>5964</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
@@ -19484,10 +19472,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>563945</v>
+        <v>564164</v>
       </c>
       <c r="R158" t="n">
-        <v>6626738</v>
+        <v>6626836</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19534,12 +19522,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>Barrved</t>
+          <t>Blandskog, fuktstråk</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -19550,63 +19533,59 @@
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Tom Sävström, Kalle Källebrink, Staffan Öström</t>
+          <t>Tom Sävström, Kalle Källebrink</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128084970</v>
+        <v>128268019</v>
       </c>
       <c r="B159" t="n">
-        <v>92674</v>
+        <v>92644</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothällen,V, Vstm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>564164</v>
+        <v>564163</v>
       </c>
       <c r="R159" t="n">
-        <v>6626836</v>
+        <v>6626834</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19641,6 +19620,11 @@
           <t>2025-08-30</t>
         </is>
       </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Återfynd.</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
@@ -19651,23 +19635,149 @@
       <c r="AG159" t="b">
         <v>0</v>
       </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>Blandskog, fuktstråk</t>
-        </is>
-      </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Kalle Källebrink</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Tom Sävström, Kalle Källebrink</t>
+          <t>Kalle Källebrink</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>128073806</v>
+      </c>
+      <c r="B160" t="n">
+        <v>56864</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Naddtorpsskogen, Ramnäs, Naddtorpsskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>564175</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6626821</v>
+      </c>
+      <c r="S160" t="n">
+        <v>5</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Staffan Öström</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -17047,7 +17047,7 @@
         <v>127689891</v>
       </c>
       <c r="B137" t="n">
-        <v>92637</v>
+        <v>92638</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>127689849</v>
       </c>
       <c r="B138" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>128046156</v>
       </c>
       <c r="B139" t="n">
-        <v>90735</v>
+        <v>90736</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>128046074</v>
       </c>
       <c r="B140" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>128046023</v>
       </c>
       <c r="B141" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>128046036</v>
       </c>
       <c r="B142" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>128046194</v>
       </c>
       <c r="B143" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>128046174</v>
       </c>
       <c r="B144" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>128046080</v>
       </c>
       <c r="B145" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>128046037</v>
       </c>
       <c r="B146" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>128046076</v>
       </c>
       <c r="B147" t="n">
-        <v>90847</v>
+        <v>90848</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>128046078</v>
       </c>
       <c r="B148" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>128046184</v>
       </c>
       <c r="B149" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>128046002</v>
       </c>
       <c r="B150" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>128046021</v>
       </c>
       <c r="B151" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>128046123</v>
       </c>
       <c r="B152" t="n">
-        <v>92643</v>
+        <v>92644</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18866,10 +18866,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128046041</v>
+        <v>128046033</v>
       </c>
       <c r="B153" t="n">
-        <v>92669</v>
+        <v>92658</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18877,26 +18877,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>563741</v>
+        <v>563749</v>
       </c>
       <c r="R153" t="n">
-        <v>6626930</v>
+        <v>6626916</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -18980,10 +18980,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128046033</v>
+        <v>128046041</v>
       </c>
       <c r="B154" t="n">
-        <v>92657</v>
+        <v>92670</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18991,26 +18991,26 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -19026,10 +19026,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563749</v>
+        <v>563741</v>
       </c>
       <c r="R154" t="n">
-        <v>6626916</v>
+        <v>6626930</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -19097,7 +19097,7 @@
         <v>128074263</v>
       </c>
       <c r="B155" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>128084971</v>
       </c>
       <c r="B156" t="n">
-        <v>92673</v>
+        <v>92674</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Tom Sävström, Kalle Källebrink, Staffan Öström</t>
+          <t>Staffan Öström, Tom Sävström, Kalle Källebrink</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -19318,7 +19318,7 @@
         <v>128085081</v>
       </c>
       <c r="B157" t="n">
-        <v>91576</v>
+        <v>91577</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Tom Sävström, Kalle Källebrink, Staffan Öström</t>
+          <t>Staffan Öström, Tom Sävström, Kalle Källebrink</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -19429,7 +19429,7 @@
         <v>128084970</v>
       </c>
       <c r="B158" t="n">
-        <v>92675</v>
+        <v>92676</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -19308,7 +19308,7 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Staffan Öström, Tom Sävström, Kalle Källebrink</t>
+          <t>Tom Sävström, Kalle Källebrink, Staffan Öström</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Staffan Öström, Tom Sävström, Kalle Källebrink</t>
+          <t>Tom Sävström, Kalle Källebrink, Staffan Öström</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY160"/>
+  <dimension ref="A1:AY164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19779,6 +19779,464 @@
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>128361382</v>
+      </c>
+      <c r="B161" t="n">
+        <v>92679</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>563579</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6626842</v>
+      </c>
+      <c r="S161" t="n">
+        <v>10</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>128361233</v>
+      </c>
+      <c r="B162" t="n">
+        <v>92637</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>563734</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6626757</v>
+      </c>
+      <c r="S162" t="n">
+        <v>10</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>1 mycel.</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>128361310</v>
+      </c>
+      <c r="B163" t="n">
+        <v>92677</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Phellodon violascens</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>563727</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6626778</v>
+      </c>
+      <c r="S163" t="n">
+        <v>10</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Ingen gran i direkt närhet.</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>Tallskog, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>128361338</v>
+      </c>
+      <c r="B164" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>563727</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6626778</v>
+      </c>
+      <c r="S164" t="n">
+        <v>10</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF164" t="inlineStr"/>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -17047,7 +17047,7 @@
         <v>127689891</v>
       </c>
       <c r="B137" t="n">
-        <v>92638</v>
+        <v>92646</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>127689849</v>
       </c>
       <c r="B138" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>128046156</v>
       </c>
       <c r="B139" t="n">
-        <v>90736</v>
+        <v>90742</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>128046074</v>
       </c>
       <c r="B140" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>128046023</v>
       </c>
       <c r="B141" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>128046036</v>
       </c>
       <c r="B142" t="n">
-        <v>92658</v>
+        <v>92666</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>128046194</v>
       </c>
       <c r="B143" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>128046174</v>
       </c>
       <c r="B144" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>128046080</v>
       </c>
       <c r="B145" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>128046037</v>
       </c>
       <c r="B146" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>128046076</v>
       </c>
       <c r="B147" t="n">
-        <v>90848</v>
+        <v>90854</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>128046078</v>
       </c>
       <c r="B148" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>128046184</v>
       </c>
       <c r="B149" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18524,37 +18524,37 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128046002</v>
+        <v>128046021</v>
       </c>
       <c r="B150" t="n">
-        <v>92658</v>
+        <v>92650</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -18570,10 +18570,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>563749</v>
+        <v>563750</v>
       </c>
       <c r="R150" t="n">
-        <v>6626807</v>
+        <v>6626840</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -18638,37 +18638,37 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128046021</v>
+        <v>128046002</v>
       </c>
       <c r="B151" t="n">
-        <v>92642</v>
+        <v>92666</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -18684,10 +18684,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>563750</v>
+        <v>563749</v>
       </c>
       <c r="R151" t="n">
-        <v>6626840</v>
+        <v>6626807</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18755,7 +18755,7 @@
         <v>128046123</v>
       </c>
       <c r="B152" t="n">
-        <v>92644</v>
+        <v>92652</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>128046033</v>
       </c>
       <c r="B153" t="n">
-        <v>92658</v>
+        <v>92666</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>128046041</v>
       </c>
       <c r="B154" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>128074263</v>
       </c>
       <c r="B155" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>128084971</v>
       </c>
       <c r="B156" t="n">
-        <v>92674</v>
+        <v>92682</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>128085081</v>
       </c>
       <c r="B157" t="n">
-        <v>91577</v>
+        <v>91585</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>128084970</v>
       </c>
       <c r="B158" t="n">
-        <v>92676</v>
+        <v>92684</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>128268019</v>
       </c>
       <c r="B159" t="n">
-        <v>92644</v>
+        <v>92652</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Kalle Källebrink</t>
+          <t>Kalle Källebrink, Annelie Öster Friberg</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -19784,7 +19784,7 @@
         <v>128361382</v>
       </c>
       <c r="B161" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>128361233</v>
       </c>
       <c r="B162" t="n">
-        <v>92637</v>
+        <v>92642</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>128361310</v>
       </c>
       <c r="B163" t="n">
-        <v>92677</v>
+        <v>92682</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>128361338</v>
       </c>
       <c r="B164" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -18752,10 +18752,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128046123</v>
+        <v>128046041</v>
       </c>
       <c r="B152" t="n">
-        <v>92652</v>
+        <v>92678</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18763,26 +18763,26 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>788</v>
+        <v>5449</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>564163</v>
+        <v>563741</v>
       </c>
       <c r="R152" t="n">
-        <v>6626836</v>
+        <v>6626930</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18848,7 +18848,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>Blandskog. fuktigt</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -18866,10 +18866,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128046033</v>
+        <v>128046123</v>
       </c>
       <c r="B153" t="n">
-        <v>92666</v>
+        <v>92652</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18877,26 +18877,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2059</v>
+        <v>788</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>563749</v>
+        <v>564163</v>
       </c>
       <c r="R153" t="n">
-        <v>6626916</v>
+        <v>6626836</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Blandskog. fuktigt</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -18980,10 +18980,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128046041</v>
+        <v>128046033</v>
       </c>
       <c r="B154" t="n">
-        <v>92678</v>
+        <v>92666</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18991,26 +18991,26 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -19026,10 +19026,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563741</v>
+        <v>563749</v>
       </c>
       <c r="R154" t="n">
-        <v>6626930</v>
+        <v>6626916</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -17276,7 +17276,7 @@
         <v>128046156</v>
       </c>
       <c r="B139" t="n">
-        <v>90742</v>
+        <v>90834</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>128046074</v>
       </c>
       <c r="B140" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>128046023</v>
       </c>
       <c r="B141" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>128046036</v>
       </c>
       <c r="B142" t="n">
-        <v>92666</v>
+        <v>92758</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>128046194</v>
       </c>
       <c r="B143" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>128046174</v>
       </c>
       <c r="B144" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>128046080</v>
       </c>
       <c r="B145" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>128046037</v>
       </c>
       <c r="B146" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>128046076</v>
       </c>
       <c r="B147" t="n">
-        <v>90854</v>
+        <v>90946</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>128046078</v>
       </c>
       <c r="B148" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>128046184</v>
       </c>
       <c r="B149" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18524,37 +18524,37 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128046021</v>
+        <v>128046002</v>
       </c>
       <c r="B150" t="n">
-        <v>92650</v>
+        <v>92758</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -18570,10 +18570,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>563750</v>
+        <v>563749</v>
       </c>
       <c r="R150" t="n">
-        <v>6626840</v>
+        <v>6626807</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -18638,37 +18638,37 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128046002</v>
+        <v>128046021</v>
       </c>
       <c r="B151" t="n">
-        <v>92666</v>
+        <v>92742</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -18684,10 +18684,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>563749</v>
+        <v>563750</v>
       </c>
       <c r="R151" t="n">
-        <v>6626807</v>
+        <v>6626840</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18752,10 +18752,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128046041</v>
+        <v>128046123</v>
       </c>
       <c r="B152" t="n">
-        <v>92678</v>
+        <v>92744</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18763,26 +18763,26 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5449</v>
+        <v>788</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>563741</v>
+        <v>564163</v>
       </c>
       <c r="R152" t="n">
-        <v>6626930</v>
+        <v>6626836</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18848,7 +18848,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Blandskog. fuktigt</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -18866,10 +18866,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128046123</v>
+        <v>128046033</v>
       </c>
       <c r="B153" t="n">
-        <v>92652</v>
+        <v>92758</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18877,26 +18877,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>788</v>
+        <v>2059</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>564163</v>
+        <v>563749</v>
       </c>
       <c r="R153" t="n">
-        <v>6626836</v>
+        <v>6626916</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Blandskog. fuktigt</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -18980,10 +18980,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128046033</v>
+        <v>128046041</v>
       </c>
       <c r="B154" t="n">
-        <v>92666</v>
+        <v>92770</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18991,26 +18991,26 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -19026,10 +19026,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563749</v>
+        <v>563741</v>
       </c>
       <c r="R154" t="n">
-        <v>6626916</v>
+        <v>6626930</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -19097,7 +19097,7 @@
         <v>128074263</v>
       </c>
       <c r="B155" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>128084971</v>
       </c>
       <c r="B156" t="n">
-        <v>92682</v>
+        <v>92774</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>128085081</v>
       </c>
       <c r="B157" t="n">
-        <v>91585</v>
+        <v>91677</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>128084970</v>
       </c>
       <c r="B158" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>128268019</v>
       </c>
       <c r="B159" t="n">
-        <v>92652</v>
+        <v>92744</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>128073806</v>
       </c>
       <c r="B160" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>128361382</v>
       </c>
       <c r="B161" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>128361233</v>
       </c>
       <c r="B162" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>128361310</v>
       </c>
       <c r="B163" t="n">
-        <v>92682</v>
+        <v>92774</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>128361338</v>
       </c>
       <c r="B164" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -18752,10 +18752,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128046123</v>
+        <v>128046041</v>
       </c>
       <c r="B152" t="n">
-        <v>92744</v>
+        <v>92770</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18763,26 +18763,26 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>788</v>
+        <v>5449</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>564163</v>
+        <v>563741</v>
       </c>
       <c r="R152" t="n">
-        <v>6626836</v>
+        <v>6626930</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18848,7 +18848,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>Blandskog. fuktigt</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -18866,10 +18866,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128046033</v>
+        <v>128046123</v>
       </c>
       <c r="B153" t="n">
-        <v>92758</v>
+        <v>92744</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18877,26 +18877,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2059</v>
+        <v>788</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>563749</v>
+        <v>564163</v>
       </c>
       <c r="R153" t="n">
-        <v>6626916</v>
+        <v>6626836</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Blandskog. fuktigt</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -18980,10 +18980,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128046041</v>
+        <v>128046033</v>
       </c>
       <c r="B154" t="n">
-        <v>92770</v>
+        <v>92758</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18991,26 +18991,26 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -19026,10 +19026,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563741</v>
+        <v>563749</v>
       </c>
       <c r="R154" t="n">
-        <v>6626930</v>
+        <v>6626916</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -17276,7 +17276,7 @@
         <v>128046156</v>
       </c>
       <c r="B139" t="n">
-        <v>90834</v>
+        <v>90846</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>128046074</v>
       </c>
       <c r="B140" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>128046023</v>
       </c>
       <c r="B141" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>128046036</v>
       </c>
       <c r="B142" t="n">
-        <v>92758</v>
+        <v>92770</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>128046194</v>
       </c>
       <c r="B143" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>128046174</v>
       </c>
       <c r="B144" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>128046080</v>
       </c>
       <c r="B145" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>128046037</v>
       </c>
       <c r="B146" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>128046076</v>
       </c>
       <c r="B147" t="n">
-        <v>90946</v>
+        <v>90958</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>128046078</v>
       </c>
       <c r="B148" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>128046184</v>
       </c>
       <c r="B149" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>128046002</v>
       </c>
       <c r="B150" t="n">
-        <v>92758</v>
+        <v>92770</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>128046021</v>
       </c>
       <c r="B151" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>128046041</v>
       </c>
       <c r="B152" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>128046123</v>
       </c>
       <c r="B153" t="n">
-        <v>92744</v>
+        <v>92756</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>128046033</v>
       </c>
       <c r="B154" t="n">
-        <v>92758</v>
+        <v>92770</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>128074263</v>
       </c>
       <c r="B155" t="n">
-        <v>98488</v>
+        <v>98502</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>128084971</v>
       </c>
       <c r="B156" t="n">
-        <v>92774</v>
+        <v>92786</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>128085081</v>
       </c>
       <c r="B157" t="n">
-        <v>91677</v>
+        <v>91689</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>128084970</v>
       </c>
       <c r="B158" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>128268019</v>
       </c>
       <c r="B159" t="n">
-        <v>92744</v>
+        <v>92756</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>128073806</v>
       </c>
       <c r="B160" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>128361382</v>
       </c>
       <c r="B161" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>128361233</v>
       </c>
       <c r="B162" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>128361310</v>
       </c>
       <c r="B163" t="n">
-        <v>92774</v>
+        <v>92786</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>128361338</v>
       </c>
       <c r="B164" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -19543,7 +19543,7 @@
         <v>128268019</v>
       </c>
       <c r="B159" t="n">
-        <v>92756</v>
+        <v>92758</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>128361382</v>
       </c>
       <c r="B161" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>128361233</v>
       </c>
       <c r="B162" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>128361310</v>
       </c>
       <c r="B163" t="n">
-        <v>92786</v>
+        <v>92788</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>128361338</v>
       </c>
       <c r="B164" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -19097,7 +19097,7 @@
         <v>128074263</v>
       </c>
       <c r="B155" t="n">
-        <v>98502</v>
+        <v>98508</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>128084971</v>
       </c>
       <c r="B156" t="n">
-        <v>92786</v>
+        <v>92788</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>128085081</v>
       </c>
       <c r="B157" t="n">
-        <v>91689</v>
+        <v>91691</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>128084970</v>
       </c>
       <c r="B158" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY164"/>
+  <dimension ref="A1:AY172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20237,6 +20237,875 @@
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>128787685</v>
+      </c>
+      <c r="B165" t="n">
+        <v>91691</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Gropticka</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>563863</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6626713</v>
+      </c>
+      <c r="S165" t="n">
+        <v>10</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Grov granlåga</t>
+        </is>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Lars Bsenko</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>128787519</v>
+      </c>
+      <c r="B166" t="n">
+        <v>92373</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>563968</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6626883</v>
+      </c>
+      <c r="S166" t="n">
+        <v>10</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Lars Bsenko</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>128787432</v>
+      </c>
+      <c r="B167" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>563765</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6626852</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF167" t="inlineStr"/>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Lars Bsenko</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>128787606</v>
+      </c>
+      <c r="B168" t="n">
+        <v>91239</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>564101</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6626838</v>
+      </c>
+      <c r="S168" t="n">
+        <v>10</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF168" t="inlineStr"/>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>Fuktig barrblandskog, lövinslag</t>
+        </is>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Lars Bsenko</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>128787422</v>
+      </c>
+      <c r="B169" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>563776</v>
+      </c>
+      <c r="R169" t="n">
+        <v>6626824</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Lars Bsenko</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>128787448</v>
+      </c>
+      <c r="B170" t="n">
+        <v>92772</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>563748</v>
+      </c>
+      <c r="R170" t="n">
+        <v>6626865</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Lars Bsenko</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>128787660</v>
+      </c>
+      <c r="B171" t="n">
+        <v>92782</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>564165</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6626760</v>
+      </c>
+      <c r="S171" t="n">
+        <v>10</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF171" t="inlineStr"/>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Lars Bsenko</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>128787454</v>
+      </c>
+      <c r="B172" t="n">
+        <v>92756</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>563748</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6626865</v>
+      </c>
+      <c r="S172" t="n">
+        <v>10</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF172" t="inlineStr"/>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Lars Bsenko</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -19543,7 +19543,7 @@
         <v>128268019</v>
       </c>
       <c r="B159" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>128361382</v>
       </c>
       <c r="B161" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>128361233</v>
       </c>
       <c r="B162" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>128361310</v>
       </c>
       <c r="B163" t="n">
-        <v>92788</v>
+        <v>92789</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>128361338</v>
       </c>
       <c r="B164" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>128787685</v>
       </c>
       <c r="B165" t="n">
-        <v>91691</v>
+        <v>91692</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>128787519</v>
       </c>
       <c r="B166" t="n">
-        <v>92373</v>
+        <v>92374</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>128787432</v>
       </c>
       <c r="B167" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20570,36 +20570,44 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128787606</v>
+        <v>128787422</v>
       </c>
       <c r="B168" t="n">
-        <v>91239</v>
+        <v>92793</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3215</v>
+        <v>5966</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
@@ -20608,10 +20616,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>564101</v>
+        <v>563776</v>
       </c>
       <c r="R168" t="n">
-        <v>6626838</v>
+        <v>6626824</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20658,7 +20666,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Fuktig barrblandskog, lövinslag</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -20676,44 +20684,36 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128787422</v>
+        <v>128787606</v>
       </c>
       <c r="B169" t="n">
-        <v>92792</v>
+        <v>91240</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5966</v>
+        <v>3215</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
@@ -20722,10 +20722,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563776</v>
+        <v>564101</v>
       </c>
       <c r="R169" t="n">
-        <v>6626824</v>
+        <v>6626838</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20772,7 +20772,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Fuktig barrblandskog, lövinslag</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -20793,7 +20793,7 @@
         <v>128787448</v>
       </c>
       <c r="B170" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>128787660</v>
       </c>
       <c r="B171" t="n">
-        <v>92782</v>
+        <v>92783</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>128787454</v>
       </c>
       <c r="B172" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -20242,7 +20242,7 @@
         <v>128787685</v>
       </c>
       <c r="B165" t="n">
-        <v>91692</v>
+        <v>91719</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>128787519</v>
       </c>
       <c r="B166" t="n">
-        <v>92374</v>
+        <v>92401</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Tom Sävström, Lars Bsenko</t>
+          <t>Lars Bsenko, Tom Sävström</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
@@ -20459,7 +20459,7 @@
         <v>128787432</v>
       </c>
       <c r="B167" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20570,44 +20570,36 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128787422</v>
+        <v>128787606</v>
       </c>
       <c r="B168" t="n">
-        <v>92793</v>
+        <v>91267</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5966</v>
+        <v>3215</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
@@ -20616,10 +20608,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>563776</v>
+        <v>564101</v>
       </c>
       <c r="R168" t="n">
-        <v>6626824</v>
+        <v>6626838</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20666,7 +20658,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Fuktig barrblandskog, lövinslag</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -20684,36 +20676,44 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128787606</v>
+        <v>128787422</v>
       </c>
       <c r="B169" t="n">
-        <v>91240</v>
+        <v>92820</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3215</v>
+        <v>5966</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
@@ -20722,10 +20722,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>564101</v>
+        <v>563776</v>
       </c>
       <c r="R169" t="n">
-        <v>6626838</v>
+        <v>6626824</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20772,7 +20772,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Fuktig barrblandskog, lövinslag</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -20793,7 +20793,7 @@
         <v>128787448</v>
       </c>
       <c r="B170" t="n">
-        <v>92773</v>
+        <v>92800</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Tom Sävström, Lars Bsenko</t>
+          <t>Lars Bsenko, Tom Sävström</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -20899,7 +20899,7 @@
         <v>128787660</v>
       </c>
       <c r="B171" t="n">
-        <v>92783</v>
+        <v>92810</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>128787454</v>
       </c>
       <c r="B172" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Tom Sävström, Lars Bsenko</t>
+          <t>Lars Bsenko, Tom Sävström</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -19543,7 +19543,7 @@
         <v>128268019</v>
       </c>
       <c r="B159" t="n">
-        <v>92759</v>
+        <v>92786</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>128073806</v>
       </c>
       <c r="B160" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>128361382</v>
       </c>
       <c r="B161" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>128361233</v>
       </c>
       <c r="B162" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>128361310</v>
       </c>
       <c r="B163" t="n">
-        <v>92789</v>
+        <v>92816</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>128361338</v>
       </c>
       <c r="B164" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Lars Bsenko, Tom Sävström</t>
+          <t>Tom Sävström, Lars Bsenko</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Lars Bsenko, Tom Sävström</t>
+          <t>Tom Sävström, Lars Bsenko</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -21101,7 +21101,7 @@
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Lars Bsenko, Tom Sävström</t>
+          <t>Tom Sävström, Lars Bsenko</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -20242,7 +20242,7 @@
         <v>128787685</v>
       </c>
       <c r="B165" t="n">
-        <v>91719</v>
+        <v>91724</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>128787519</v>
       </c>
       <c r="B166" t="n">
-        <v>92401</v>
+        <v>92406</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>128787432</v>
       </c>
       <c r="B167" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>128787606</v>
       </c>
       <c r="B168" t="n">
-        <v>91267</v>
+        <v>91272</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>128787422</v>
       </c>
       <c r="B169" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>128787448</v>
       </c>
       <c r="B170" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>128787660</v>
       </c>
       <c r="B171" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>128787454</v>
       </c>
       <c r="B172" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -20570,44 +20570,36 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128787422</v>
+        <v>128787606</v>
       </c>
       <c r="B168" t="n">
-        <v>92849</v>
+        <v>91293</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5966</v>
+        <v>3215</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
@@ -20616,10 +20608,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>563776</v>
+        <v>564101</v>
       </c>
       <c r="R168" t="n">
-        <v>6626824</v>
+        <v>6626838</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20666,7 +20658,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Fuktig barrblandskog, lövinslag</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -20684,36 +20676,44 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128787606</v>
+        <v>128787422</v>
       </c>
       <c r="B169" t="n">
-        <v>91293</v>
+        <v>92849</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3215</v>
+        <v>5966</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
@@ -20722,10 +20722,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>564101</v>
+        <v>563776</v>
       </c>
       <c r="R169" t="n">
-        <v>6626838</v>
+        <v>6626824</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20772,7 +20772,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Fuktig barrblandskog, lövinslag</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -20242,7 +20242,7 @@
         <v>128787685</v>
       </c>
       <c r="B165" t="n">
-        <v>91745</v>
+        <v>91748</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>128787519</v>
       </c>
       <c r="B166" t="n">
-        <v>92428</v>
+        <v>92433</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>128787432</v>
       </c>
       <c r="B167" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>128787606</v>
       </c>
       <c r="B168" t="n">
-        <v>91293</v>
+        <v>91296</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>128787422</v>
       </c>
       <c r="B169" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>128787448</v>
       </c>
       <c r="B170" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>128787660</v>
       </c>
       <c r="B171" t="n">
-        <v>92837</v>
+        <v>92842</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>128787454</v>
       </c>
       <c r="B172" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY172"/>
+  <dimension ref="A1:AY173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20242,7 +20242,7 @@
         <v>128787685</v>
       </c>
       <c r="B165" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>128787519</v>
       </c>
       <c r="B166" t="n">
-        <v>92433</v>
+        <v>92436</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>128787432</v>
       </c>
       <c r="B167" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>128787606</v>
       </c>
       <c r="B168" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>128787422</v>
       </c>
       <c r="B169" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>128787448</v>
       </c>
       <c r="B170" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>128787660</v>
       </c>
       <c r="B171" t="n">
-        <v>92842</v>
+        <v>92845</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>128787454</v>
       </c>
       <c r="B172" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -21106,6 +21106,122 @@
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>129182686</v>
+      </c>
+      <c r="B173" t="n">
+        <v>92857</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Naddtorpsskogen, Naddtorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>563877</v>
+      </c>
+      <c r="R173" t="n">
+        <v>6626930</v>
+      </c>
+      <c r="S173" t="n">
+        <v>5</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -20350,10 +20350,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128787519</v>
+        <v>128787432</v>
       </c>
       <c r="B166" t="n">
-        <v>92436</v>
+        <v>92857</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20361,25 +20361,33 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
@@ -20388,10 +20396,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>563968</v>
+        <v>563765</v>
       </c>
       <c r="R166" t="n">
-        <v>6626883</v>
+        <v>6626852</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -20456,10 +20464,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128787432</v>
+        <v>128787519</v>
       </c>
       <c r="B167" t="n">
-        <v>92857</v>
+        <v>92436</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20467,33 +20475,25 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
@@ -20502,10 +20502,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>563765</v>
+        <v>563968</v>
       </c>
       <c r="R167" t="n">
-        <v>6626852</v>
+        <v>6626883</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -20242,7 +20242,7 @@
         <v>128787685</v>
       </c>
       <c r="B165" t="n">
-        <v>91751</v>
+        <v>91758</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20350,10 +20350,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128787432</v>
+        <v>128787519</v>
       </c>
       <c r="B166" t="n">
-        <v>92857</v>
+        <v>92443</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20361,33 +20361,25 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
@@ -20396,10 +20388,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>563765</v>
+        <v>563968</v>
       </c>
       <c r="R166" t="n">
-        <v>6626852</v>
+        <v>6626883</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -20464,10 +20456,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128787519</v>
+        <v>128787432</v>
       </c>
       <c r="B167" t="n">
-        <v>92436</v>
+        <v>92864</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20475,25 +20467,33 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
@@ -20502,10 +20502,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>563968</v>
+        <v>563765</v>
       </c>
       <c r="R167" t="n">
-        <v>6626883</v>
+        <v>6626852</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20573,7 +20573,7 @@
         <v>128787606</v>
       </c>
       <c r="B168" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>128787422</v>
       </c>
       <c r="B169" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>128787448</v>
       </c>
       <c r="B170" t="n">
-        <v>92835</v>
+        <v>92842</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>128787660</v>
       </c>
       <c r="B171" t="n">
-        <v>92845</v>
+        <v>92852</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>128787454</v>
       </c>
       <c r="B172" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>129182686</v>
       </c>
       <c r="B173" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -20242,7 +20242,7 @@
         <v>128787685</v>
       </c>
       <c r="B165" t="n">
-        <v>91758</v>
+        <v>91765</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20350,10 +20350,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128787519</v>
+        <v>128787432</v>
       </c>
       <c r="B166" t="n">
-        <v>92443</v>
+        <v>92871</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20361,25 +20361,33 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
@@ -20388,10 +20396,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>563968</v>
+        <v>563765</v>
       </c>
       <c r="R166" t="n">
-        <v>6626883</v>
+        <v>6626852</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -20456,10 +20464,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128787432</v>
+        <v>128787519</v>
       </c>
       <c r="B167" t="n">
-        <v>92864</v>
+        <v>92450</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20467,33 +20475,25 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
@@ -20502,10 +20502,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>563765</v>
+        <v>563968</v>
       </c>
       <c r="R167" t="n">
-        <v>6626852</v>
+        <v>6626883</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20570,36 +20570,44 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128787606</v>
+        <v>128787422</v>
       </c>
       <c r="B168" t="n">
-        <v>91305</v>
+        <v>92871</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3215</v>
+        <v>5966</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
@@ -20608,10 +20616,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>564101</v>
+        <v>563776</v>
       </c>
       <c r="R168" t="n">
-        <v>6626838</v>
+        <v>6626824</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20658,7 +20666,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Fuktig barrblandskog, lövinslag</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -20676,44 +20684,36 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128787422</v>
+        <v>128787606</v>
       </c>
       <c r="B169" t="n">
-        <v>92864</v>
+        <v>91312</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5966</v>
+        <v>3215</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
@@ -20722,10 +20722,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563776</v>
+        <v>564101</v>
       </c>
       <c r="R169" t="n">
-        <v>6626824</v>
+        <v>6626838</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20772,7 +20772,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Fuktig barrblandskog, lövinslag</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -20793,7 +20793,7 @@
         <v>128787448</v>
       </c>
       <c r="B170" t="n">
-        <v>92842</v>
+        <v>92849</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>128787660</v>
       </c>
       <c r="B171" t="n">
-        <v>92852</v>
+        <v>92859</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>128787454</v>
       </c>
       <c r="B172" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>129182686</v>
       </c>
       <c r="B173" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -20242,7 +20242,7 @@
         <v>128787685</v>
       </c>
       <c r="B165" t="n">
-        <v>91765</v>
+        <v>91767</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>128787432</v>
       </c>
       <c r="B166" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>128787519</v>
       </c>
       <c r="B167" t="n">
-        <v>92450</v>
+        <v>92452</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>128787422</v>
       </c>
       <c r="B168" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>128787606</v>
       </c>
       <c r="B169" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>128787448</v>
       </c>
       <c r="B170" t="n">
-        <v>92849</v>
+        <v>92851</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>128787660</v>
       </c>
       <c r="B171" t="n">
-        <v>92859</v>
+        <v>92861</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>128787454</v>
       </c>
       <c r="B172" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>129182686</v>
       </c>
       <c r="B173" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -20570,44 +20570,36 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128787422</v>
+        <v>128787606</v>
       </c>
       <c r="B168" t="n">
-        <v>92873</v>
+        <v>91314</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5966</v>
+        <v>3215</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
@@ -20616,10 +20608,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>563776</v>
+        <v>564101</v>
       </c>
       <c r="R168" t="n">
-        <v>6626824</v>
+        <v>6626838</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20666,7 +20658,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Fuktig barrblandskog, lövinslag</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -20684,36 +20676,44 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128787606</v>
+        <v>128787422</v>
       </c>
       <c r="B169" t="n">
-        <v>91314</v>
+        <v>92873</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3215</v>
+        <v>5966</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
@@ -20722,10 +20722,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>564101</v>
+        <v>563776</v>
       </c>
       <c r="R169" t="n">
-        <v>6626838</v>
+        <v>6626824</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20772,7 +20772,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Fuktig barrblandskog, lövinslag</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -20350,10 +20350,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128787432</v>
+        <v>128787519</v>
       </c>
       <c r="B166" t="n">
-        <v>92873</v>
+        <v>92452</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20361,33 +20361,25 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
@@ -20396,10 +20388,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>563765</v>
+        <v>563968</v>
       </c>
       <c r="R166" t="n">
-        <v>6626852</v>
+        <v>6626883</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -20464,10 +20456,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128787519</v>
+        <v>128787432</v>
       </c>
       <c r="B167" t="n">
-        <v>92452</v>
+        <v>92873</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20475,25 +20467,33 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
@@ -20502,10 +20502,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>563968</v>
+        <v>563765</v>
       </c>
       <c r="R167" t="n">
-        <v>6626883</v>
+        <v>6626852</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -20242,7 +20242,7 @@
         <v>128787685</v>
       </c>
       <c r="B165" t="n">
-        <v>91767</v>
+        <v>91776</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>128787519</v>
       </c>
       <c r="B166" t="n">
-        <v>92452</v>
+        <v>92466</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>128787432</v>
       </c>
       <c r="B167" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>128787606</v>
       </c>
       <c r="B168" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>128787422</v>
       </c>
       <c r="B169" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>128787448</v>
       </c>
       <c r="B170" t="n">
-        <v>92851</v>
+        <v>92837</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>128787660</v>
       </c>
       <c r="B171" t="n">
-        <v>92861</v>
+        <v>92847</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>128787454</v>
       </c>
       <c r="B172" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>129182686</v>
       </c>
       <c r="B173" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -21111,7 +21111,7 @@
         <v>129182686</v>
       </c>
       <c r="B173" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -21111,7 +21111,7 @@
         <v>129182686</v>
       </c>
       <c r="B173" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -21111,7 +21111,7 @@
         <v>129182686</v>
       </c>
       <c r="B173" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -21111,7 +21111,7 @@
         <v>129182686</v>
       </c>
       <c r="B173" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -21111,7 +21111,7 @@
         <v>129182686</v>
       </c>
       <c r="B173" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -21111,7 +21111,7 @@
         <v>129182686</v>
       </c>
       <c r="B173" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -21111,7 +21111,7 @@
         <v>129182686</v>
       </c>
       <c r="B173" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -15419,7 +15419,7 @@
         <v>126858024</v>
       </c>
       <c r="B123" t="n">
-        <v>92654</v>
+        <v>92643</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>126857966</v>
       </c>
       <c r="B124" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>126857867</v>
       </c>
       <c r="B125" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>126857945</v>
       </c>
       <c r="B126" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>126857691</v>
       </c>
       <c r="B127" t="n">
-        <v>92612</v>
+        <v>92601</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>126882807</v>
       </c>
       <c r="B128" t="n">
-        <v>91332</v>
+        <v>91319</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>126882851</v>
       </c>
       <c r="B129" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>126882773</v>
       </c>
       <c r="B130" t="n">
-        <v>56590</v>
+        <v>56584</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>126882801</v>
       </c>
       <c r="B131" t="n">
-        <v>91628</v>
+        <v>91615</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>126882697</v>
       </c>
       <c r="B132" t="n">
-        <v>92614</v>
+        <v>92601</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>127063880</v>
       </c>
       <c r="B133" t="n">
-        <v>92631</v>
+        <v>92609</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>127063850</v>
       </c>
       <c r="B134" t="n">
-        <v>92631</v>
+        <v>92609</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>127063878</v>
       </c>
       <c r="B135" t="n">
-        <v>92631</v>
+        <v>92609</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>127063858</v>
       </c>
       <c r="B136" t="n">
-        <v>92631</v>
+        <v>92609</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY211"/>
+  <dimension ref="A1:AY233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14106,48 +14106,56 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2595020</v>
+        <v>134585918</v>
       </c>
       <c r="B122" t="n">
-        <v>110078</v>
+        <v>99230</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220299</v>
+        <v>219874</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Sothällen SV (linja), Vstm</t>
+          <t>Sothälls linjegata, Vstm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>564244</v>
+        <v>564164</v>
       </c>
       <c r="R122" t="n">
-        <v>6626786</v>
+        <v>6626900</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14171,12 +14179,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2011-06-08</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2011-06-08</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14185,12 +14193,13 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Linjegata, örtrik, enbuskar, lövsly, omgiven av barrblandskog.</t>
+          <t>Fuktstråk i linjegata</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14208,56 +14217,56 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>103555316</v>
+        <v>134585976</v>
       </c>
       <c r="B123" t="n">
-        <v>110078</v>
+        <v>99230</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220299</v>
+        <v>219874</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Sothälls linjegata, Vstm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>564082</v>
+        <v>564185</v>
       </c>
       <c r="R123" t="n">
-        <v>6626716</v>
+        <v>6626887</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14281,12 +14290,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14301,7 +14310,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Gräsmark i linjegata</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -14319,27 +14328,27 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118724975</v>
+        <v>134585710</v>
       </c>
       <c r="B124" t="n">
-        <v>106813</v>
+        <v>111153</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220785</v>
+        <v>220240</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -14348,27 +14357,27 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothälls linjegata, Vstm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>564182</v>
+        <v>564131</v>
       </c>
       <c r="R124" t="n">
-        <v>6626791</v>
+        <v>6626911</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14392,12 +14401,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14412,7 +14421,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>Fuktig blandskog</t>
+          <t>Linjegata med gräs- och hällmark</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14430,27 +14439,27 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122485587</v>
+        <v>2595020</v>
       </c>
       <c r="B125" t="n">
-        <v>106813</v>
+        <v>110078</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -14461,17 +14470,17 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Väst Sothällen, Vstm</t>
+          <t>Sothällen SV (linja), Vstm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>564206</v>
+        <v>564244</v>
       </c>
       <c r="R125" t="n">
-        <v>6626790</v>
+        <v>6626786</v>
       </c>
       <c r="S125" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14495,17 +14504,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2011-06-08</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>småträd</t>
+          <t>2011-06-08</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14519,66 +14523,54 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>Fuktig blandskog, mindre dalsänka</t>
+          <t>Linjegata, örtrik, enbuskar, lövsly, omgiven av barrblandskog.</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>72976497</v>
+        <v>103555316</v>
       </c>
       <c r="B126" t="n">
-        <v>99118</v>
+        <v>110078</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>220299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -14588,17 +14580,17 @@
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>564097</v>
+        <v>564082</v>
       </c>
       <c r="R126" t="n">
-        <v>6626643</v>
+        <v>6626716</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14622,12 +14614,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2018-08-31</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2018-08-31</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14642,7 +14634,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>Äldre mossig barrblandskog, inslag av löv</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -14660,64 +14652,56 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>72976505</v>
+        <v>118724975</v>
       </c>
       <c r="B127" t="n">
-        <v>99118</v>
+        <v>106813</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>220785</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>564104</v>
+        <v>564182</v>
       </c>
       <c r="R127" t="n">
-        <v>6626654</v>
+        <v>6626791</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14741,12 +14725,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2018-08-31</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2018-08-31</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14761,7 +14745,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>Äldre mossig barrblandskog, inslag av löv</t>
+          <t>Fuktig blandskog</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -14779,64 +14763,48 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>72976664</v>
+        <v>122485587</v>
       </c>
       <c r="B128" t="n">
-        <v>99118</v>
+        <v>106813</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>220785</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Väst Sothällen, Vstm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>564075</v>
+        <v>564206</v>
       </c>
       <c r="R128" t="n">
-        <v>6626696</v>
+        <v>6626790</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14860,12 +14828,17 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2018-08-31</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2018-08-31</t>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>småträd</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14874,31 +14847,34 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>Äldre mossig barrblandskog, inslag av löv</t>
+          <t>Fuktig blandskog, mindre dalsänka</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>103555750</v>
+        <v>72976497</v>
       </c>
       <c r="B129" t="n">
         <v>99118</v>
@@ -14928,12 +14904,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -14945,17 +14921,17 @@
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>564061</v>
+        <v>564097</v>
       </c>
       <c r="R129" t="n">
-        <v>6626713</v>
+        <v>6626643</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14979,12 +14955,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2018-08-31</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2018-08-31</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14999,7 +14975,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Äldre mossig barrblandskog, inslag av löv</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -15017,7 +14993,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>103555783</v>
+        <v>72976505</v>
       </c>
       <c r="B130" t="n">
         <v>99118</v>
@@ -15047,12 +15023,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -15064,17 +15040,17 @@
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>564068</v>
+        <v>564104</v>
       </c>
       <c r="R130" t="n">
-        <v>6626734</v>
+        <v>6626654</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15098,12 +15074,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2018-08-31</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2018-08-31</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15118,7 +15094,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Äldre mossig barrblandskog, inslag av löv</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -15136,7 +15112,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>103591824</v>
+        <v>72976664</v>
       </c>
       <c r="B131" t="n">
         <v>99118</v>
@@ -15183,17 +15159,17 @@
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Grotten OSO, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>563487</v>
+        <v>564075</v>
       </c>
       <c r="R131" t="n">
-        <v>6626863</v>
+        <v>6626696</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15217,17 +15193,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2018-08-31</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>med grönpyrola.</t>
+          <t>2018-08-31</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15242,7 +15213,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog</t>
+          <t>Äldre mossig barrblandskog, inslag av löv</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15260,7 +15231,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>104689769</v>
+        <v>103555750</v>
       </c>
       <c r="B132" t="n">
         <v>99118</v>
@@ -15290,7 +15261,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -15303,16 +15274,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Grotten, SO (knärot4), Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>563486</v>
+        <v>564061</v>
       </c>
       <c r="R132" t="n">
-        <v>6626863</v>
+        <v>6626713</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15337,24 +15310,14 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>U-Sur-0510</t>
-        </is>
-      </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>med grönpyrola</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15363,18 +15326,19 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>äldre barrblandskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
@@ -15382,15 +15346,11 @@
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY132" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>111850130</v>
+        <v>103555783</v>
       </c>
       <c r="B133" t="n">
         <v>99118</v>
@@ -15420,12 +15380,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -15437,14 +15397,14 @@
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Grotten OSO, Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>563343</v>
+        <v>564068</v>
       </c>
       <c r="R133" t="n">
-        <v>6626818</v>
+        <v>6626734</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15471,17 +15431,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>inom ca 1 kvadratmeter.</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15496,7 +15451,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -15514,7 +15469,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>111875136</v>
+        <v>103591824</v>
       </c>
       <c r="B134" t="n">
         <v>99118</v>
@@ -15544,7 +15499,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15565,13 +15520,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>563524</v>
+        <v>563487</v>
       </c>
       <c r="R134" t="n">
-        <v>6626804</v>
+        <v>6626863</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15595,12 +15550,17 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>med grönpyrola.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15615,7 +15575,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Äldre barrblandskog</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15633,7 +15593,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>111875235</v>
+        <v>104689769</v>
       </c>
       <c r="B135" t="n">
         <v>99118</v>
@@ -15663,7 +15623,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15676,21 +15636,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Grotten OSO, Vstm</t>
+          <t>Grotten, SO (knärot4), Vstm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>563532</v>
+        <v>563486</v>
       </c>
       <c r="R135" t="n">
-        <v>6626798</v>
+        <v>6626863</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15712,14 +15670,24 @@
           <t>Ramnäs</t>
         </is>
       </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>U-Sur-0510</t>
+        </is>
+      </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>med grönpyrola</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15728,19 +15696,18 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>äldre barrblandskog</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
@@ -15748,11 +15715,15 @@
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY135" t="inlineStr"/>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>111875274</v>
+        <v>111850130</v>
       </c>
       <c r="B136" t="n">
         <v>99118</v>
@@ -15782,7 +15753,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15790,7 +15761,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
@@ -15799,13 +15774,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>563544</v>
+        <v>563343</v>
       </c>
       <c r="R136" t="n">
-        <v>6626788</v>
+        <v>6626818</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15829,12 +15804,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>inom ca 1 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15867,7 +15847,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>111875286</v>
+        <v>111875136</v>
       </c>
       <c r="B137" t="n">
         <v>99118</v>
@@ -15897,7 +15877,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15918,10 +15898,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>563550</v>
+        <v>563524</v>
       </c>
       <c r="R137" t="n">
-        <v>6626792</v>
+        <v>6626804</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15986,7 +15966,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>111875305</v>
+        <v>111875235</v>
       </c>
       <c r="B138" t="n">
         <v>99118</v>
@@ -16016,7 +15996,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -16037,10 +16017,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>563544</v>
+        <v>563532</v>
       </c>
       <c r="R138" t="n">
-        <v>6626796</v>
+        <v>6626798</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -16105,7 +16085,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>111875320</v>
+        <v>111875274</v>
       </c>
       <c r="B139" t="n">
         <v>99118</v>
@@ -16135,7 +16115,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -16143,11 +16123,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
@@ -16156,10 +16132,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>563555</v>
+        <v>563544</v>
       </c>
       <c r="R139" t="n">
-        <v>6626792</v>
+        <v>6626788</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -16224,7 +16200,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>111875333</v>
+        <v>111875286</v>
       </c>
       <c r="B140" t="n">
         <v>99118</v>
@@ -16254,7 +16230,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -16275,10 +16251,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>563570</v>
+        <v>563550</v>
       </c>
       <c r="R140" t="n">
-        <v>6626775</v>
+        <v>6626792</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -16343,7 +16319,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>111875358</v>
+        <v>111875305</v>
       </c>
       <c r="B141" t="n">
         <v>99118</v>
@@ -16373,7 +16349,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>95</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -16394,10 +16370,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>563561</v>
+        <v>563544</v>
       </c>
       <c r="R141" t="n">
-        <v>6626786</v>
+        <v>6626796</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16462,7 +16438,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>111875425</v>
+        <v>111875320</v>
       </c>
       <c r="B142" t="n">
         <v>99118</v>
@@ -16492,7 +16468,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16513,10 +16489,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>563568</v>
+        <v>563555</v>
       </c>
       <c r="R142" t="n">
-        <v>6626795</v>
+        <v>6626792</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16581,7 +16557,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>111875460</v>
+        <v>111875333</v>
       </c>
       <c r="B143" t="n">
         <v>99118</v>
@@ -16611,7 +16587,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -16632,10 +16608,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>563585</v>
+        <v>563570</v>
       </c>
       <c r="R143" t="n">
-        <v>6626810</v>
+        <v>6626775</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -16700,7 +16676,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>111875522</v>
+        <v>111875358</v>
       </c>
       <c r="B144" t="n">
         <v>99118</v>
@@ -16730,7 +16706,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -16751,10 +16727,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>563595</v>
+        <v>563561</v>
       </c>
       <c r="R144" t="n">
-        <v>6626842</v>
+        <v>6626786</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -16819,7 +16795,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>111899767</v>
+        <v>111875425</v>
       </c>
       <c r="B145" t="n">
         <v>99118</v>
@@ -16849,7 +16825,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -16866,17 +16842,17 @@
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Grotten OSO, Vstm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>563937</v>
+        <v>563568</v>
       </c>
       <c r="R145" t="n">
-        <v>6626698</v>
+        <v>6626795</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16900,12 +16876,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16920,7 +16896,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -16938,7 +16914,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>112081924</v>
+        <v>111875460</v>
       </c>
       <c r="B146" t="n">
         <v>99118</v>
@@ -16968,7 +16944,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -16989,13 +16965,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>563345</v>
+        <v>563585</v>
       </c>
       <c r="R146" t="n">
-        <v>6626815</v>
+        <v>6626810</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -17019,12 +16995,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17039,7 +17015,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog, inslag av björk, klibbal</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -17057,7 +17033,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>112141871</v>
+        <v>111875522</v>
       </c>
       <c r="B147" t="n">
         <v>99118</v>
@@ -17087,7 +17063,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -17108,13 +17084,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>563505</v>
+        <v>563595</v>
       </c>
       <c r="R147" t="n">
-        <v>6626902</v>
+        <v>6626842</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -17138,12 +17114,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17158,7 +17134,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>Gammal mossig barrblandskog</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -17176,7 +17152,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>112141910</v>
+        <v>111899767</v>
       </c>
       <c r="B148" t="n">
         <v>99118</v>
@@ -17206,7 +17182,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -17223,14 +17199,14 @@
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Grotten OSO, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>563510</v>
+        <v>563937</v>
       </c>
       <c r="R148" t="n">
-        <v>6626896</v>
+        <v>6626698</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17257,12 +17233,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17277,7 +17253,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>Gammal mossig barrblandskog</t>
+          <t>Äldre barrblandskog</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -17295,7 +17271,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>112977272</v>
+        <v>112081924</v>
       </c>
       <c r="B149" t="n">
         <v>99118</v>
@@ -17325,7 +17301,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -17342,14 +17318,14 @@
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Grotten OSO, Vstm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>564101</v>
+        <v>563345</v>
       </c>
       <c r="R149" t="n">
-        <v>6626677</v>
+        <v>6626815</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17376,12 +17352,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2023-10-28</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2023-10-28</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17396,7 +17372,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Gammal barrblandskog, inslag av björk, klibbal</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
@@ -17414,7 +17390,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118405005</v>
+        <v>112141871</v>
       </c>
       <c r="B150" t="n">
         <v>99118</v>
@@ -17442,25 +17418,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Grotten OSO, Vstm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>563342</v>
+        <v>563505</v>
       </c>
       <c r="R150" t="n">
-        <v>6626819</v>
+        <v>6626902</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17487,12 +17471,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17507,7 +17491,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Gammal mossig barrblandskog</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>
@@ -17525,7 +17509,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118703452</v>
+        <v>112141910</v>
       </c>
       <c r="B151" t="n">
         <v>99118</v>
@@ -17555,7 +17539,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -17565,7 +17549,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
@@ -17576,10 +17560,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>563797</v>
+        <v>563510</v>
       </c>
       <c r="R151" t="n">
-        <v>6626917</v>
+        <v>6626896</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17606,12 +17590,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17626,7 +17610,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog, blåbärsris</t>
+          <t>Gammal mossig barrblandskog</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -17644,7 +17628,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118725553</v>
+        <v>112977272</v>
       </c>
       <c r="B152" t="n">
         <v>99118</v>
@@ -17674,12 +17658,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -17695,10 +17679,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>564180</v>
+        <v>564101</v>
       </c>
       <c r="R152" t="n">
-        <v>6626838</v>
+        <v>6626677</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17725,12 +17709,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2023-10-28</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2023-10-28</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17745,7 +17729,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -17763,7 +17747,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118852324</v>
+        <v>118405005</v>
       </c>
       <c r="B153" t="n">
         <v>99118</v>
@@ -17791,19 +17775,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
@@ -17814,10 +17790,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>564081</v>
+        <v>563342</v>
       </c>
       <c r="R153" t="n">
-        <v>6626690</v>
+        <v>6626819</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17844,17 +17820,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>2 överblommade.</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17869,7 +17840,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -17887,7 +17858,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118852333</v>
+        <v>118703452</v>
       </c>
       <c r="B154" t="n">
         <v>99118</v>
@@ -17917,7 +17888,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -17927,21 +17898,21 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Grotten OSO, Vstm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>564104</v>
+        <v>563797</v>
       </c>
       <c r="R154" t="n">
-        <v>6626694</v>
+        <v>6626917</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17968,17 +17939,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>3 överblommade.</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17993,7 +17959,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Äldre barrblandskog, blåbärsris</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -18011,7 +17977,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119653166</v>
+        <v>118725553</v>
       </c>
       <c r="B155" t="n">
         <v>99118</v>
@@ -18041,12 +18007,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -18058,17 +18024,17 @@
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Grotten OSO, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>563655</v>
+        <v>564180</v>
       </c>
       <c r="R155" t="n">
-        <v>6626789</v>
+        <v>6626838</v>
       </c>
       <c r="S155" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18092,12 +18058,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18112,7 +18078,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Äldre barrblandskog</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr"/>
@@ -18130,7 +18096,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121229232</v>
+        <v>118852324</v>
       </c>
       <c r="B156" t="n">
         <v>99118</v>
@@ -18160,12 +18126,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -18177,17 +18143,17 @@
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Grotten, SO (knärot2), Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>563403</v>
+        <v>564081</v>
       </c>
       <c r="R156" t="n">
-        <v>6626849</v>
+        <v>6626690</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18209,24 +18175,19 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>U-Sur-0787</t>
-        </is>
-      </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>X(10) 1 m2, A::211/364 (10) 1 m2</t>
+          <t>2 överblommade.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18239,10 +18200,15 @@
       <c r="AG156" t="b">
         <v>0</v>
       </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
@@ -18250,15 +18216,11 @@
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY156" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121229337</v>
+        <v>118852333</v>
       </c>
       <c r="B157" t="n">
         <v>99118</v>
@@ -18288,10 +18250,14 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K157" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -18301,14 +18267,14 @@
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Grotten, SO (knärot3), Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>563455</v>
+        <v>564104</v>
       </c>
       <c r="R157" t="n">
-        <v>6626817</v>
+        <v>6626694</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18333,24 +18299,19 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>U-Sur-0786</t>
-        </is>
-      </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>8 stjälkar i blom</t>
+          <t>3 överblommade.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18365,13 +18326,13 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>gammal barrblandskog</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
@@ -18379,15 +18340,11 @@
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY157" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122485588</v>
+        <v>119653166</v>
       </c>
       <c r="B158" t="n">
         <v>99118</v>
@@ -18415,20 +18372,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Väst Sothällen, Vstm</t>
+          <t>Grotten OSO, Vstm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>564140</v>
+        <v>563655</v>
       </c>
       <c r="R158" t="n">
-        <v>6626788</v>
+        <v>6626789</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18452,12 +18425,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18466,34 +18439,31 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>Äldre barrskog,</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>122485589</v>
+        <v>121229232</v>
       </c>
       <c r="B159" t="n">
         <v>99118</v>
@@ -18521,17 +18491,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Väst Sothällen, Vstm</t>
+          <t>Grotten, SO (knärot2), Vstm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>563487</v>
+        <v>563403</v>
       </c>
       <c r="R159" t="n">
-        <v>6626901</v>
+        <v>6626849</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -18556,14 +18542,24 @@
           <t>Ramnäs</t>
         </is>
       </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>U-Sur-0787</t>
+        </is>
+      </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>X(10) 1 m2, A::211/364 (10) 1 m2</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18572,34 +18568,30 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>Äldre barrskog, frisk blåb.typ</t>
-        </is>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126857867</v>
+        <v>121229337</v>
       </c>
       <c r="B160" t="n">
         <v>99118</v>
@@ -18629,31 +18621,27 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Grotten, SO (knärot3), Vstm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>564098</v>
+        <v>563455</v>
       </c>
       <c r="R160" t="n">
-        <v>6626697</v>
+        <v>6626817</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18678,14 +18666,24 @@
           <t>Ramnäs</t>
         </is>
       </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>U-Sur-0786</t>
+        </is>
+      </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>8 stjälkar i blom</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18700,13 +18698,13 @@
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>Barrblandskog, lövinslag</t>
+          <t>gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
@@ -18714,11 +18712,15 @@
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY160" t="inlineStr"/>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126857945</v>
+        <v>122485588</v>
       </c>
       <c r="B161" t="n">
         <v>99118</v>
@@ -18746,36 +18748,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Väst Sothällen, Vstm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>563581</v>
+        <v>564140</v>
       </c>
       <c r="R161" t="n">
-        <v>6626826</v>
+        <v>6626788</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18799,12 +18785,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18813,31 +18799,34 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>Barrblandskog, lövinslag</t>
+          <t>Äldre barrskog,</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY161" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126857966</v>
+        <v>122485589</v>
       </c>
       <c r="B162" t="n">
         <v>99118</v>
@@ -18865,36 +18854,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Väst Sothällen, Vstm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>563562</v>
+        <v>563487</v>
       </c>
       <c r="R162" t="n">
-        <v>6626774</v>
+        <v>6626901</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18918,12 +18891,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18932,31 +18905,34 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>Barrblandskog, lövinslag</t>
+          <t>Äldre barrskog, frisk blåb.typ</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY162" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126882851</v>
+        <v>126857867</v>
       </c>
       <c r="B163" t="n">
         <v>99118</v>
@@ -18984,8 +18960,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K163" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -18995,17 +18979,17 @@
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>564111</v>
+        <v>564098</v>
       </c>
       <c r="R163" t="n">
-        <v>6626656</v>
+        <v>6626697</v>
       </c>
       <c r="S163" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -19029,17 +19013,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>spridda förekomster.</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19054,12 +19033,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Barrblandskog, lövinslag</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -19070,14 +19044,14 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Tom Sävström, Bertil Svensson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127689849</v>
+        <v>126857945</v>
       </c>
       <c r="B164" t="n">
         <v>99118</v>
@@ -19112,10 +19086,14 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
@@ -19124,10 +19102,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>563681</v>
+        <v>563581</v>
       </c>
       <c r="R164" t="n">
-        <v>6626774</v>
+        <v>6626826</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19154,12 +19132,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19174,7 +19152,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Barrblandskog, lövinslag</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -19192,53 +19170,61 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>109874946</v>
+        <v>126857966</v>
       </c>
       <c r="B165" t="n">
-        <v>106156</v>
+        <v>99118</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>221141</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Grotten OSO, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>563484</v>
+        <v>563562</v>
       </c>
       <c r="R165" t="n">
-        <v>6626755</v>
+        <v>6626774</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19265,12 +19251,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19285,7 +19271,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>Skogsbilväg, gräsmark</t>
+          <t>Barrblandskog, lövinslag</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -19303,47 +19289,39 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>89004606</v>
+        <v>126882851</v>
       </c>
       <c r="B166" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L166" t="inlineStr"/>
@@ -19354,13 +19332,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>564070</v>
+        <v>564111</v>
       </c>
       <c r="R166" t="n">
-        <v>6626692</v>
+        <v>6626656</v>
       </c>
       <c r="S166" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19384,12 +19362,17 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>spridda förekomster.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19404,7 +19387,12 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
@@ -19415,68 +19403,64 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Tom Sävström, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>103555656</v>
+        <v>127689849</v>
       </c>
       <c r="B167" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>564017</v>
+        <v>563681</v>
       </c>
       <c r="R167" t="n">
-        <v>6626678</v>
+        <v>6626774</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19503,17 +19487,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Två stänglar.</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19528,7 +19507,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
@@ -19546,10 +19525,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>103555693</v>
+        <v>109874946</v>
       </c>
       <c r="B168" t="n">
-        <v>106244</v>
+        <v>106156</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19557,50 +19536,42 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>221144</v>
+        <v>221141</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Grotten OSO, Vstm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>564079</v>
+        <v>563484</v>
       </c>
       <c r="R168" t="n">
-        <v>6626693</v>
+        <v>6626755</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19627,17 +19598,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>1 stängel.</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19652,7 +19618,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Skogsbilväg, gräsmark</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -19670,7 +19636,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>103591055</v>
+        <v>89004606</v>
       </c>
       <c r="B169" t="n">
         <v>106244</v>
@@ -19700,7 +19666,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -19717,17 +19683,17 @@
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Grotten O, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563487</v>
+        <v>564070</v>
       </c>
       <c r="R169" t="n">
-        <v>6626863</v>
+        <v>6626692</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19751,17 +19717,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Minst. I två delförekomster, 4 m emellan bestånden, 60+20. 13 överblommade stänglar. I mossa och barrförna i anslutning till gran.</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19776,7 +19737,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -19794,7 +19755,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>109874925</v>
+        <v>103555656</v>
       </c>
       <c r="B170" t="n">
         <v>106244</v>
@@ -19824,7 +19785,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -19841,14 +19802,14 @@
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Grotten OSO, Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>563484</v>
+        <v>564017</v>
       </c>
       <c r="R170" t="n">
-        <v>6626805</v>
+        <v>6626678</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19875,12 +19836,17 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Två stänglar.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19913,7 +19879,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>118725958</v>
+        <v>103555693</v>
       </c>
       <c r="B171" t="n">
         <v>106244</v>
@@ -19943,7 +19909,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -19960,14 +19926,14 @@
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>563678</v>
+        <v>564079</v>
       </c>
       <c r="R171" t="n">
-        <v>6626862</v>
+        <v>6626693</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19994,12 +19960,17 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>1 stängel.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20032,7 +20003,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>122485585</v>
+        <v>103591055</v>
       </c>
       <c r="B172" t="n">
         <v>106244</v>
@@ -20060,20 +20031,36 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Väst Sothällen, Vstm</t>
+          <t>Grotten O, Vstm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>564155</v>
+        <v>563487</v>
       </c>
       <c r="R172" t="n">
-        <v>6626751</v>
+        <v>6626863</v>
       </c>
       <c r="S172" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -20097,12 +20084,17 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>Minst. I två delförekomster, 4 m emellan bestånden, 60+20. 13 överblommade stänglar. I mossa och barrförna i anslutning till gran.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20111,37 +20103,34 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrblandskog</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY172" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>7287698</v>
+        <v>109874925</v>
       </c>
       <c r="B173" t="n">
-        <v>97989</v>
+        <v>106244</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20149,34 +20138,50 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Grotten O, Vstm</t>
+          <t>Grotten OSO, Vstm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>563938</v>
+        <v>563484</v>
       </c>
       <c r="R173" t="n">
-        <v>6626957</v>
+        <v>6626805</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20203,12 +20208,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2014-05-08</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2014-05-08</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20217,12 +20222,13 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>Ledningsgata</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -20240,10 +20246,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>4225741</v>
+        <v>118725958</v>
       </c>
       <c r="B174" t="n">
-        <v>97983</v>
+        <v>106244</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20251,37 +20257,53 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Grottenskogen, Ramnäs sn, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>564127</v>
+        <v>563678</v>
       </c>
       <c r="R174" t="n">
-        <v>6626915</v>
+        <v>6626862</v>
       </c>
       <c r="S174" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -20305,12 +20327,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2012-11-12</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2012-11-12</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20319,33 +20341,34 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>Kraftledningsgata, barrblandskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>7287861</v>
+        <v>122485585</v>
       </c>
       <c r="B175" t="n">
-        <v>97983</v>
+        <v>106244</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20353,37 +20376,37 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Grotten O, Vstm</t>
+          <t>Väst Sothällen, Vstm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>563843</v>
+        <v>564155</v>
       </c>
       <c r="R175" t="n">
-        <v>6626958</v>
+        <v>6626751</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -20407,12 +20430,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2014-05-08</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2014-05-08</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20426,28 +20449,32 @@
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>Ledningsgata</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY175" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>7287871</v>
+        <v>134585563</v>
       </c>
       <c r="B176" t="n">
-        <v>97983</v>
+        <v>106199</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20455,37 +20482,41 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>221945</v>
+        <v>221154</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lysimachia europaea</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) U. Manns &amp; Anderb.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Grotten O, Vstm</t>
+          <t>Sothälls linjegata, Vstm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>563597</v>
+        <v>564037</v>
       </c>
       <c r="R176" t="n">
-        <v>6626967</v>
+        <v>6626951</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20509,12 +20540,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2014-05-08</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2014-05-08</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20523,12 +20554,13 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>Ledningsgata</t>
+          <t>Kärr i linjegata</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -20546,10 +20578,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>112141153</v>
+        <v>134585603</v>
       </c>
       <c r="B177" t="n">
-        <v>97983</v>
+        <v>106358</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20557,16 +20589,16 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>221945</v>
+        <v>221157</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -20581,17 +20613,17 @@
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothälls linjegata, Vstm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>563684</v>
+        <v>564037</v>
       </c>
       <c r="R177" t="n">
-        <v>6626952</v>
+        <v>6626951</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20615,12 +20647,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20635,7 +20667,7 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>Barrblandskog, renlavshällar</t>
+          <t>Kärr i linjegata</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -20653,10 +20685,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>118726322</v>
+        <v>134585560</v>
       </c>
       <c r="B178" t="n">
-        <v>97983</v>
+        <v>107695</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20664,16 +20696,16 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>221945</v>
+        <v>221705</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Melampyrum pratense</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -20683,19 +20715,23 @@
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothälls linjegata, Vstm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>563336</v>
+        <v>564037</v>
       </c>
       <c r="R178" t="n">
-        <v>6626866</v>
+        <v>6626951</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -20722,12 +20758,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20742,7 +20778,7 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Kärr i linjegata</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr"/>
@@ -20760,10 +20796,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120496678</v>
+        <v>7287698</v>
       </c>
       <c r="B179" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20771,16 +20807,16 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -20788,36 +20824,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Naddtorpsskogen, Naddtorpsskogen, Vstm</t>
+          <t>Grotten O, Vstm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>564098</v>
+        <v>563938</v>
       </c>
       <c r="R179" t="n">
-        <v>6626756</v>
+        <v>6626957</v>
       </c>
       <c r="S179" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20841,22 +20861,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2014-05-08</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2014-05-08</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20865,34 +20875,33 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
-      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>Ledningsgata</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>4251435</v>
+        <v>4225741</v>
       </c>
       <c r="B180" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20900,16 +20909,16 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -20991,10 +21000,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>7287699</v>
+        <v>7287861</v>
       </c>
       <c r="B181" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21002,16 +21011,16 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -21026,10 +21035,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>563938</v>
+        <v>563843</v>
       </c>
       <c r="R181" t="n">
-        <v>6626957</v>
+        <v>6626958</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21093,10 +21102,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>7287862</v>
+        <v>7287871</v>
       </c>
       <c r="B182" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21104,16 +21113,16 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -21128,10 +21137,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>563843</v>
+        <v>563597</v>
       </c>
       <c r="R182" t="n">
-        <v>6626958</v>
+        <v>6626967</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21195,10 +21204,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>7287872</v>
+        <v>112141153</v>
       </c>
       <c r="B183" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21206,16 +21215,16 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -21224,16 +21233,20 @@
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Grotten O, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>563597</v>
+        <v>563684</v>
       </c>
       <c r="R183" t="n">
-        <v>6626967</v>
+        <v>6626952</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21260,12 +21273,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2014-05-08</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2014-05-08</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21274,12 +21287,13 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>Ledningsgata</t>
+          <t>Barrblandskog, renlavshällar</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -21297,10 +21311,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>7287876</v>
+        <v>118726322</v>
       </c>
       <c r="B184" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21308,16 +21322,16 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -21326,19 +21340,23 @@
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Grotten O, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>563485</v>
+        <v>563336</v>
       </c>
       <c r="R184" t="n">
-        <v>6626966</v>
+        <v>6626866</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21362,17 +21380,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2014-05-08</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2014-05-08</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21381,12 +21394,13 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>Ledningsgata</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -21404,10 +21418,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>72976672</v>
+        <v>120496678</v>
       </c>
       <c r="B185" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21415,16 +21429,16 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -21432,24 +21446,36 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Naddtorpsskogen, Naddtorpsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>564075</v>
+        <v>564098</v>
       </c>
       <c r="R185" t="n">
-        <v>6626696</v>
+        <v>6626756</v>
       </c>
       <c r="S185" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21473,12 +21499,22 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2018-08-31</t>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2018-08-31</t>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21491,30 +21527,30 @@
       <c r="AG185" t="b">
         <v>0</v>
       </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>Äldre mossig barrblandskog, inslag av löv</t>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>89004760</v>
+        <v>134585732</v>
       </c>
       <c r="B186" t="n">
-        <v>97986</v>
+        <v>98060</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21522,16 +21558,16 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -21546,17 +21582,17 @@
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Sothälls linjegata, Vstm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>564143</v>
+        <v>564131</v>
       </c>
       <c r="R186" t="n">
-        <v>6626719</v>
+        <v>6626911</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21580,12 +21616,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21600,7 +21636,7 @@
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Linjegata med gräs- och hällmark</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr"/>
@@ -21618,10 +21654,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>103588654</v>
+        <v>134585802</v>
       </c>
       <c r="B187" t="n">
-        <v>97986</v>
+        <v>98060</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21629,16 +21665,16 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -21653,17 +21689,17 @@
       <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Grotten OSO, Vstm</t>
+          <t>Sothälls linjegata, Vstm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>563809</v>
+        <v>564139</v>
       </c>
       <c r="R187" t="n">
-        <v>6626783</v>
+        <v>6626912</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21687,12 +21723,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21707,7 +21743,7 @@
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Fuktstråk i linjegata</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr"/>
@@ -21725,10 +21761,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>111875539</v>
+        <v>134585922</v>
       </c>
       <c r="B188" t="n">
-        <v>97986</v>
+        <v>98060</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21736,16 +21772,16 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -21760,17 +21796,17 @@
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Grotten OSO, Vstm</t>
+          <t>Sothälls linjegata, Vstm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>563670</v>
+        <v>564164</v>
       </c>
       <c r="R188" t="n">
-        <v>6626863</v>
+        <v>6626900</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21794,12 +21830,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21814,7 +21850,7 @@
       </c>
       <c r="AI188" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Fuktstråk i linjegata</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr"/>
@@ -21832,7 +21868,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>112141064</v>
+        <v>4251435</v>
       </c>
       <c r="B189" t="n">
         <v>97986</v>
@@ -21861,23 +21897,19 @@
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Grottenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>563824</v>
+        <v>564127</v>
       </c>
       <c r="R189" t="n">
-        <v>6626769</v>
+        <v>6626915</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21901,12 +21933,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2012-11-12</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2012-11-12</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21915,36 +21947,30 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
-      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
       <c r="AI189" t="inlineStr">
         <is>
-          <t>Barrblandskog, renlavshällar</t>
-        </is>
-      </c>
-      <c r="AO189" t="inlineStr">
-        <is>
-          <t>på trampad renlavshäll</t>
+          <t>Kraftledningsgata, barrblandskog</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>112141158</v>
+        <v>7287699</v>
       </c>
       <c r="B190" t="n">
         <v>97986</v>
@@ -21973,20 +21999,16 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Grotten O, Vstm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>563654</v>
+        <v>563938</v>
       </c>
       <c r="R190" t="n">
-        <v>6626930</v>
+        <v>6626957</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -22013,12 +22035,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2014-05-08</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2014-05-08</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22027,13 +22049,12 @@
       <c r="AE190" t="b">
         <v>0</v>
       </c>
-      <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
       <c r="AI190" t="inlineStr">
         <is>
-          <t>Barrblandskog, renlavshällar</t>
+          <t>Ledningsgata</t>
         </is>
       </c>
       <c r="AT190" t="inlineStr"/>
@@ -22051,7 +22072,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>112141175</v>
+        <v>7287862</v>
       </c>
       <c r="B191" t="n">
         <v>97986</v>
@@ -22080,20 +22101,16 @@
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Grotten O, Vstm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>563473</v>
+        <v>563843</v>
       </c>
       <c r="R191" t="n">
-        <v>6626952</v>
+        <v>6626958</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -22120,12 +22137,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2014-05-08</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2014-05-08</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22134,13 +22151,12 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
-      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>Barrblandskog, renlavshällar</t>
+          <t>Ledningsgata</t>
         </is>
       </c>
       <c r="AT191" t="inlineStr"/>
@@ -22158,7 +22174,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>118725918</v>
+        <v>7287872</v>
       </c>
       <c r="B192" t="n">
         <v>97986</v>
@@ -22187,20 +22203,16 @@
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Grotten O, Vstm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>563403</v>
+        <v>563597</v>
       </c>
       <c r="R192" t="n">
-        <v>6626849</v>
+        <v>6626967</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -22227,12 +22239,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2014-05-08</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2014-05-08</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22241,13 +22253,12 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>Fuktig blandskog</t>
+          <t>Ledningsgata</t>
         </is>
       </c>
       <c r="AT192" t="inlineStr"/>
@@ -22265,7 +22276,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>118725977</v>
+        <v>7287876</v>
       </c>
       <c r="B193" t="n">
         <v>97986</v>
@@ -22294,20 +22305,16 @@
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Grotten O, Vstm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>563678</v>
+        <v>563485</v>
       </c>
       <c r="R193" t="n">
-        <v>6626862</v>
+        <v>6626966</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22334,12 +22341,17 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2014-05-08</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2014-05-08</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22348,13 +22360,12 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Ledningsgata</t>
         </is>
       </c>
       <c r="AT193" t="inlineStr"/>
@@ -22372,10 +22383,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>4951641</v>
+        <v>72976672</v>
       </c>
       <c r="B194" t="n">
-        <v>101326</v>
+        <v>97986</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22383,37 +22394,41 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Sothällen SV (linja), Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>564244</v>
+        <v>564075</v>
       </c>
       <c r="R194" t="n">
-        <v>6626786</v>
+        <v>6626696</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -22437,12 +22452,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2011-06-08</t>
+          <t>2018-08-31</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2011-06-08</t>
+          <t>2018-08-31</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22451,12 +22466,13 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>Linjegata, örtrik, enbuskar, lövsly, omgiven av barrblandskog.</t>
+          <t>Äldre mossig barrblandskog, inslag av löv</t>
         </is>
       </c>
       <c r="AT194" t="inlineStr"/>
@@ -22474,10 +22490,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>54881151</v>
+        <v>89004760</v>
       </c>
       <c r="B195" t="n">
-        <v>101326</v>
+        <v>97986</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22485,37 +22501,38 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>564237</v>
+        <v>564143</v>
       </c>
       <c r="R195" t="n">
-        <v>6626785</v>
+        <v>6626719</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22542,12 +22559,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2015-08-19</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2015-08-19</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22556,12 +22573,13 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
       <c r="AI195" t="inlineStr">
         <is>
-          <t>Blandskog, rörligt markvatten, sumpskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT195" t="inlineStr"/>
@@ -22579,10 +22597,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>103555558</v>
+        <v>103588654</v>
       </c>
       <c r="B196" t="n">
-        <v>101326</v>
+        <v>97986</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22590,42 +22608,38 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Grotten OSO, Vstm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>564211</v>
+        <v>563809</v>
       </c>
       <c r="R196" t="n">
-        <v>6626792</v>
+        <v>6626783</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22652,12 +22666,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22672,7 +22686,7 @@
       </c>
       <c r="AI196" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT196" t="inlineStr"/>
@@ -22690,10 +22704,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>118725057</v>
+        <v>111875539</v>
       </c>
       <c r="B197" t="n">
-        <v>101326</v>
+        <v>97986</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22701,21 +22715,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -22725,17 +22739,17 @@
       <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Grotten OSO, Vstm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>564243</v>
+        <v>563670</v>
       </c>
       <c r="R197" t="n">
-        <v>6626780</v>
+        <v>6626863</v>
       </c>
       <c r="S197" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -22759,12 +22773,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22779,7 +22793,7 @@
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>Örtrik blandskog</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT197" t="inlineStr"/>
@@ -22797,10 +22811,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122485586</v>
+        <v>112141064</v>
       </c>
       <c r="B198" t="n">
-        <v>101326</v>
+        <v>97986</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22808,37 +22822,41 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Väst Sothällen, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>564170</v>
+        <v>563824</v>
       </c>
       <c r="R198" t="n">
-        <v>6626836</v>
+        <v>6626769</v>
       </c>
       <c r="S198" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -22862,12 +22880,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22876,37 +22894,39 @@
       <c r="AE198" t="b">
         <v>0</v>
       </c>
+      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
       <c r="AI198" t="inlineStr">
         <is>
-          <t>Äldre barrskog, fuktstråk</t>
+          <t>Barrblandskog, renlavshällar</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>på trampad renlavshäll</t>
         </is>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY198" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>123809320</v>
+        <v>112141158</v>
       </c>
       <c r="B199" t="n">
-        <v>101326</v>
+        <v>97986</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22914,30 +22934,26 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
       <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
@@ -22946,10 +22962,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>564165</v>
+        <v>563654</v>
       </c>
       <c r="R199" t="n">
-        <v>6626834</v>
+        <v>6626930</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22976,12 +22992,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22996,7 +23012,7 @@
       </c>
       <c r="AI199" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog, översilning</t>
+          <t>Barrblandskog, renlavshällar</t>
         </is>
       </c>
       <c r="AT199" t="inlineStr"/>
@@ -23014,57 +23030,52 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>5764341</v>
+        <v>112141175</v>
       </c>
       <c r="B200" t="n">
-        <v>103403</v>
+        <v>97986</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>223246</v>
+        <v>221946</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>564248</v>
+        <v>563473</v>
       </c>
       <c r="R200" t="n">
-        <v>6626782</v>
+        <v>6626952</v>
       </c>
       <c r="S200" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -23088,12 +23099,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2011-06-08</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2011-06-08</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23102,12 +23113,13 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>Blandskog, örtrik, luckig</t>
+          <t>Barrblandskog, renlavshällar</t>
         </is>
       </c>
       <c r="AT200" t="inlineStr"/>
@@ -23125,52 +23137,49 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>54880974</v>
+        <v>118725918</v>
       </c>
       <c r="B201" t="n">
-        <v>103403</v>
+        <v>97986</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>223246</v>
+        <v>221946</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>564237</v>
+        <v>563403</v>
       </c>
       <c r="R201" t="n">
-        <v>6626785</v>
+        <v>6626849</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -23197,12 +23206,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2015-08-19</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2015-08-19</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23211,8 +23220,14 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
+      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>Fuktig blandskog</t>
+        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
@@ -23229,57 +23244,49 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>72976736</v>
+        <v>118725977</v>
       </c>
       <c r="B202" t="n">
-        <v>103403</v>
+        <v>97986</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>223246</v>
+        <v>221946</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Sothällen VSV, Vstm</t>
+          <t>Sothällen V, Vstm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>564218</v>
+        <v>563678</v>
       </c>
       <c r="R202" t="n">
-        <v>6626766</v>
+        <v>6626862</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23306,17 +23313,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2018-08-31</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2018-08-31</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>Unbga buskformade plantor på övertäckt gammal soptipp</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23331,7 +23333,7 @@
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT202" t="inlineStr"/>
@@ -23349,60 +23351,52 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>103555513</v>
+        <v>134585724</v>
       </c>
       <c r="B203" t="n">
-        <v>103403</v>
+        <v>98063</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>223246</v>
+        <v>221946</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Sothälls linjegata, Vstm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>564211</v>
+        <v>564131</v>
       </c>
       <c r="R203" t="n">
-        <v>6626792</v>
+        <v>6626911</v>
       </c>
       <c r="S203" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -23426,17 +23420,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>Friskt träd, 150 cm omkrets.</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23451,7 +23440,7 @@
       </c>
       <c r="AI203" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Linjegata med gräs- och hällmark</t>
         </is>
       </c>
       <c r="AT203" t="inlineStr"/>
@@ -23469,32 +23458,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>118725050</v>
+        <v>134585911</v>
       </c>
       <c r="B204" t="n">
-        <v>103403</v>
+        <v>98063</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>223246</v>
+        <v>221946</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -23504,14 +23493,14 @@
       <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothälls linjegata, Vstm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>564243</v>
+        <v>564164</v>
       </c>
       <c r="R204" t="n">
-        <v>6626780</v>
+        <v>6626900</v>
       </c>
       <c r="S204" t="n">
         <v>25</v>
@@ -23538,12 +23527,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23558,7 +23547,7 @@
       </c>
       <c r="AI204" t="inlineStr">
         <is>
-          <t>Örtrik blandskog</t>
+          <t>Fuktstråk i linjegata</t>
         </is>
       </c>
       <c r="AT204" t="inlineStr"/>
@@ -23576,10 +23565,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>7287869</v>
+        <v>134585463</v>
       </c>
       <c r="B205" t="n">
-        <v>99038</v>
+        <v>103764</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23587,38 +23576,41 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>223597</v>
+        <v>222004</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr"/>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I205" t="inlineStr"/>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Grotten O, Vstm</t>
+          <t>Sothälls linjegata, Vstm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>563843</v>
+        <v>564037</v>
       </c>
       <c r="R205" t="n">
-        <v>6626958</v>
+        <v>6626951</v>
       </c>
       <c r="S205" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -23642,12 +23634,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2014-05-08</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2014-05-08</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23656,12 +23648,13 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
+      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
       <c r="AI205" t="inlineStr">
         <is>
-          <t>Ledningsgata</t>
+          <t>Kärr i linjegata</t>
         </is>
       </c>
       <c r="AT205" t="inlineStr"/>
@@ -23679,10 +23672,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>118724731</v>
+        <v>134585830</v>
       </c>
       <c r="B206" t="n">
-        <v>99038</v>
+        <v>103764</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23690,41 +23683,41 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>223597</v>
+        <v>222004</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr"/>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothälls linjegata, Vstm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>564069</v>
+        <v>564139</v>
       </c>
       <c r="R206" t="n">
-        <v>6626755</v>
+        <v>6626912</v>
       </c>
       <c r="S206" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -23748,12 +23741,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23768,7 +23761,7 @@
       </c>
       <c r="AI206" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Fuktstråk i linjegata</t>
         </is>
       </c>
       <c r="AT206" t="inlineStr"/>
@@ -23786,10 +23779,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>118724826</v>
+        <v>134585443</v>
       </c>
       <c r="B207" t="n">
-        <v>99038</v>
+        <v>99853</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23797,41 +23790,45 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>223597</v>
+        <v>222306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Stjärnstarr</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr"/>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothälls linjegata, Vstm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>564170</v>
+        <v>564037</v>
       </c>
       <c r="R207" t="n">
-        <v>6626785</v>
+        <v>6626951</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -23855,12 +23852,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23875,7 +23872,7 @@
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>Fuktig blandskog</t>
+          <t>Kärr i linjegata</t>
         </is>
       </c>
       <c r="AT207" t="inlineStr"/>
@@ -23893,10 +23890,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>118725694</v>
+        <v>134585859</v>
       </c>
       <c r="B208" t="n">
-        <v>99038</v>
+        <v>99853</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23904,37 +23901,45 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>223597</v>
+        <v>222306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Stjärnstarr</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr"/>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothälls linjegata, Vstm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>564010</v>
+        <v>564139</v>
       </c>
       <c r="R208" t="n">
-        <v>6626775</v>
+        <v>6626912</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -23958,12 +23963,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23978,7 +23983,7 @@
       </c>
       <c r="AI208" t="inlineStr">
         <is>
-          <t>Fuktig blandskog</t>
+          <t>Fuktstråk i linjegata</t>
         </is>
       </c>
       <c r="AT208" t="inlineStr"/>
@@ -23996,10 +24001,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>118725875</v>
+        <v>4951641</v>
       </c>
       <c r="B209" t="n">
-        <v>99038</v>
+        <v>101326</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24007,45 +24012,37 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>223597</v>
+        <v>222498</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr"/>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothällen SV (linja), Vstm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>563367</v>
+        <v>564244</v>
       </c>
       <c r="R209" t="n">
-        <v>6626884</v>
+        <v>6626786</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -24069,12 +24066,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2011-06-08</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2011-06-08</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -24083,13 +24080,12 @@
       <c r="AE209" t="b">
         <v>0</v>
       </c>
-      <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="b">
         <v>0</v>
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>Fuktig blandskog</t>
+          <t>Linjegata, örtrik, enbuskar, lövsly, omgiven av barrblandskog.</t>
         </is>
       </c>
       <c r="AT209" t="inlineStr"/>
@@ -24107,10 +24103,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>118726341</v>
+        <v>54881151</v>
       </c>
       <c r="B210" t="n">
-        <v>99038</v>
+        <v>101326</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24118,41 +24114,40 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>223597</v>
+        <v>222498</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Sothällen V, Vstm</t>
+          <t>Sothällen VSV, Vstm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>563336</v>
+        <v>564237</v>
       </c>
       <c r="R210" t="n">
-        <v>6626866</v>
+        <v>6626785</v>
       </c>
       <c r="S210" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -24176,12 +24171,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2015-08-19</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2015-08-19</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24190,13 +24185,12 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
-      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AI210" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blandskog, rörligt markvatten, sumpskog</t>
         </is>
       </c>
       <c r="AT210" t="inlineStr"/>
@@ -24214,44 +24208,56 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122485584</v>
+        <v>103555558</v>
       </c>
       <c r="B211" t="n">
-        <v>103404</v>
+        <v>101326</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>225046</v>
+        <v>222498</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Väst Sothällen, Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>564245</v>
+        <v>564211</v>
       </c>
       <c r="R211" t="n">
-        <v>6626786</v>
+        <v>6626792</v>
       </c>
       <c r="S211" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -24275,17 +24281,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>diam. ca 45 cm</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24300,21 +24301,2398 @@
       </c>
       <c r="AI211" t="inlineStr">
         <is>
-          <t>Barrskog lövinslag, fuktstråk</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>118725057</v>
+      </c>
+      <c r="B212" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>564243</v>
+      </c>
+      <c r="R212" t="n">
+        <v>6626780</v>
+      </c>
+      <c r="S212" t="n">
+        <v>25</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AD212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF212" t="inlineStr"/>
+      <c r="AG212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>Örtrik blandskog</t>
+        </is>
+      </c>
+      <c r="AT212" t="inlineStr"/>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>122485586</v>
+      </c>
+      <c r="B213" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Väst Sothällen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>564170</v>
+      </c>
+      <c r="R213" t="n">
+        <v>6626836</v>
+      </c>
+      <c r="S213" t="n">
+        <v>25</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>Äldre barrskog, fuktstråk</t>
+        </is>
+      </c>
+      <c r="AT213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr">
+        <is>
           <t>Aivars Dunskis</t>
         </is>
       </c>
-      <c r="AX211" t="inlineStr">
+      <c r="AX213" t="inlineStr">
         <is>
           <t>Tommy Pettersson</t>
         </is>
       </c>
-      <c r="AY211" t="inlineStr">
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>123809320</v>
+      </c>
+      <c r="B214" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>564165</v>
+      </c>
+      <c r="R214" t="n">
+        <v>6626834</v>
+      </c>
+      <c r="S214" t="n">
+        <v>10</v>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AD214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF214" t="inlineStr"/>
+      <c r="AG214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog, översilning</t>
+        </is>
+      </c>
+      <c r="AT214" t="inlineStr"/>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>134585822</v>
+      </c>
+      <c r="B215" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Sothälls linjegata, Vstm</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>564139</v>
+      </c>
+      <c r="R215" t="n">
+        <v>6626912</v>
+      </c>
+      <c r="S215" t="n">
+        <v>25</v>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF215" t="inlineStr"/>
+      <c r="AG215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>Fuktstråk i linjegata</t>
+        </is>
+      </c>
+      <c r="AT215" t="inlineStr"/>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>134585741</v>
+      </c>
+      <c r="B216" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Sothälls linjegata, Vstm</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>564131</v>
+      </c>
+      <c r="R216" t="n">
+        <v>6626911</v>
+      </c>
+      <c r="S216" t="n">
+        <v>25</v>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF216" t="inlineStr"/>
+      <c r="AG216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>Linjegata med gräs- och hällmark</t>
+        </is>
+      </c>
+      <c r="AT216" t="inlineStr"/>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>5764341</v>
+      </c>
+      <c r="B217" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Sothällen SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>564248</v>
+      </c>
+      <c r="R217" t="n">
+        <v>6626782</v>
+      </c>
+      <c r="S217" t="n">
+        <v>5</v>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>2011-06-08</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>2011-06-08</t>
+        </is>
+      </c>
+      <c r="AD217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>Blandskog, örtrik, luckig</t>
+        </is>
+      </c>
+      <c r="AT217" t="inlineStr"/>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>54880974</v>
+      </c>
+      <c r="B218" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Sothällen VSV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>564237</v>
+      </c>
+      <c r="R218" t="n">
+        <v>6626785</v>
+      </c>
+      <c r="S218" t="n">
+        <v>10</v>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>2015-08-19</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>2015-08-19</t>
+        </is>
+      </c>
+      <c r="AD218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT218" t="inlineStr"/>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>72976736</v>
+      </c>
+      <c r="B219" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Sothällen VSV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>564218</v>
+      </c>
+      <c r="R219" t="n">
+        <v>6626766</v>
+      </c>
+      <c r="S219" t="n">
+        <v>10</v>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>2018-08-31</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>2018-08-31</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Unbga buskformade plantor på övertäckt gammal soptipp</t>
+        </is>
+      </c>
+      <c r="AD219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF219" t="inlineStr"/>
+      <c r="AG219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT219" t="inlineStr"/>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>103555513</v>
+      </c>
+      <c r="B220" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Sothällen SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>564211</v>
+      </c>
+      <c r="R220" t="n">
+        <v>6626792</v>
+      </c>
+      <c r="S220" t="n">
+        <v>10</v>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>Friskt träd, 150 cm omkrets.</t>
+        </is>
+      </c>
+      <c r="AD220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF220" t="inlineStr"/>
+      <c r="AG220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT220" t="inlineStr"/>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>118725050</v>
+      </c>
+      <c r="B221" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>564243</v>
+      </c>
+      <c r="R221" t="n">
+        <v>6626780</v>
+      </c>
+      <c r="S221" t="n">
+        <v>25</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AD221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF221" t="inlineStr"/>
+      <c r="AG221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>Örtrik blandskog</t>
+        </is>
+      </c>
+      <c r="AT221" t="inlineStr"/>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>134585787</v>
+      </c>
+      <c r="B222" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Sothälls linjegata, Vstm</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>564139</v>
+      </c>
+      <c r="R222" t="n">
+        <v>6626912</v>
+      </c>
+      <c r="S222" t="n">
+        <v>25</v>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF222" t="inlineStr"/>
+      <c r="AG222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>Fuktstråk i linjegata</t>
+        </is>
+      </c>
+      <c r="AT222" t="inlineStr"/>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>7287869</v>
+      </c>
+      <c r="B223" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Grotten O, Vstm</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>563843</v>
+      </c>
+      <c r="R223" t="n">
+        <v>6626958</v>
+      </c>
+      <c r="S223" t="n">
+        <v>10</v>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>2014-05-08</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>2014-05-08</t>
+        </is>
+      </c>
+      <c r="AD223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>Ledningsgata</t>
+        </is>
+      </c>
+      <c r="AT223" t="inlineStr"/>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>118724731</v>
+      </c>
+      <c r="B224" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>564069</v>
+      </c>
+      <c r="R224" t="n">
+        <v>6626755</v>
+      </c>
+      <c r="S224" t="n">
+        <v>10</v>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AD224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF224" t="inlineStr"/>
+      <c r="AG224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT224" t="inlineStr"/>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>118724826</v>
+      </c>
+      <c r="B225" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>564170</v>
+      </c>
+      <c r="R225" t="n">
+        <v>6626785</v>
+      </c>
+      <c r="S225" t="n">
+        <v>10</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AD225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF225" t="inlineStr"/>
+      <c r="AG225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>Fuktig blandskog</t>
+        </is>
+      </c>
+      <c r="AT225" t="inlineStr"/>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>118725694</v>
+      </c>
+      <c r="B226" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>564010</v>
+      </c>
+      <c r="R226" t="n">
+        <v>6626775</v>
+      </c>
+      <c r="S226" t="n">
+        <v>10</v>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AD226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF226" t="inlineStr"/>
+      <c r="AG226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>Fuktig blandskog</t>
+        </is>
+      </c>
+      <c r="AT226" t="inlineStr"/>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>118725875</v>
+      </c>
+      <c r="B227" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>563367</v>
+      </c>
+      <c r="R227" t="n">
+        <v>6626884</v>
+      </c>
+      <c r="S227" t="n">
+        <v>10</v>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AD227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF227" t="inlineStr"/>
+      <c r="AG227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>Fuktig blandskog</t>
+        </is>
+      </c>
+      <c r="AT227" t="inlineStr"/>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>118726341</v>
+      </c>
+      <c r="B228" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Sothällen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>563336</v>
+      </c>
+      <c r="R228" t="n">
+        <v>6626866</v>
+      </c>
+      <c r="S228" t="n">
+        <v>25</v>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AD228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF228" t="inlineStr"/>
+      <c r="AG228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT228" t="inlineStr"/>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>134585542</v>
+      </c>
+      <c r="B229" t="n">
+        <v>99115</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Sothälls linjegata, Vstm</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>564037</v>
+      </c>
+      <c r="R229" t="n">
+        <v>6626951</v>
+      </c>
+      <c r="S229" t="n">
+        <v>25</v>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF229" t="inlineStr"/>
+      <c r="AG229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>Kärr i linjegata</t>
+        </is>
+      </c>
+      <c r="AT229" t="inlineStr"/>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>134585782</v>
+      </c>
+      <c r="B230" t="n">
+        <v>99115</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Sothälls linjegata, Vstm</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>564139</v>
+      </c>
+      <c r="R230" t="n">
+        <v>6626912</v>
+      </c>
+      <c r="S230" t="n">
+        <v>25</v>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF230" t="inlineStr"/>
+      <c r="AG230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>Fuktstråk i linjegata</t>
+        </is>
+      </c>
+      <c r="AT230" t="inlineStr"/>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>134585892</v>
+      </c>
+      <c r="B231" t="n">
+        <v>99115</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Sothälls linjegata, Vstm</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>564164</v>
+      </c>
+      <c r="R231" t="n">
+        <v>6626900</v>
+      </c>
+      <c r="S231" t="n">
+        <v>25</v>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF231" t="inlineStr"/>
+      <c r="AG231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>Fuktstråk i linjegata</t>
+        </is>
+      </c>
+      <c r="AT231" t="inlineStr"/>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>134585980</v>
+      </c>
+      <c r="B232" t="n">
+        <v>99115</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Sothälls linjegata, Vstm</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>564185</v>
+      </c>
+      <c r="R232" t="n">
+        <v>6626887</v>
+      </c>
+      <c r="S232" t="n">
+        <v>25</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF232" t="inlineStr"/>
+      <c r="AG232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>Gräsmark i linjegata</t>
+        </is>
+      </c>
+      <c r="AT232" t="inlineStr"/>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>122485584</v>
+      </c>
+      <c r="B233" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Väst Sothällen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>564245</v>
+      </c>
+      <c r="R233" t="n">
+        <v>6626786</v>
+      </c>
+      <c r="S233" t="n">
+        <v>25</v>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>diam. ca 45 cm</t>
+        </is>
+      </c>
+      <c r="AD233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF233" t="inlineStr"/>
+      <c r="AG233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>Barrskog lövinslag, fuktstråk</t>
+        </is>
+      </c>
+      <c r="AT233" t="inlineStr"/>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY233"/>
+  <dimension ref="A1:AZ233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555278</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111797162</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485582</t>
         </is>
       </c>
     </row>
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126882801</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/278339</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60760765</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485579</t>
         </is>
       </c>
     </row>
@@ -1560,6 +1600,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119359828</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128085081</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787685</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113126226</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89004574</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2120,6 +2185,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555275</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2231,6 +2301,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111797167</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2342,6 +2417,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126882807</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2453,6 +2533,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121247537</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2564,6 +2649,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123809435</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2678,6 +2768,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119653045</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2792,6 +2887,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111900029</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2911,6 +3011,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128361310</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3025,6 +3130,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118703238</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3139,6 +3249,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046076</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3253,6 +3368,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111899922</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3367,6 +3487,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111900116</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3481,6 +3606,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111900230</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3587,6 +3717,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112141141</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3701,6 +3836,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046002</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3815,6 +3955,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046033</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3929,6 +4074,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046036</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4035,6 +4185,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787448</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4147,6 +4302,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485583</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4252,6 +4412,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72976704</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4363,6 +4528,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555606</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4478,6 +4648,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1153846</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4584,6 +4759,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111798045</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4703,6 +4883,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118725673</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4809,6 +4994,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485581</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4923,6 +5113,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126857691</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5037,6 +5232,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126882697</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5151,6 +5351,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046184</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5270,6 +5475,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128361233</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5376,6 +5586,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111798037</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5490,6 +5705,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127689891</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5604,6 +5824,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555356</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5718,6 +5943,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555435</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5824,6 +6054,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103587679</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5930,6 +6165,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103588043</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6036,6 +6276,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111798024</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6142,6 +6387,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111899965</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6248,6 +6498,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111900122</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6354,6 +6609,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112141136</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6460,6 +6720,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112141142</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6571,6 +6836,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119652976</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6682,6 +6952,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119653000</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6788,6 +7063,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119653050</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6894,6 +7174,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485580</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7008,6 +7293,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127063850</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7122,6 +7412,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127063858</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7236,6 +7531,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127063878</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7350,6 +7650,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127063880</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7464,6 +7769,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046021</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7578,6 +7888,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046023</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7692,6 +8007,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046037</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7806,6 +8126,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046062</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7920,6 +8245,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046078</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8034,6 +8364,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046080</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8148,6 +8483,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046083</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8262,6 +8602,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046174</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8376,6 +8721,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046194</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8490,6 +8840,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128361338</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8596,6 +8951,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787454</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8702,6 +9062,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111798032</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8808,6 +9173,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112141097</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8923,6 +9293,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1444675</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9037,6 +9412,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046077</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9143,6 +9523,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128361366</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9249,6 +9634,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787519</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9360,6 +9750,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103587698</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9471,6 +9866,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112977390</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9582,6 +9982,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118726560</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9693,6 +10098,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111850232</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9802,6 +10212,11 @@
       <c r="AY83" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485578</t>
         </is>
       </c>
     </row>
@@ -9915,6 +10330,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046156</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10029,6 +10449,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126858024</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10135,6 +10560,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128361382</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10249,6 +10679,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112141001</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10363,6 +10798,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112141021</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10477,6 +10917,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112141150</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10583,6 +11028,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485576</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10697,6 +11147,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787422</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10811,6 +11266,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787432</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10925,6 +11385,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787523</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11041,6 +11506,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129182686</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11158,6 +11628,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111899773</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11270,6 +11745,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120495592</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11400,6 +11880,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126882773</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11507,6 +11992,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128074263</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11618,6 +12108,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555316</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11737,6 +12232,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72976664</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11856,6 +12356,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555750</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11975,6 +12480,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555783</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12099,6 +12609,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103591824</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12229,6 +12744,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104689769</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12353,6 +12873,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111850130</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12472,6 +12997,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111875136</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12591,6 +13121,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111875235</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12706,6 +13241,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111875274</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12825,6 +13365,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111875286</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12944,6 +13489,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111875305</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13063,6 +13613,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111875320</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13182,6 +13737,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111875333</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13301,6 +13861,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111875358</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13420,6 +13985,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111875425</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13539,6 +14109,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111875460</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13658,6 +14233,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111875522</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13777,6 +14357,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111899767</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13896,6 +14481,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112081924</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14015,6 +14605,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112141871</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14134,6 +14729,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112141910</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14245,6 +14845,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118405005</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14364,6 +14969,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118703452</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14488,6 +15098,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852324</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14607,6 +15222,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119653166</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14735,6 +15355,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121229232</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14864,6 +15489,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121229337</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14970,6 +15600,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485589</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15089,6 +15724,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126857945</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15208,6 +15848,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126857966</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15323,6 +15968,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127689849</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15434,6 +16084,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109874946</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15553,6 +16208,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89004606</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15677,6 +16337,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555656</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15801,6 +16466,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555693</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15925,6 +16595,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103591055</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16044,6 +16719,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109874925</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16163,6 +16843,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118725958</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16270,6 +16955,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585563</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16377,6 +17067,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585603</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16488,6 +17183,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585560</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16590,6 +17290,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7287698</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16692,6 +17397,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7287861</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16794,6 +17504,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7287871</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16901,6 +17616,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112141153</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17008,6 +17728,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118726322</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17110,6 +17835,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7287699</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17212,6 +17942,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7287862</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17314,6 +18049,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7287872</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17421,6 +18161,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7287876</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17528,6 +18273,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72976672</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17635,6 +18385,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103588654</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17742,6 +18497,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111875539</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17854,6 +18614,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112141064</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17961,6 +18726,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112141158</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18068,6 +18838,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112141175</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18175,6 +18950,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118725918</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18282,6 +19062,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118725977</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18389,6 +19174,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585463</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18500,6 +19290,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585443</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18603,6 +19398,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7287869</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18710,6 +19510,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118724731</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18813,6 +19618,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118725694</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18924,6 +19734,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118725875</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19031,6 +19846,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118726341</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19138,6 +19958,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585542</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19253,6 +20078,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73913557</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19368,6 +20198,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73913573</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19482,6 +20317,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046123</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19592,6 +20432,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128268019</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19698,6 +20543,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111797468</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19812,6 +20662,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128084971</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19917,6 +20772,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54881182</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20023,6 +20883,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787606</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20137,6 +21002,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555543</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20251,6 +21121,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046090</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20357,6 +21232,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555552</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20471,6 +21351,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046106</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20584,6 +21469,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54881222</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20695,6 +21585,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111797397</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20809,6 +21704,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111940136</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20923,6 +21823,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046128</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21034,6 +21939,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111797755</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21145,6 +22055,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128046112</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21251,6 +22166,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787660</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21365,6 +22285,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128084970</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21476,6 +22401,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89004773</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21607,6 +22537,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128073806</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21734,6 +22669,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120496305</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21845,6 +22785,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585918</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21956,6 +22901,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585976</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22067,6 +23017,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585710</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22169,6 +23124,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2595020</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22280,6 +23240,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118724975</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22391,6 +23356,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485587</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22510,6 +23480,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72976497</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22629,6 +23604,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72976505</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22748,6 +23728,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112977272</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22867,6 +23852,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118725553</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22991,6 +23981,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852333</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -23097,6 +24092,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485588</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -23216,6 +24216,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126857867</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23337,6 +24342,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126882851</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23443,6 +24453,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485585</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23545,6 +24560,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4225741</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23674,6 +24694,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120496678</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23781,6 +24806,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585732</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23888,6 +24918,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585802</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23995,6 +25030,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585922</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -24097,6 +25137,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4251435</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -24204,6 +25249,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89004760</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -24311,6 +25361,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585724</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24418,6 +25473,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585911</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24525,6 +25585,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585830</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24636,6 +25701,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585859</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24738,6 +25808,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4951641</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24843,6 +25918,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54881151</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24954,6 +26034,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555558</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -25061,6 +26146,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118725057</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -25167,6 +26257,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485586</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -25278,6 +26373,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123809320</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -25385,6 +26485,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585822</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -25492,6 +26597,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585741</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25603,6 +26713,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5764341</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25707,6 +26822,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54880974</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25827,6 +26947,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72976736</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25947,6 +27072,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555513</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -26054,6 +27184,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118725050</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -26161,6 +27296,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585787</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -26268,6 +27408,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118724826</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -26375,6 +27520,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585782</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26482,6 +27632,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585892</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26589,6 +27744,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134585980</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26697,8 +27857,247 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485584</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -3022,7 +3022,7 @@
         <v>118703238</v>
       </c>
       <c r="B22" t="n">
-        <v>91394</v>
+        <v>91533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -3022,7 +3022,7 @@
         <v>118703238</v>
       </c>
       <c r="B22" t="n">
-        <v>91533</v>
+        <v>91535</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -3022,7 +3022,7 @@
         <v>118703238</v>
       </c>
       <c r="B22" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -3022,7 +3022,7 @@
         <v>118703238</v>
       </c>
       <c r="B22" t="n">
-        <v>91536</v>
+        <v>91537</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -3022,7 +3022,7 @@
         <v>118703238</v>
       </c>
       <c r="B22" t="n">
-        <v>91537</v>
+        <v>91538</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -3022,7 +3022,7 @@
         <v>118703238</v>
       </c>
       <c r="B22" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -3022,7 +3022,7 @@
         <v>118703238</v>
       </c>
       <c r="B22" t="n">
-        <v>91544</v>
+        <v>91545</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -3022,7 +3022,7 @@
         <v>118703238</v>
       </c>
       <c r="B22" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -3022,7 +3022,7 @@
         <v>118703238</v>
       </c>
       <c r="B22" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -3022,7 +3022,7 @@
         <v>118703238</v>
       </c>
       <c r="B22" t="n">
-        <v>91558</v>
+        <v>91559</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -3022,7 +3022,7 @@
         <v>118703238</v>
       </c>
       <c r="B22" t="n">
-        <v>91559</v>
+        <v>91572</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -3022,7 +3022,7 @@
         <v>118703238</v>
       </c>
       <c r="B22" t="n">
-        <v>91572</v>
+        <v>91573</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
